--- a/comparison_bapa.xlsx
+++ b/comparison_bapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mudathir\all\sls-reachability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B101A1CF-342A-47C5-905B-11306966678B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8361F679-605C-4DCA-A272-9789CB069924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{43139118-C9B1-4C53-BA07-4D51B812E9BD}"/>
   </bookViews>
@@ -18,13 +18,13 @@
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="6" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1987" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="982">
   <si>
     <t>sls file</t>
   </si>
@@ -6951,8 +6951,270 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9C2B9FD1-8D62-45DD-A4E2-32DD8409B436}" name="PivotTable5" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="cvc5 sets results" colHeaderCaption="z3 results">
-  <location ref="A38:F43" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{1384F712-2556-4EB1-8339-9906247C6153}" name="PivotTable7" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="cvc5 sets results">
+  <location ref="A11:E16" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="7"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4BC8F53-2274-4AC0-86BC-064C65B395C4}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="cvc5 lia results">
+  <location ref="A19:D24" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="3">
+        <item x="0"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="10"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4FC8CDAD-3D92-4F0B-9E24-6C06120CE61E}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="z3 results">
+  <location ref="A3:F8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="5">
+        <item x="0"/>
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9C2B9FD1-8D62-45DD-A4E2-32DD8409B436}" name="PivotTable5" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="cvc5 sets results" colHeaderCaption="z3 results">
+  <location ref="A45:F50" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -7047,9 +7309,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD56A477-6F55-4B44-8764-ADBE83C4C0E6}" name="PivotTable4" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="cvc5 sets results" colHeaderCaption="cvc5 lia results">
-  <location ref="A29:D34" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD56A477-6F55-4B44-8764-ADBE83C4C0E6}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="cvc5 sets results" colHeaderCaption="cvc5 lia results">
+  <location ref="A36:D41" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -7138,9 +7400,9 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2FC91BDE-3A03-4BB4-88F7-FC6B1F14B00A}" name="PivotTable3" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="z3 results" colHeaderCaption="cvc5 lia results">
-  <location ref="A20:D26" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<file path=xl/pivotTables/pivotTable6.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2FC91BDE-3A03-4BB4-88F7-FC6B1F14B00A}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="z3 results" colHeaderCaption="cvc5 lia results">
+  <location ref="A27:D33" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField showAll="0">
@@ -7205,174 +7467,6 @@
     </i>
     <i>
       <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A4BC8F53-2274-4AC0-86BC-064C65B395C4}" name="PivotTable2" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="cvc5 lia results">
-  <location ref="A12:D17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="3">
-        <item x="0"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="10"/>
-  </colFields>
-  <colItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4FC8CDAD-3D92-4F0B-9E24-6C06120CE61E}" name="PivotTable1" cacheId="6" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="z3 results">
-  <location ref="A3:F8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="12">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="5">
-        <item x="0"/>
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="5">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
     </i>
     <i t="grand">
       <x/>
@@ -7731,15 +7825,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6651627E-A0CF-441C-976A-9DDF30242CC0}">
-  <dimension ref="A3:F43"/>
+  <dimension ref="A3:F50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="5.54296875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
@@ -7778,15 +7870,13 @@
       <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>110</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3">
+      <c r="D5">
         <v>6</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3">
+      <c r="F5">
         <v>116</v>
       </c>
     </row>
@@ -7794,19 +7884,19 @@
       <c r="A6" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>9</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D6">
         <v>40</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F6">
         <v>51</v>
       </c>
     </row>
@@ -7814,15 +7904,13 @@
       <c r="A7" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3">
+      <c r="D7">
         <v>4</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7">
         <v>69</v>
       </c>
-      <c r="F7" s="3">
+      <c r="F7">
         <v>73</v>
       </c>
     </row>
@@ -7830,361 +7918,442 @@
       <c r="A8" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>119</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8">
         <v>1</v>
       </c>
-      <c r="D8" s="3">
+      <c r="D8">
         <v>50</v>
       </c>
-      <c r="E8" s="3">
+      <c r="E8">
         <v>70</v>
       </c>
-      <c r="F8" s="3">
+      <c r="F8">
         <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>981</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>675</v>
+      </c>
+      <c r="D12" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" t="s">
+        <v>976</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>979</v>
-      </c>
-      <c r="B13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" t="s">
-        <v>976</v>
+      <c r="A13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="3">
+        <v>116</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3">
+        <v>116</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>675</v>
       </c>
       <c r="B14" s="3">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D14" s="3">
-        <v>116</v>
+        <v>17</v>
+      </c>
+      <c r="E14" s="3">
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B15" s="3">
-        <v>13</v>
-      </c>
-      <c r="C15" s="3">
-        <v>38</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
       <c r="D15" s="3">
-        <v>51</v>
+        <v>73</v>
+      </c>
+      <c r="E15" s="3">
+        <v>73</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B16" s="3"/>
+        <v>976</v>
+      </c>
+      <c r="B16" s="3">
+        <v>146</v>
+      </c>
       <c r="C16" s="3">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="D16" s="3">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="B17" s="3">
-        <v>128</v>
-      </c>
-      <c r="C17" s="3">
-        <v>112</v>
-      </c>
-      <c r="D17" s="3">
+        <v>90</v>
+      </c>
+      <c r="E16" s="3">
         <v>240</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>980</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
+      </c>
+      <c r="B20" t="s">
+        <v>13</v>
+      </c>
+      <c r="C20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" t="s">
+        <v>976</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
-        <v>978</v>
-      </c>
-      <c r="B21" t="s">
-        <v>13</v>
-      </c>
-      <c r="C21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D21" t="s">
-        <v>976</v>
+      <c r="A21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21">
+        <v>115</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>116</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B22" s="3">
-        <v>114</v>
-      </c>
-      <c r="C22" s="3">
-        <v>5</v>
-      </c>
-      <c r="D22" s="3">
-        <v>119</v>
+        <v>675</v>
+      </c>
+      <c r="B22">
+        <v>13</v>
+      </c>
+      <c r="C22">
+        <v>38</v>
+      </c>
+      <c r="D22">
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="B23" s="3">
-        <v>1</v>
-      </c>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3">
-        <v>1</v>
+        <v>94</v>
+      </c>
+      <c r="C23">
+        <v>73</v>
+      </c>
+      <c r="D23">
+        <v>73</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B24" s="3">
-        <v>13</v>
-      </c>
-      <c r="C24" s="3">
-        <v>37</v>
-      </c>
-      <c r="D24" s="3">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3">
-        <v>70</v>
-      </c>
-      <c r="D25" s="3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B24">
         <v>128</v>
       </c>
-      <c r="C26" s="3">
+      <c r="C24">
         <v>112</v>
       </c>
-      <c r="D26" s="3">
+      <c r="D24">
         <v>240</v>
       </c>
     </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C28" t="s">
+        <v>94</v>
+      </c>
+      <c r="D28" t="s">
+        <v>976</v>
+      </c>
+    </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>980</v>
+      <c r="A29" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B29">
+        <v>114</v>
+      </c>
+      <c r="C29">
+        <v>5</v>
+      </c>
+      <c r="D29">
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="B30" t="s">
-        <v>13</v>
-      </c>
-      <c r="C30" t="s">
-        <v>94</v>
-      </c>
-      <c r="D30" t="s">
-        <v>976</v>
+      <c r="A30" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="3">
-        <v>123</v>
-      </c>
-      <c r="C31" s="3">
-        <v>23</v>
-      </c>
-      <c r="D31" s="3">
-        <v>146</v>
+        <v>675</v>
+      </c>
+      <c r="B31">
+        <v>13</v>
+      </c>
+      <c r="C31">
+        <v>37</v>
+      </c>
+      <c r="D31">
+        <v>50</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B32" s="3">
-        <v>1</v>
-      </c>
-      <c r="C32" s="3">
-        <v>3</v>
-      </c>
-      <c r="D32" s="3">
-        <v>4</v>
+        <v>94</v>
+      </c>
+      <c r="C32">
+        <v>70</v>
+      </c>
+      <c r="D32">
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B33" s="3">
+        <v>976</v>
+      </c>
+      <c r="B33">
+        <v>128</v>
+      </c>
+      <c r="C33">
+        <v>112</v>
+      </c>
+      <c r="D33">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B37" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A38" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B38">
+        <v>123</v>
+      </c>
+      <c r="C38">
+        <v>23</v>
+      </c>
+      <c r="D38">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B39">
+        <v>1</v>
+      </c>
+      <c r="C39">
+        <v>3</v>
+      </c>
+      <c r="D39">
         <v>4</v>
-      </c>
-      <c r="C33" s="3">
-        <v>86</v>
-      </c>
-      <c r="D33" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>976</v>
-      </c>
-      <c r="B34" s="3">
-        <v>128</v>
-      </c>
-      <c r="C34" s="3">
-        <v>112</v>
-      </c>
-      <c r="D34" s="3">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="1" t="s">
-        <v>977</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="B39" t="s">
-        <v>13</v>
-      </c>
-      <c r="C39" t="s">
-        <v>821</v>
-      </c>
-      <c r="D39" t="s">
-        <v>675</v>
-      </c>
-      <c r="E39" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" t="s">
-        <v>976</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B40" s="3">
-        <v>116</v>
-      </c>
-      <c r="C40" s="3">
-        <v>1</v>
-      </c>
-      <c r="D40" s="3">
-        <v>29</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3">
-        <v>146</v>
+        <v>94</v>
+      </c>
+      <c r="B40">
+        <v>4</v>
+      </c>
+      <c r="C40">
+        <v>86</v>
+      </c>
+      <c r="D40">
+        <v>90</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
+        <v>976</v>
+      </c>
+      <c r="B41">
+        <v>128</v>
+      </c>
+      <c r="C41">
+        <v>112</v>
+      </c>
+      <c r="D41">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B46" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" t="s">
+        <v>821</v>
+      </c>
+      <c r="D46" t="s">
         <v>675</v>
       </c>
-      <c r="B41" s="3">
+      <c r="E46" t="s">
+        <v>94</v>
+      </c>
+      <c r="F46" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B47">
+        <v>116</v>
+      </c>
+      <c r="C47">
         <v>1</v>
       </c>
-      <c r="C41" s="3"/>
-      <c r="D41" s="3">
+      <c r="D47">
+        <v>29</v>
+      </c>
+      <c r="F47">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A48" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B48">
+        <v>1</v>
+      </c>
+      <c r="D48">
         <v>3</v>
       </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3">
+      <c r="F48">
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="B42" s="3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49">
         <v>2</v>
       </c>
-      <c r="C42" s="3"/>
-      <c r="D42" s="3">
+      <c r="D49">
         <v>18</v>
       </c>
-      <c r="E42" s="3">
+      <c r="E49">
         <v>70</v>
       </c>
-      <c r="F42" s="3">
+      <c r="F49">
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="B43" s="3">
+      <c r="B50">
         <v>119</v>
       </c>
-      <c r="C43" s="3">
+      <c r="C50">
         <v>1</v>
       </c>
-      <c r="D43" s="3">
+      <c r="D50">
         <v>50</v>
       </c>
-      <c r="E43" s="3">
+      <c r="E50">
         <v>70</v>
       </c>
-      <c r="F43" s="3">
+      <c r="F50">
         <v>240</v>
       </c>
     </row>

--- a/comparison_bapa.xlsx
+++ b/comparison_bapa.xlsx
@@ -8,23 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mudathir\all\sls-reachability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8361F679-605C-4DCA-A272-9789CB069924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3E41CB3-3C35-4941-A1A8-4C7CC2EF9A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{43139118-C9B1-4C53-BA07-4D51B812E9BD}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{43139118-C9B1-4C53-BA07-4D51B812E9BD}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
-    <sheet name="comparison_bapa" sheetId="1" r:id="rId2"/>
+    <sheet name="Detail1" sheetId="3" r:id="rId1"/>
+    <sheet name="Detail2" sheetId="4" r:id="rId2"/>
+    <sheet name="different liastar results" sheetId="5" r:id="rId3"/>
+    <sheet name="pivot tables" sheetId="2" r:id="rId4"/>
+    <sheet name="comparison_bapa" sheetId="1" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId3"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1998" uniqueCount="982">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2189" uniqueCount="985">
   <si>
     <t>sls file</t>
   </si>
@@ -2970,6 +2973,15 @@
   </si>
   <si>
     <t>cvc5 sets results</t>
+  </si>
+  <si>
+    <t>Details for Count of sls duration - sls result: timeout, z3 result: error</t>
+  </si>
+  <si>
+    <t>Details for Count of sls duration - sls result: timeout, cvc5 sets result: unsat</t>
+  </si>
+  <si>
+    <t>Details for Count of sls duration - sls result: sat, cvc5 lia result: unsat</t>
   </si>
 </sst>
 </file>
@@ -3459,7 +3471,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -7488,6 +7500,69 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{CF321229-C4FB-4567-9609-053E3929CC2C}" name="Table2" displayName="Table2" ref="A3:L4" totalsRowShown="0">
+  <autoFilter ref="A3:L4" xr:uid="{CF321229-C4FB-4567-9609-053E3929CC2C}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{C1D1A504-77B8-4BC6-BCEA-BF2117B4813F}" name="sls file"/>
+    <tableColumn id="2" xr3:uid="{B34D40DE-0716-4934-815C-5804EC7794A1}" name="sls result"/>
+    <tableColumn id="3" xr3:uid="{D4944FD7-E54F-43B5-BC63-8B7B119DE8C2}" name="sls duration"/>
+    <tableColumn id="4" xr3:uid="{8E8E8A2B-6E44-42D0-A190-E72C776E77E8}" name="z3 filename"/>
+    <tableColumn id="5" xr3:uid="{78D2A0EA-B906-4880-9D0B-1C692546F3C2}" name="z3 result"/>
+    <tableColumn id="6" xr3:uid="{D5F0F521-A5D0-4868-B579-86B76AC72410}" name="z3 duration"/>
+    <tableColumn id="7" xr3:uid="{876F87D2-4AEA-4AA3-9F13-4D905173FEAC}" name="cvc5 sets filename"/>
+    <tableColumn id="8" xr3:uid="{FA189FB9-8B83-4123-9DEF-5E19353B101A}" name="cvc5 sets result"/>
+    <tableColumn id="9" xr3:uid="{A43A99A8-ECFB-48F5-8DCE-B17E02D607B4}" name="cvc5 sets duration"/>
+    <tableColumn id="10" xr3:uid="{63802994-1F4E-4563-A479-BE20C9243119}" name="cvc5 lia filename"/>
+    <tableColumn id="11" xr3:uid="{3E6A3053-8826-4C3F-AE16-D707D49374F3}" name="cvc5 lia result"/>
+    <tableColumn id="12" xr3:uid="{5932F436-C616-4FE9-B69C-DF2C0A2C0230}" name="cvc5 lia duration"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E76FAFC5-C848-4D71-99E0-2C797120E87A}" name="Table3" displayName="Table3" ref="A3:L20" totalsRowShown="0">
+  <autoFilter ref="A3:L20" xr:uid="{E76FAFC5-C848-4D71-99E0-2C797120E87A}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{EC06406A-C921-4466-BC4B-BDFB6BA9F343}" name="sls file"/>
+    <tableColumn id="2" xr3:uid="{E8AA1725-9C2C-4333-9572-6F0EAAA15B77}" name="sls result"/>
+    <tableColumn id="3" xr3:uid="{CECBE5EB-F634-48B2-9C65-E54EB527484B}" name="sls duration"/>
+    <tableColumn id="4" xr3:uid="{F296D518-874D-4261-A86D-7B72365EAEDB}" name="z3 filename"/>
+    <tableColumn id="5" xr3:uid="{A8644F5C-3DA9-4966-B731-0713BDB307A3}" name="z3 result"/>
+    <tableColumn id="6" xr3:uid="{1E5F85B4-A594-4D98-BE56-781EACD54E68}" name="z3 duration"/>
+    <tableColumn id="7" xr3:uid="{3DB06807-7124-4481-AA4E-D03D63173BFA}" name="cvc5 sets filename"/>
+    <tableColumn id="8" xr3:uid="{D2558473-3270-42D8-B3C5-6F552A4F6E6B}" name="cvc5 sets result"/>
+    <tableColumn id="9" xr3:uid="{6ABA3EF3-D94D-4D62-A43F-C075E5E38FAD}" name="cvc5 sets duration"/>
+    <tableColumn id="10" xr3:uid="{99BBEC2D-E969-4D1D-B577-F01066EBFB7D}" name="cvc5 lia filename"/>
+    <tableColumn id="11" xr3:uid="{C47E4F63-E34A-4625-9B0D-97D675B23755}" name="cvc5 lia result"/>
+    <tableColumn id="12" xr3:uid="{E976CF8F-7785-45F5-AFE4-FBC95AE2F0DE}" name="cvc5 lia duration"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{26B13B5A-D5C8-4066-AEF6-6207E01FCC4B}" name="Table4" displayName="Table4" ref="A3:L4" totalsRowShown="0">
+  <autoFilter ref="A3:L4" xr:uid="{26B13B5A-D5C8-4066-AEF6-6207E01FCC4B}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{EF175C72-A691-4FD4-A014-C5BB44E1D65B}" name="sls file"/>
+    <tableColumn id="2" xr3:uid="{DDB6A95C-E598-4CD6-8D25-7E6F0BC07E09}" name="sls result"/>
+    <tableColumn id="3" xr3:uid="{4BB0FE44-0EB1-4A0D-BA2A-9D763778BE5A}" name="sls duration"/>
+    <tableColumn id="4" xr3:uid="{346F43E5-95CB-4AA0-98D1-3B80B7C8E473}" name="z3 filename"/>
+    <tableColumn id="5" xr3:uid="{1F919634-4F9F-43B5-B8D7-940187B18E63}" name="z3 result"/>
+    <tableColumn id="6" xr3:uid="{984E83F5-601E-494B-80C2-1AF42B64D675}" name="z3 duration"/>
+    <tableColumn id="7" xr3:uid="{9D25D888-54F8-44CB-ADBA-2D14B6D2C1F0}" name="cvc5 sets filename"/>
+    <tableColumn id="8" xr3:uid="{5BB9400D-CE52-4FA1-B041-641508422475}" name="cvc5 sets result"/>
+    <tableColumn id="9" xr3:uid="{81BE9DB0-F7F5-4145-A62A-A73EE56352D8}" name="cvc5 sets duration"/>
+    <tableColumn id="10" xr3:uid="{33D380B9-4225-4574-98F8-6D8F3589F0B3}" name="cvc5 lia filename"/>
+    <tableColumn id="11" xr3:uid="{032B6537-DB09-4235-A75A-F88A6454D940}" name="cvc5 lia result"/>
+    <tableColumn id="12" xr3:uid="{CF3E727E-8F75-4634-9144-676E64960E51}" name="cvc5 lia duration"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{7408DD88-DFA5-4A5F-A614-C258ABB88750}" name="Table1" displayName="Table1" ref="A1:L241" totalsRowShown="0">
   <autoFilter ref="A1:L241" xr:uid="{7408DD88-DFA5-4A5F-A614-C258ABB88750}"/>
   <tableColumns count="12">
@@ -7824,6 +7899,938 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B57D651D-E1AF-4776-B229-3018FD542461}">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>819</v>
+      </c>
+      <c r="B4" t="s">
+        <v>675</v>
+      </c>
+      <c r="C4">
+        <v>50.611493109999998</v>
+      </c>
+      <c r="D4" t="s">
+        <v>820</v>
+      </c>
+      <c r="E4" t="s">
+        <v>821</v>
+      </c>
+      <c r="F4">
+        <v>0.23681044600000001</v>
+      </c>
+      <c r="G4" t="s">
+        <v>822</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4">
+        <v>3.9801121000000002E-2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>823</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4">
+        <v>0.54450774199999996</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6874FC8-FD07-4EC7-9F75-AA769EF152BF}">
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>972</v>
+      </c>
+      <c r="B4" t="s">
+        <v>675</v>
+      </c>
+      <c r="C4">
+        <v>51.31768417</v>
+      </c>
+      <c r="D4" t="s">
+        <v>973</v>
+      </c>
+      <c r="E4" t="s">
+        <v>675</v>
+      </c>
+      <c r="F4">
+        <v>51.860954999999997</v>
+      </c>
+      <c r="G4" t="s">
+        <v>974</v>
+      </c>
+      <c r="H4" t="s">
+        <v>94</v>
+      </c>
+      <c r="I4">
+        <v>6.0765742999999997E-2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>975</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4">
+        <v>3.119985819</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>956</v>
+      </c>
+      <c r="B5" t="s">
+        <v>675</v>
+      </c>
+      <c r="C5">
+        <v>51.290453669999998</v>
+      </c>
+      <c r="D5" t="s">
+        <v>957</v>
+      </c>
+      <c r="E5" t="s">
+        <v>675</v>
+      </c>
+      <c r="F5">
+        <v>51.8436904</v>
+      </c>
+      <c r="G5" t="s">
+        <v>958</v>
+      </c>
+      <c r="H5" t="s">
+        <v>94</v>
+      </c>
+      <c r="I5">
+        <v>5.8766603000000001E-2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>959</v>
+      </c>
+      <c r="K5" t="s">
+        <v>13</v>
+      </c>
+      <c r="L5">
+        <v>3.1783001419999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>952</v>
+      </c>
+      <c r="B6" t="s">
+        <v>675</v>
+      </c>
+      <c r="C6">
+        <v>50.664122339999999</v>
+      </c>
+      <c r="D6" t="s">
+        <v>953</v>
+      </c>
+      <c r="E6" t="s">
+        <v>675</v>
+      </c>
+      <c r="F6">
+        <v>50.944791080000002</v>
+      </c>
+      <c r="G6" t="s">
+        <v>954</v>
+      </c>
+      <c r="H6" t="s">
+        <v>94</v>
+      </c>
+      <c r="I6">
+        <v>2.0400762999999999E-2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>955</v>
+      </c>
+      <c r="K6" t="s">
+        <v>94</v>
+      </c>
+      <c r="L6">
+        <v>0.50214147600000003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>940</v>
+      </c>
+      <c r="B7" t="s">
+        <v>675</v>
+      </c>
+      <c r="C7">
+        <v>51.271746399999998</v>
+      </c>
+      <c r="D7" t="s">
+        <v>941</v>
+      </c>
+      <c r="E7" t="s">
+        <v>675</v>
+      </c>
+      <c r="F7">
+        <v>51.966396570000001</v>
+      </c>
+      <c r="G7" t="s">
+        <v>942</v>
+      </c>
+      <c r="H7" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7">
+        <v>0.228644133</v>
+      </c>
+      <c r="J7" t="s">
+        <v>943</v>
+      </c>
+      <c r="K7" t="s">
+        <v>94</v>
+      </c>
+      <c r="L7">
+        <v>0.28160738899999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>936</v>
+      </c>
+      <c r="B8" t="s">
+        <v>675</v>
+      </c>
+      <c r="C8">
+        <v>50.703265909999999</v>
+      </c>
+      <c r="D8" t="s">
+        <v>937</v>
+      </c>
+      <c r="E8" t="s">
+        <v>675</v>
+      </c>
+      <c r="F8">
+        <v>51.824228290000001</v>
+      </c>
+      <c r="G8" t="s">
+        <v>938</v>
+      </c>
+      <c r="H8" t="s">
+        <v>94</v>
+      </c>
+      <c r="I8">
+        <v>2.6983022999999998E-2</v>
+      </c>
+      <c r="J8" t="s">
+        <v>939</v>
+      </c>
+      <c r="K8" t="s">
+        <v>94</v>
+      </c>
+      <c r="L8">
+        <v>0.50826597200000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>880</v>
+      </c>
+      <c r="B9" t="s">
+        <v>675</v>
+      </c>
+      <c r="C9">
+        <v>50.667820220000003</v>
+      </c>
+      <c r="D9" t="s">
+        <v>881</v>
+      </c>
+      <c r="E9" t="s">
+        <v>675</v>
+      </c>
+      <c r="F9">
+        <v>51.857316969999999</v>
+      </c>
+      <c r="G9" t="s">
+        <v>882</v>
+      </c>
+      <c r="H9" t="s">
+        <v>94</v>
+      </c>
+      <c r="I9">
+        <v>5.0558922290000003</v>
+      </c>
+      <c r="J9" t="s">
+        <v>883</v>
+      </c>
+      <c r="K9" t="s">
+        <v>94</v>
+      </c>
+      <c r="L9">
+        <v>1.629296064</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>872</v>
+      </c>
+      <c r="B10" t="s">
+        <v>675</v>
+      </c>
+      <c r="C10">
+        <v>51.326945539999997</v>
+      </c>
+      <c r="D10" t="s">
+        <v>873</v>
+      </c>
+      <c r="E10" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10">
+        <v>2.0763396999999999E-2</v>
+      </c>
+      <c r="G10" t="s">
+        <v>874</v>
+      </c>
+      <c r="H10" t="s">
+        <v>94</v>
+      </c>
+      <c r="I10">
+        <v>0.23372983899999999</v>
+      </c>
+      <c r="J10" t="s">
+        <v>875</v>
+      </c>
+      <c r="K10" t="s">
+        <v>94</v>
+      </c>
+      <c r="L10">
+        <v>0.27394270900000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>848</v>
+      </c>
+      <c r="B11" t="s">
+        <v>675</v>
+      </c>
+      <c r="C11">
+        <v>51.256371739999999</v>
+      </c>
+      <c r="D11" t="s">
+        <v>849</v>
+      </c>
+      <c r="E11" t="s">
+        <v>675</v>
+      </c>
+      <c r="F11">
+        <v>50.932335850000001</v>
+      </c>
+      <c r="G11" t="s">
+        <v>850</v>
+      </c>
+      <c r="H11" t="s">
+        <v>94</v>
+      </c>
+      <c r="I11">
+        <v>0.221822977</v>
+      </c>
+      <c r="J11" t="s">
+        <v>851</v>
+      </c>
+      <c r="K11" t="s">
+        <v>94</v>
+      </c>
+      <c r="L11">
+        <v>0.27293872800000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>844</v>
+      </c>
+      <c r="B12" t="s">
+        <v>675</v>
+      </c>
+      <c r="C12">
+        <v>51.320613379999998</v>
+      </c>
+      <c r="D12" t="s">
+        <v>845</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12">
+        <v>2.1147490000000001E-2</v>
+      </c>
+      <c r="G12" t="s">
+        <v>846</v>
+      </c>
+      <c r="H12" t="s">
+        <v>94</v>
+      </c>
+      <c r="I12">
+        <v>0.22350144399999999</v>
+      </c>
+      <c r="J12" t="s">
+        <v>847</v>
+      </c>
+      <c r="K12" t="s">
+        <v>94</v>
+      </c>
+      <c r="L12">
+        <v>0.273928642</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>840</v>
+      </c>
+      <c r="B13" t="s">
+        <v>675</v>
+      </c>
+      <c r="C13">
+        <v>50.641766310000001</v>
+      </c>
+      <c r="D13" t="s">
+        <v>841</v>
+      </c>
+      <c r="E13" t="s">
+        <v>675</v>
+      </c>
+      <c r="F13">
+        <v>51.868062020000004</v>
+      </c>
+      <c r="G13" t="s">
+        <v>842</v>
+      </c>
+      <c r="H13" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13">
+        <v>2.0163298E-2</v>
+      </c>
+      <c r="J13" t="s">
+        <v>843</v>
+      </c>
+      <c r="K13" t="s">
+        <v>94</v>
+      </c>
+      <c r="L13">
+        <v>0.50035643600000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>824</v>
+      </c>
+      <c r="B14" t="s">
+        <v>675</v>
+      </c>
+      <c r="C14">
+        <v>51.136517759999997</v>
+      </c>
+      <c r="D14" t="s">
+        <v>825</v>
+      </c>
+      <c r="E14" t="s">
+        <v>675</v>
+      </c>
+      <c r="F14">
+        <v>50.92865682</v>
+      </c>
+      <c r="G14" t="s">
+        <v>826</v>
+      </c>
+      <c r="H14" t="s">
+        <v>94</v>
+      </c>
+      <c r="I14">
+        <v>2.1515131E-2</v>
+      </c>
+      <c r="J14" t="s">
+        <v>827</v>
+      </c>
+      <c r="K14" t="s">
+        <v>94</v>
+      </c>
+      <c r="L14">
+        <v>0.49274754500000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>803</v>
+      </c>
+      <c r="B15" t="s">
+        <v>675</v>
+      </c>
+      <c r="C15">
+        <v>51.169895169999997</v>
+      </c>
+      <c r="D15" t="s">
+        <v>804</v>
+      </c>
+      <c r="E15" t="s">
+        <v>675</v>
+      </c>
+      <c r="F15">
+        <v>51.786777499999999</v>
+      </c>
+      <c r="G15" t="s">
+        <v>805</v>
+      </c>
+      <c r="H15" t="s">
+        <v>94</v>
+      </c>
+      <c r="I15">
+        <v>6.4560651999999996E-2</v>
+      </c>
+      <c r="J15" t="s">
+        <v>806</v>
+      </c>
+      <c r="K15" t="s">
+        <v>13</v>
+      </c>
+      <c r="L15">
+        <v>3.1866209510000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>771</v>
+      </c>
+      <c r="B16" t="s">
+        <v>675</v>
+      </c>
+      <c r="C16">
+        <v>51.079448939999999</v>
+      </c>
+      <c r="D16" t="s">
+        <v>772</v>
+      </c>
+      <c r="E16" t="s">
+        <v>675</v>
+      </c>
+      <c r="F16">
+        <v>52.802242990000003</v>
+      </c>
+      <c r="G16" t="s">
+        <v>773</v>
+      </c>
+      <c r="H16" t="s">
+        <v>94</v>
+      </c>
+      <c r="I16">
+        <v>0.13435339900000001</v>
+      </c>
+      <c r="J16" t="s">
+        <v>774</v>
+      </c>
+      <c r="K16" t="s">
+        <v>94</v>
+      </c>
+      <c r="L16">
+        <v>0.27846503299999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>751</v>
+      </c>
+      <c r="B17" t="s">
+        <v>675</v>
+      </c>
+      <c r="C17">
+        <v>50.577882770000002</v>
+      </c>
+      <c r="D17" t="s">
+        <v>752</v>
+      </c>
+      <c r="E17" t="s">
+        <v>675</v>
+      </c>
+      <c r="F17">
+        <v>51.940913199999997</v>
+      </c>
+      <c r="G17" t="s">
+        <v>753</v>
+      </c>
+      <c r="H17" t="s">
+        <v>94</v>
+      </c>
+      <c r="I17">
+        <v>1.5604972999999999E-2</v>
+      </c>
+      <c r="J17" t="s">
+        <v>754</v>
+      </c>
+      <c r="K17" t="s">
+        <v>94</v>
+      </c>
+      <c r="L17">
+        <v>5.6289433999999999E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>735</v>
+      </c>
+      <c r="B18" t="s">
+        <v>675</v>
+      </c>
+      <c r="C18">
+        <v>51.138786320000001</v>
+      </c>
+      <c r="D18" t="s">
+        <v>736</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18">
+        <v>0.26286029799999999</v>
+      </c>
+      <c r="G18" t="s">
+        <v>737</v>
+      </c>
+      <c r="H18" t="s">
+        <v>94</v>
+      </c>
+      <c r="I18">
+        <v>1.6002893000000001E-2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>738</v>
+      </c>
+      <c r="K18" t="s">
+        <v>94</v>
+      </c>
+      <c r="L18">
+        <v>5.6864976999999997E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>711</v>
+      </c>
+      <c r="B19" t="s">
+        <v>675</v>
+      </c>
+      <c r="C19">
+        <v>51.117910389999999</v>
+      </c>
+      <c r="D19" t="s">
+        <v>712</v>
+      </c>
+      <c r="E19" t="s">
+        <v>675</v>
+      </c>
+      <c r="F19">
+        <v>51.862462520000001</v>
+      </c>
+      <c r="G19" t="s">
+        <v>713</v>
+      </c>
+      <c r="H19" t="s">
+        <v>94</v>
+      </c>
+      <c r="I19">
+        <v>0.113097906</v>
+      </c>
+      <c r="J19" t="s">
+        <v>714</v>
+      </c>
+      <c r="K19" t="s">
+        <v>13</v>
+      </c>
+      <c r="L19">
+        <v>3.1498923300000001</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>679</v>
+      </c>
+      <c r="B20" t="s">
+        <v>675</v>
+      </c>
+      <c r="C20">
+        <v>50.565519809999998</v>
+      </c>
+      <c r="D20" t="s">
+        <v>680</v>
+      </c>
+      <c r="E20" t="s">
+        <v>675</v>
+      </c>
+      <c r="F20">
+        <v>50.929439780000003</v>
+      </c>
+      <c r="G20" t="s">
+        <v>681</v>
+      </c>
+      <c r="H20" t="s">
+        <v>94</v>
+      </c>
+      <c r="I20">
+        <v>4.9223423000000002E-2</v>
+      </c>
+      <c r="J20" t="s">
+        <v>682</v>
+      </c>
+      <c r="K20" t="s">
+        <v>94</v>
+      </c>
+      <c r="L20">
+        <v>0.275665045</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ADF70EBC-F86F-4580-BAA0-9ADCDD5465AC}">
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="34.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>787</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4">
+        <v>3.225478888</v>
+      </c>
+      <c r="D4" t="s">
+        <v>788</v>
+      </c>
+      <c r="E4" t="s">
+        <v>675</v>
+      </c>
+      <c r="F4">
+        <v>51.811887259999999</v>
+      </c>
+      <c r="G4" t="s">
+        <v>789</v>
+      </c>
+      <c r="H4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I4">
+        <v>1.513195E-2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>790</v>
+      </c>
+      <c r="K4" t="s">
+        <v>94</v>
+      </c>
+      <c r="L4">
+        <v>0.28650450700000002</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6651627E-A0CF-441C-976A-9DDF30242CC0}">
   <dimension ref="A3:F50"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -7966,12 +8973,10 @@
       <c r="A13" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13">
         <v>116</v>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3">
+      <c r="E13">
         <v>116</v>
       </c>
     </row>
@@ -7979,16 +8984,16 @@
       <c r="A14" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14">
         <v>30</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14">
         <v>4</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14">
         <v>17</v>
       </c>
-      <c r="E14" s="3">
+      <c r="E14">
         <v>51</v>
       </c>
     </row>
@@ -7996,12 +9001,10 @@
       <c r="A15" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3">
+      <c r="D15">
         <v>73</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15">
         <v>73</v>
       </c>
     </row>
@@ -8009,16 +9012,16 @@
       <c r="A16" s="2" t="s">
         <v>976</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16">
         <v>146</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16">
         <v>4</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16">
         <v>90</v>
       </c>
-      <c r="E16" s="3">
+      <c r="E16">
         <v>240</v>
       </c>
     </row>
@@ -8362,7 +9365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEEC5DD9-14C3-4C18-9355-6C6BFA91C6D6}">
   <dimension ref="A1:L241"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/comparison_bapa.xlsx
+++ b/comparison_bapa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mudathir\all\sls-reachability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{892FD2CE-B726-4C54-8686-DC76AA4BCDCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378CF71F-99BD-425B-8CB2-5CA82FA7CEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{43139118-C9B1-4C53-BA07-4D51B812E9BD}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="492">
   <si>
     <t>sls file</t>
   </si>
@@ -776,6 +776,726 @@
   </si>
   <si>
     <t>lia normaliz duration</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000001.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000002.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000003.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000004.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000005.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000006.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000007.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000008.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000009.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000010.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000011.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000012.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000013.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000014.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000015.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000016.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000017.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000018.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000019.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000020.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000021.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000022.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000023.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000024.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000025.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000026.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000027.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000028.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000029.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000030.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000031.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000032.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000033.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000034.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000035.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000036.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000037.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000038.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000039.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000040.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000041.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000042.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000043.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000044.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000045.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000046.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000047.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000048.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000049.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000050.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000051.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000052.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000053.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000054.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000055.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000056.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000057.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000058.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000059.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000060.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000061.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000062.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000063.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000064.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000065.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000066.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000067.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000068.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000069.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000070.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000071.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000072.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000073.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000074.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000075.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000076.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000077.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000078.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000079.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000080.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000081.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000082.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000083.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000084.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000085.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000086.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000087.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000088.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000089.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000090.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000091.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000092.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000093.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000094.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000095.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000096.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000097.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000098.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000099.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000100.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000101.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000102.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000103.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000104.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000105.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000106.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000107.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000108.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000109.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000110.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000111.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000112.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000113.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000114.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000115.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000116.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000117.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000118.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000119.smt2</t>
+  </si>
+  <si>
+    <t>bapa/arith/fol_0000120.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000001.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000002.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000003.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000004.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000005.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000006.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000007.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000008.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000009.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000010.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000011.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000012.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000013.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000014.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000015.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000016.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000017.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000018.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000019.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000020.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000021.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000022.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000023.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000024.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000025.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000026.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000027.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000028.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000029.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000030.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000031.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000032.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000033.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000034.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000035.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000036.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000037.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000038.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000039.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000040.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000041.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000042.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000043.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000044.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000045.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000046.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000047.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000048.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000049.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000050.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000051.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000052.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000053.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000054.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000055.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000056.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000057.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000058.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000059.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000060.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000061.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000062.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000063.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000064.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000065.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000066.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000067.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000068.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000069.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000070.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000071.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000072.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000073.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000074.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000075.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000076.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000077.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000078.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000079.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000080.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000081.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000082.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000083.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000084.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000085.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000086.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000087.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000088.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000089.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000090.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000091.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000092.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000093.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000094.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000095.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000096.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000097.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000098.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000099.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000100.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000101.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000102.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000103.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000104.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000105.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000106.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000107.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000108.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000109.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000110.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000111.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000112.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000113.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000114.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000115.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000116.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000117.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000118.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000119.smt2</t>
+  </si>
+  <si>
+    <t>bapa/card/fol_0000120.smt2</t>
   </si>
 </sst>
 </file>
@@ -1341,18 +2061,18 @@
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="33" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="15" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1409,6 +2129,24 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E729566-643F-4C03-A5FC-1C062252F9B9}" name="Table1" displayName="Table1" ref="A1:I241" totalsRowShown="0">
+  <autoFilter ref="A1:I241" xr:uid="{1E729566-643F-4C03-A5FC-1C062252F9B9}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{E3805889-3FE1-402D-BB6D-F7B17E3DEA31}" name="sls file"/>
+    <tableColumn id="2" xr3:uid="{90A6288E-50A4-4863-AF83-0088DD98FE4D}" name="sls result"/>
+    <tableColumn id="3" xr3:uid="{A267AAC5-40E4-4F1B-86EC-9C8AA546ADF6}" name="sls duration"/>
+    <tableColumn id="4" xr3:uid="{ACF2AEE7-7E08-4C28-9CF1-90DE44FFE626}" name="cvc5 lia filename"/>
+    <tableColumn id="5" xr3:uid="{6D20C19E-8CE9-4386-A7E5-A4C7737FAF18}" name="cvc5 lia result"/>
+    <tableColumn id="6" xr3:uid="{73812892-778F-4FF9-9FB6-49CE20A90DC1}" name="cvc5 lia duration"/>
+    <tableColumn id="7" xr3:uid="{EC93C786-0848-4FCD-8041-AFBB16DD425B}" name="lia normaliz filename"/>
+    <tableColumn id="8" xr3:uid="{C1192E6F-5378-47BD-878E-BE1FBFF24DF0}" name="lia normaliz result"/>
+    <tableColumn id="9" xr3:uid="{0F440ABC-08B3-464F-9622-2B4B82B9535E}" name="lia normaliz duration"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1731,14 +2469,15 @@
   <dimension ref="A1:I241"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.36328125" customWidth="1"/>
     <col min="3" max="3" width="12.6328125" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
+    <col min="4" max="4" width="44.90625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.36328125" customWidth="1"/>
     <col min="6" max="6" width="16.6328125" customWidth="1"/>
     <col min="7" max="7" width="44.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.7265625" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
@@ -1771,9 +2510,15 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="10"/>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
+      <c r="A2" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0.99435853958129805</v>
+      </c>
       <c r="D2" s="11" t="s">
         <v>7</v>
       </c>
@@ -1794,9 +2539,15 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="8"/>
-      <c r="C3" s="8"/>
+      <c r="A3" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="8">
+        <v>0.76033210754394498</v>
+      </c>
       <c r="D3" s="8" t="s">
         <v>8</v>
       </c>
@@ -1817,9 +2568,15 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="10"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
+      <c r="A4" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.63649606704711903</v>
+      </c>
       <c r="D4" s="11" t="s">
         <v>9</v>
       </c>
@@ -1840,9 +2597,15 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="7"/>
-      <c r="B5" s="8"/>
-      <c r="C5" s="8"/>
+      <c r="A5" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.80373120307922297</v>
+      </c>
       <c r="D5" s="8" t="s">
         <v>10</v>
       </c>
@@ -1863,9 +2626,15 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="10"/>
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
+      <c r="A6" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.63803029060363703</v>
+      </c>
       <c r="D6" s="11" t="s">
         <v>11</v>
       </c>
@@ -1886,9 +2655,15 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="7"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
+      <c r="A7" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.568917036056518</v>
+      </c>
       <c r="D7" s="8" t="s">
         <v>12</v>
       </c>
@@ -1909,9 +2684,15 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="10"/>
-      <c r="B8" s="11"/>
-      <c r="C8" s="11"/>
+      <c r="A8" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0.79503488540649403</v>
+      </c>
       <c r="D8" s="11" t="s">
         <v>13</v>
       </c>
@@ -1932,9 +2713,15 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="7"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
+      <c r="A9" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="8">
+        <v>0.63126659393310502</v>
+      </c>
       <c r="D9" s="8" t="s">
         <v>14</v>
       </c>
@@ -1955,9 +2742,15 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="10"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+      <c r="A10" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="11">
+        <v>0.79279041290283203</v>
+      </c>
       <c r="D10" s="11" t="s">
         <v>15</v>
       </c>
@@ -1978,9 +2771,15 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="7"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
+      <c r="A11" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C11" s="8">
+        <v>0.64874768257141102</v>
+      </c>
       <c r="D11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2001,9 +2800,15 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="10"/>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
+      <c r="A12" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="11">
+        <v>0.65620541572570801</v>
+      </c>
       <c r="D12" s="11" t="s">
         <v>17</v>
       </c>
@@ -2024,9 +2829,15 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="7"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
+      <c r="A13" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="8">
+        <v>0.67011260986328103</v>
+      </c>
       <c r="D13" s="8" t="s">
         <v>18</v>
       </c>
@@ -2047,9 +2858,15 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="10"/>
-      <c r="B14" s="11"/>
-      <c r="C14" s="11"/>
+      <c r="A14" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="11">
+        <v>0.61955571174621504</v>
+      </c>
       <c r="D14" s="11" t="s">
         <v>19</v>
       </c>
@@ -2070,9 +2887,15 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="7"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
+      <c r="A15" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="8">
+        <v>0.167417287826538</v>
+      </c>
       <c r="D15" s="8" t="s">
         <v>20</v>
       </c>
@@ -2093,9 +2916,15 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="10"/>
-      <c r="B16" s="11"/>
-      <c r="C16" s="11"/>
+      <c r="A16" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="11">
+        <v>1.01652908325195</v>
+      </c>
       <c r="D16" s="11" t="s">
         <v>21</v>
       </c>
@@ -2116,9 +2945,15 @@
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A17" s="7"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
+      <c r="A17" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C17" s="8">
+        <v>0.84496617317199696</v>
+      </c>
       <c r="D17" s="8" t="s">
         <v>22</v>
       </c>
@@ -2139,9 +2974,15 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A18" s="10"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
+      <c r="A18" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C18" s="11">
+        <v>0.53039336204528797</v>
+      </c>
       <c r="D18" s="11" t="s">
         <v>23</v>
       </c>
@@ -2162,9 +3003,15 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A19" s="7"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
+      <c r="A19" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C19" s="8">
+        <v>0.93049621582031194</v>
+      </c>
       <c r="D19" s="8" t="s">
         <v>24</v>
       </c>
@@ -2185,9 +3032,15 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A20" s="10"/>
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
+      <c r="A20" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="11">
+        <v>0.74736404418945301</v>
+      </c>
       <c r="D20" s="11" t="s">
         <v>25</v>
       </c>
@@ -2208,9 +3061,15 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A21" s="7"/>
-      <c r="B21" s="8"/>
-      <c r="C21" s="8"/>
+      <c r="A21" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C21" s="8">
+        <v>0.171578884124755</v>
+      </c>
       <c r="D21" s="8" t="s">
         <v>26</v>
       </c>
@@ -2231,9 +3090,15 @@
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A22" s="10"/>
-      <c r="B22" s="11"/>
-      <c r="C22" s="11"/>
+      <c r="A22" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="11">
+        <v>0.16096591949462799</v>
+      </c>
       <c r="D22" s="11" t="s">
         <v>28</v>
       </c>
@@ -2254,9 +3119,15 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A23" s="7"/>
-      <c r="B23" s="8"/>
-      <c r="C23" s="8"/>
+      <c r="A23" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="8">
+        <v>0.40941166877746499</v>
+      </c>
       <c r="D23" s="8" t="s">
         <v>29</v>
       </c>
@@ -2277,9 +3148,15 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="11"/>
+      <c r="A24" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="11">
+        <v>0.16520500183105399</v>
+      </c>
       <c r="D24" s="11" t="s">
         <v>30</v>
       </c>
@@ -2300,9 +3177,15 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A25" s="7"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
+      <c r="A25" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="8">
+        <v>0.65459823608398404</v>
+      </c>
       <c r="D25" s="8" t="s">
         <v>31</v>
       </c>
@@ -2323,9 +3206,15 @@
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="11"/>
+      <c r="A26" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="11">
+        <v>0.162420749664306</v>
+      </c>
       <c r="D26" s="11" t="s">
         <v>32</v>
       </c>
@@ -2346,9 +3235,15 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A27" s="7"/>
-      <c r="B27" s="8"/>
-      <c r="C27" s="8"/>
+      <c r="A27" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="8">
+        <v>0.37980604171752902</v>
+      </c>
       <c r="D27" s="8" t="s">
         <v>33</v>
       </c>
@@ -2369,9 +3264,15 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A28" s="10"/>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
+      <c r="A28" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="11">
+        <v>0.163376569747924</v>
+      </c>
       <c r="D28" s="11" t="s">
         <v>34</v>
       </c>
@@ -2392,9 +3293,15 @@
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A29" s="7"/>
-      <c r="B29" s="8"/>
-      <c r="C29" s="8"/>
+      <c r="A29" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="8">
+        <v>0.47155237197875899</v>
+      </c>
       <c r="D29" s="8" t="s">
         <v>35</v>
       </c>
@@ -2415,9 +3322,15 @@
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A30" s="10"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
+      <c r="A30" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="11">
+        <v>0.53534078598022405</v>
+      </c>
       <c r="D30" s="11" t="s">
         <v>36</v>
       </c>
@@ -2438,9 +3351,15 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A31" s="7"/>
-      <c r="B31" s="8"/>
-      <c r="C31" s="8"/>
+      <c r="A31" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="8">
+        <v>0.16627836227416901</v>
+      </c>
       <c r="D31" s="8" t="s">
         <v>37</v>
       </c>
@@ -2461,9 +3380,15 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A32" s="10"/>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
+      <c r="A32" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="11">
+        <v>0.62550663948059004</v>
+      </c>
       <c r="D32" s="11" t="s">
         <v>38</v>
       </c>
@@ -2484,9 +3409,15 @@
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A33" s="7"/>
-      <c r="B33" s="8"/>
-      <c r="C33" s="8"/>
+      <c r="A33" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C33" s="8">
+        <v>0.16071510314941401</v>
+      </c>
       <c r="D33" s="8" t="s">
         <v>39</v>
       </c>
@@ -2507,9 +3438,15 @@
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A34" s="10"/>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
+      <c r="A34" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="11">
+        <v>0.686598300933837</v>
+      </c>
       <c r="D34" s="11" t="s">
         <v>40</v>
       </c>
@@ -2530,9 +3467,15 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A35" s="7"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
+      <c r="A35" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" s="8">
+        <v>0.15680384635925201</v>
+      </c>
       <c r="D35" s="8" t="s">
         <v>41</v>
       </c>
@@ -2553,9 +3496,15 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
-      <c r="C36" s="11"/>
+      <c r="A36" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C36" s="11">
+        <v>0.71952629089355402</v>
+      </c>
       <c r="D36" s="11" t="s">
         <v>42</v>
       </c>
@@ -2576,9 +3525,15 @@
       </c>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A37" s="7"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
+      <c r="A37" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C37" s="8">
+        <v>0.76075839996337802</v>
+      </c>
       <c r="D37" s="8" t="s">
         <v>43</v>
       </c>
@@ -2599,9 +3554,15 @@
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11"/>
-      <c r="C38" s="11"/>
+      <c r="A38" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="11">
+        <v>0.61400890350341797</v>
+      </c>
       <c r="D38" s="11" t="s">
         <v>44</v>
       </c>
@@ -2622,9 +3583,15 @@
       </c>
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A39" s="7"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
+      <c r="A39" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="B39" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="8">
+        <v>0.15881991386413499</v>
+      </c>
       <c r="D39" s="8" t="s">
         <v>45</v>
       </c>
@@ -2645,9 +3612,15 @@
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A40" s="10"/>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
+      <c r="A40" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C40" s="11">
+        <v>0.55142021179199197</v>
+      </c>
       <c r="D40" s="11" t="s">
         <v>46</v>
       </c>
@@ -2668,9 +3641,15 @@
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A41" s="7"/>
-      <c r="B41" s="8"/>
-      <c r="C41" s="8"/>
+      <c r="A41" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="8">
+        <v>0.159366369247436</v>
+      </c>
       <c r="D41" s="8" t="s">
         <v>47</v>
       </c>
@@ -2691,9 +3670,15 @@
       </c>
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
+      <c r="A42" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="11">
+        <v>0.79223847389221103</v>
+      </c>
       <c r="D42" s="11" t="s">
         <v>48</v>
       </c>
@@ -2714,9 +3699,15 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A43" s="7"/>
-      <c r="B43" s="8"/>
-      <c r="C43" s="8"/>
+      <c r="A43" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C43" s="8">
+        <v>0.211480617523193</v>
+      </c>
       <c r="D43" s="8" t="s">
         <v>49</v>
       </c>
@@ -2737,9 +3728,15 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
+      <c r="A44" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C44" s="11">
+        <v>0.16698408126830999</v>
+      </c>
       <c r="D44" s="11" t="s">
         <v>50</v>
       </c>
@@ -2760,9 +3757,15 @@
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A45" s="7"/>
-      <c r="B45" s="8"/>
-      <c r="C45" s="8"/>
+      <c r="A45" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C45" s="8">
+        <v>0.618000268936157</v>
+      </c>
       <c r="D45" s="8" t="s">
         <v>51</v>
       </c>
@@ -2783,9 +3786,15 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
+      <c r="A46" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="11">
+        <v>0.22474837303161599</v>
+      </c>
       <c r="D46" s="11" t="s">
         <v>52</v>
       </c>
@@ -2806,9 +3815,15 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A47" s="7"/>
-      <c r="B47" s="8"/>
-      <c r="C47" s="8"/>
+      <c r="A47" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="8">
+        <v>0.17848396301269501</v>
+      </c>
       <c r="D47" s="8" t="s">
         <v>53</v>
       </c>
@@ -2829,9 +3844,15 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
+      <c r="A48" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="11">
+        <v>0.219141244888305</v>
+      </c>
       <c r="D48" s="11" t="s">
         <v>54</v>
       </c>
@@ -2852,9 +3873,15 @@
       </c>
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A49" s="7"/>
-      <c r="B49" s="8"/>
-      <c r="C49" s="8"/>
+      <c r="A49" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C49" s="8">
+        <v>0.42846250534057601</v>
+      </c>
       <c r="D49" s="8" t="s">
         <v>55</v>
       </c>
@@ -2875,9 +3902,15 @@
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A50" s="10"/>
-      <c r="B50" s="11"/>
-      <c r="C50" s="11"/>
+      <c r="A50" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C50" s="11">
+        <v>0.52458643913268999</v>
+      </c>
       <c r="D50" s="11" t="s">
         <v>56</v>
       </c>
@@ -2898,9 +3931,15 @@
       </c>
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A51" s="7"/>
-      <c r="B51" s="8"/>
-      <c r="C51" s="8"/>
+      <c r="A51" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="B51" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1.5994741916656401</v>
+      </c>
       <c r="D51" s="8" t="s">
         <v>57</v>
       </c>
@@ -2921,9 +3960,15 @@
       </c>
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
-      <c r="C52" s="11"/>
+      <c r="A52" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="11">
+        <v>0.57938766479492099</v>
+      </c>
       <c r="D52" s="11" t="s">
         <v>58</v>
       </c>
@@ -2944,9 +3989,15 @@
       </c>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A53" s="7"/>
-      <c r="B53" s="8"/>
-      <c r="C53" s="8"/>
+      <c r="A53" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="B53" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C53" s="8">
+        <v>0.54706501960754395</v>
+      </c>
       <c r="D53" s="8" t="s">
         <v>59</v>
       </c>
@@ -2967,9 +4018,15 @@
       </c>
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A54" s="10"/>
-      <c r="B54" s="11"/>
-      <c r="C54" s="11"/>
+      <c r="A54" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C54" s="11">
+        <v>0.43974351882934498</v>
+      </c>
       <c r="D54" s="11" t="s">
         <v>60</v>
       </c>
@@ -2990,9 +4047,15 @@
       </c>
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A55" s="7"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="8"/>
+      <c r="A55" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="8">
+        <v>0.18849515914916901</v>
+      </c>
       <c r="D55" s="8" t="s">
         <v>61</v>
       </c>
@@ -3013,9 +4076,15 @@
       </c>
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A56" s="10"/>
-      <c r="B56" s="11"/>
-      <c r="C56" s="11"/>
+      <c r="A56" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C56" s="11">
+        <v>0.17217445373535101</v>
+      </c>
       <c r="D56" s="11" t="s">
         <v>62</v>
       </c>
@@ -3036,9 +4105,15 @@
       </c>
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A57" s="7"/>
-      <c r="B57" s="8"/>
-      <c r="C57" s="8"/>
+      <c r="A57" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C57" s="8">
+        <v>0.72484612464904696</v>
+      </c>
       <c r="D57" s="8" t="s">
         <v>63</v>
       </c>
@@ -3059,9 +4134,15 @@
       </c>
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A58" s="10"/>
-      <c r="B58" s="11"/>
-      <c r="C58" s="11"/>
+      <c r="A58" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="11">
+        <v>0.39650130271911599</v>
+      </c>
       <c r="D58" s="11" t="s">
         <v>64</v>
       </c>
@@ -3082,9 +4163,15 @@
       </c>
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A59" s="7"/>
-      <c r="B59" s="8"/>
-      <c r="C59" s="8"/>
+      <c r="A59" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" s="8">
+        <v>0.47390007972717202</v>
+      </c>
       <c r="D59" s="8" t="s">
         <v>65</v>
       </c>
@@ -3105,9 +4192,15 @@
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A60" s="10"/>
-      <c r="B60" s="11"/>
-      <c r="C60" s="11"/>
+      <c r="A60" s="10" t="s">
+        <v>310</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C60" s="11">
+        <v>0.15601181983947701</v>
+      </c>
       <c r="D60" s="11" t="s">
         <v>66</v>
       </c>
@@ -3128,9 +4221,15 @@
       </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A61" s="7"/>
-      <c r="B61" s="8"/>
-      <c r="C61" s="8"/>
+      <c r="A61" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" s="8">
+        <v>0.234406948089599</v>
+      </c>
       <c r="D61" s="8" t="s">
         <v>67</v>
       </c>
@@ -3151,9 +4250,15 @@
       </c>
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A62" s="10"/>
-      <c r="B62" s="11"/>
-      <c r="C62" s="11"/>
+      <c r="A62" s="10" t="s">
+        <v>312</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="11">
+        <v>0.47082734107971103</v>
+      </c>
       <c r="D62" s="11" t="s">
         <v>68</v>
       </c>
@@ -3174,9 +4279,15 @@
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A63" s="7"/>
-      <c r="B63" s="8"/>
-      <c r="C63" s="8"/>
+      <c r="A63" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="8">
+        <v>0.42225170135498002</v>
+      </c>
       <c r="D63" s="8" t="s">
         <v>69</v>
       </c>
@@ -3197,9 +4308,15 @@
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A64" s="10"/>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
+      <c r="A64" s="10" t="s">
+        <v>314</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C64" s="11">
+        <v>0.233814477920532</v>
+      </c>
       <c r="D64" s="11" t="s">
         <v>70</v>
       </c>
@@ -3220,9 +4337,15 @@
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A65" s="7"/>
-      <c r="B65" s="8"/>
-      <c r="C65" s="8"/>
+      <c r="A65" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" s="8">
+        <v>0.152176618576049</v>
+      </c>
       <c r="D65" s="8" t="s">
         <v>71</v>
       </c>
@@ -3243,9 +4366,15 @@
       </c>
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A66" s="10"/>
-      <c r="B66" s="11"/>
-      <c r="C66" s="11"/>
+      <c r="A66" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" s="11">
+        <v>0.48354673385620101</v>
+      </c>
       <c r="D66" s="11" t="s">
         <v>72</v>
       </c>
@@ -3266,9 +4395,15 @@
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A67" s="7"/>
-      <c r="B67" s="8"/>
-      <c r="C67" s="8"/>
+      <c r="A67" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" s="8">
+        <v>0.59694933891296298</v>
+      </c>
       <c r="D67" s="8" t="s">
         <v>73</v>
       </c>
@@ -3289,9 +4424,15 @@
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A68" s="10"/>
-      <c r="B68" s="11"/>
-      <c r="C68" s="11"/>
+      <c r="A68" s="10" t="s">
+        <v>318</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="11">
+        <v>0.60850429534912098</v>
+      </c>
       <c r="D68" s="11" t="s">
         <v>74</v>
       </c>
@@ -3312,9 +4453,15 @@
       </c>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A69" s="7"/>
-      <c r="B69" s="8"/>
-      <c r="C69" s="8"/>
+      <c r="A69" s="7" t="s">
+        <v>319</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" s="8">
+        <v>0.22384619712829501</v>
+      </c>
       <c r="D69" s="8" t="s">
         <v>75</v>
       </c>
@@ -3335,9 +4482,15 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A70" s="10"/>
-      <c r="B70" s="11"/>
-      <c r="C70" s="11"/>
+      <c r="A70" s="10" t="s">
+        <v>320</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C70" s="11">
+        <v>0.55266261100768999</v>
+      </c>
       <c r="D70" s="11" t="s">
         <v>76</v>
       </c>
@@ -3358,9 +4511,15 @@
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A71" s="7"/>
-      <c r="B71" s="8"/>
-      <c r="C71" s="8"/>
+      <c r="A71" s="7" t="s">
+        <v>321</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C71" s="8">
+        <v>0.22388839721679599</v>
+      </c>
       <c r="D71" s="8" t="s">
         <v>77</v>
       </c>
@@ -3381,9 +4540,15 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A72" s="10"/>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
+      <c r="A72" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C72" s="11">
+        <v>0.51312685012817305</v>
+      </c>
       <c r="D72" s="11" t="s">
         <v>78</v>
       </c>
@@ -3404,9 +4569,15 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A73" s="7"/>
-      <c r="B73" s="8"/>
-      <c r="C73" s="8"/>
+      <c r="A73" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C73" s="8">
+        <v>0.19146013259887601</v>
+      </c>
       <c r="D73" s="8" t="s">
         <v>79</v>
       </c>
@@ -3427,9 +4598,15 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A74" s="10"/>
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
+      <c r="A74" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C74" s="11">
+        <v>0.58962893486022905</v>
+      </c>
       <c r="D74" s="11" t="s">
         <v>80</v>
       </c>
@@ -3450,9 +4627,15 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A75" s="7"/>
-      <c r="B75" s="8"/>
-      <c r="C75" s="8"/>
+      <c r="A75" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C75" s="8">
+        <v>0.42420721054077098</v>
+      </c>
       <c r="D75" s="8" t="s">
         <v>81</v>
       </c>
@@ -3473,9 +4656,15 @@
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A76" s="10"/>
-      <c r="B76" s="11"/>
-      <c r="C76" s="11"/>
+      <c r="A76" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C76" s="11">
+        <v>0.56092762947082497</v>
+      </c>
       <c r="D76" s="11" t="s">
         <v>82</v>
       </c>
@@ -3496,9 +4685,15 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A77" s="7"/>
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
+      <c r="A77" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77" s="8">
+        <v>0.18892359733581501</v>
+      </c>
       <c r="D77" s="8" t="s">
         <v>83</v>
       </c>
@@ -3519,9 +4714,15 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A78" s="10"/>
-      <c r="B78" s="11"/>
-      <c r="C78" s="11"/>
+      <c r="A78" s="10" t="s">
+        <v>328</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C78" s="11">
+        <v>0.52262091636657704</v>
+      </c>
       <c r="D78" s="11" t="s">
         <v>84</v>
       </c>
@@ -3542,9 +4743,15 @@
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A79" s="7"/>
-      <c r="B79" s="8"/>
-      <c r="C79" s="8"/>
+      <c r="A79" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C79" s="8">
+        <v>0.17058753967285101</v>
+      </c>
       <c r="D79" s="8" t="s">
         <v>85</v>
       </c>
@@ -3565,9 +4772,15 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A80" s="10"/>
-      <c r="B80" s="11"/>
-      <c r="C80" s="11"/>
+      <c r="A80" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C80" s="11">
+        <v>0.89729022979736295</v>
+      </c>
       <c r="D80" s="11" t="s">
         <v>86</v>
       </c>
@@ -3588,9 +4801,15 @@
       </c>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A81" s="7"/>
-      <c r="B81" s="8"/>
-      <c r="C81" s="8"/>
+      <c r="A81" s="7" t="s">
+        <v>331</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C81" s="8">
+        <v>0.17688155174255299</v>
+      </c>
       <c r="D81" s="8" t="s">
         <v>87</v>
       </c>
@@ -3611,9 +4830,15 @@
       </c>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A82" s="10"/>
-      <c r="B82" s="11"/>
-      <c r="C82" s="11"/>
+      <c r="A82" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C82" s="11">
+        <v>0.15490198135375899</v>
+      </c>
       <c r="D82" s="11" t="s">
         <v>88</v>
       </c>
@@ -3634,9 +4859,15 @@
       </c>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A83" s="7"/>
-      <c r="B83" s="8"/>
-      <c r="C83" s="8"/>
+      <c r="A83" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C83" s="8">
+        <v>0.66412115097045898</v>
+      </c>
       <c r="D83" s="8" t="s">
         <v>89</v>
       </c>
@@ -3657,9 +4888,15 @@
       </c>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A84" s="10"/>
-      <c r="B84" s="11"/>
-      <c r="C84" s="11"/>
+      <c r="A84" s="10" t="s">
+        <v>334</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C84" s="11">
+        <v>0.16417956352233801</v>
+      </c>
       <c r="D84" s="11" t="s">
         <v>90</v>
       </c>
@@ -3680,9 +4917,15 @@
       </c>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A85" s="7"/>
-      <c r="B85" s="8"/>
-      <c r="C85" s="8"/>
+      <c r="A85" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C85" s="8">
+        <v>0.17815995216369601</v>
+      </c>
       <c r="D85" s="8" t="s">
         <v>91</v>
       </c>
@@ -3703,9 +4946,15 @@
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A86" s="10"/>
-      <c r="B86" s="11"/>
-      <c r="C86" s="11"/>
+      <c r="A86" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C86" s="11">
+        <v>0.47321844100952098</v>
+      </c>
       <c r="D86" s="11" t="s">
         <v>92</v>
       </c>
@@ -3726,9 +4975,15 @@
       </c>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A87" s="7"/>
-      <c r="B87" s="8"/>
-      <c r="C87" s="8"/>
+      <c r="A87" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C87" s="8">
+        <v>0.20443201065063399</v>
+      </c>
       <c r="D87" s="8" t="s">
         <v>93</v>
       </c>
@@ -3749,9 +5004,15 @@
       </c>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A88" s="10"/>
-      <c r="B88" s="11"/>
-      <c r="C88" s="11"/>
+      <c r="A88" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C88" s="11">
+        <v>0.16650128364562899</v>
+      </c>
       <c r="D88" s="11" t="s">
         <v>94</v>
       </c>
@@ -3772,9 +5033,15 @@
       </c>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A89" s="7"/>
-      <c r="B89" s="8"/>
-      <c r="C89" s="8"/>
+      <c r="A89" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C89" s="8">
+        <v>0.46969437599182101</v>
+      </c>
       <c r="D89" s="8" t="s">
         <v>95</v>
       </c>
@@ -3795,9 +5062,15 @@
       </c>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A90" s="10"/>
-      <c r="B90" s="11"/>
-      <c r="C90" s="11"/>
+      <c r="A90" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C90" s="11">
+        <v>0.60850167274475098</v>
+      </c>
       <c r="D90" s="11" t="s">
         <v>96</v>
       </c>
@@ -3818,9 +5091,15 @@
       </c>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A91" s="7"/>
-      <c r="B91" s="8"/>
-      <c r="C91" s="8"/>
+      <c r="A91" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C91" s="8">
+        <v>0.69072961807250899</v>
+      </c>
       <c r="D91" s="8" t="s">
         <v>97</v>
       </c>
@@ -3841,9 +5120,15 @@
       </c>
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A92" s="10"/>
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
+      <c r="A92" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C92" s="11">
+        <v>0.16004705429077101</v>
+      </c>
       <c r="D92" s="11" t="s">
         <v>98</v>
       </c>
@@ -3864,9 +5149,15 @@
       </c>
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A93" s="7"/>
-      <c r="B93" s="8"/>
-      <c r="C93" s="8"/>
+      <c r="A93" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C93" s="8">
+        <v>0.166557312011718</v>
+      </c>
       <c r="D93" s="8" t="s">
         <v>99</v>
       </c>
@@ -3887,9 +5178,15 @@
       </c>
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A94" s="10"/>
-      <c r="B94" s="11"/>
-      <c r="C94" s="11"/>
+      <c r="A94" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C94" s="11">
+        <v>0.17809796333312899</v>
+      </c>
       <c r="D94" s="11" t="s">
         <v>100</v>
       </c>
@@ -3910,9 +5207,15 @@
       </c>
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A95" s="7"/>
-      <c r="B95" s="8"/>
-      <c r="C95" s="8"/>
+      <c r="A95" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C95" s="8">
+        <v>0.22989678382873499</v>
+      </c>
       <c r="D95" s="8" t="s">
         <v>101</v>
       </c>
@@ -3933,9 +5236,15 @@
       </c>
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A96" s="10"/>
-      <c r="B96" s="11"/>
-      <c r="C96" s="11"/>
+      <c r="A96" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C96" s="11">
+        <v>0.59611082077026301</v>
+      </c>
       <c r="D96" s="11" t="s">
         <v>102</v>
       </c>
@@ -3956,9 +5265,15 @@
       </c>
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A97" s="7"/>
-      <c r="B97" s="8"/>
-      <c r="C97" s="8"/>
+      <c r="A97" s="7" t="s">
+        <v>347</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C97" s="8">
+        <v>0.41368675231933499</v>
+      </c>
       <c r="D97" s="8" t="s">
         <v>103</v>
       </c>
@@ -3979,9 +5294,15 @@
       </c>
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A98" s="10"/>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
+      <c r="A98" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C98" s="11">
+        <v>0.468215942382812</v>
+      </c>
       <c r="D98" s="11" t="s">
         <v>104</v>
       </c>
@@ -4002,9 +5323,15 @@
       </c>
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A99" s="7"/>
-      <c r="B99" s="8"/>
-      <c r="C99" s="8"/>
+      <c r="A99" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C99" s="8">
+        <v>0.47069001197814903</v>
+      </c>
       <c r="D99" s="8" t="s">
         <v>105</v>
       </c>
@@ -4025,9 +5352,15 @@
       </c>
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A100" s="10"/>
-      <c r="B100" s="11"/>
-      <c r="C100" s="11"/>
+      <c r="A100" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C100" s="11">
+        <v>0.45036292076110801</v>
+      </c>
       <c r="D100" s="11" t="s">
         <v>106</v>
       </c>
@@ -4048,9 +5381,15 @@
       </c>
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A101" s="7"/>
-      <c r="B101" s="8"/>
-      <c r="C101" s="8"/>
+      <c r="A101" s="7" t="s">
+        <v>351</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C101" s="8">
+        <v>0.45693588256835899</v>
+      </c>
       <c r="D101" s="8" t="s">
         <v>107</v>
       </c>
@@ -4071,9 +5410,15 @@
       </c>
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A102" s="10"/>
-      <c r="B102" s="11"/>
-      <c r="C102" s="11"/>
+      <c r="A102" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C102" s="11">
+        <v>1.283203125</v>
+      </c>
       <c r="D102" s="11" t="s">
         <v>108</v>
       </c>
@@ -4094,9 +5439,15 @@
       </c>
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A103" s="7"/>
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
+      <c r="A103" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C103" s="8">
+        <v>0.593713998794555</v>
+      </c>
       <c r="D103" s="8" t="s">
         <v>109</v>
       </c>
@@ -4117,9 +5468,15 @@
       </c>
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A104" s="10"/>
-      <c r="B104" s="11"/>
-      <c r="C104" s="11"/>
+      <c r="A104" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C104" s="11">
+        <v>0.57118177413940396</v>
+      </c>
       <c r="D104" s="11" t="s">
         <v>110</v>
       </c>
@@ -4140,9 +5497,15 @@
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A105" s="7"/>
-      <c r="B105" s="8"/>
-      <c r="C105" s="8"/>
+      <c r="A105" s="7" t="s">
+        <v>355</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" s="8">
+        <v>0.20302200317382799</v>
+      </c>
       <c r="D105" s="8" t="s">
         <v>111</v>
       </c>
@@ -4163,9 +5526,15 @@
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A106" s="10"/>
-      <c r="B106" s="11"/>
-      <c r="C106" s="11"/>
+      <c r="A106" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C106" s="11">
+        <v>0.1976318359375</v>
+      </c>
       <c r="D106" s="11" t="s">
         <v>112</v>
       </c>
@@ -4186,9 +5555,15 @@
       </c>
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A107" s="7"/>
-      <c r="B107" s="8"/>
-      <c r="C107" s="8"/>
+      <c r="A107" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C107" s="8">
+        <v>0.44295406341552701</v>
+      </c>
       <c r="D107" s="8" t="s">
         <v>113</v>
       </c>
@@ -4209,9 +5584,15 @@
       </c>
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A108" s="10"/>
-      <c r="B108" s="11"/>
-      <c r="C108" s="11"/>
+      <c r="A108" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C108" s="11">
+        <v>0.172296047210693</v>
+      </c>
       <c r="D108" s="11" t="s">
         <v>114</v>
       </c>
@@ -4232,9 +5613,15 @@
       </c>
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A109" s="7"/>
-      <c r="B109" s="8"/>
-      <c r="C109" s="8"/>
+      <c r="A109" s="7" t="s">
+        <v>359</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C109" s="8">
+        <v>0.98990082740783603</v>
+      </c>
       <c r="D109" s="8" t="s">
         <v>115</v>
       </c>
@@ -4255,9 +5642,15 @@
       </c>
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A110" s="10"/>
-      <c r="B110" s="11"/>
-      <c r="C110" s="11"/>
+      <c r="A110" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C110" s="11">
+        <v>0.423665761947631</v>
+      </c>
       <c r="D110" s="11" t="s">
         <v>116</v>
       </c>
@@ -4278,9 +5671,15 @@
       </c>
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A111" s="7"/>
-      <c r="B111" s="8"/>
-      <c r="C111" s="8"/>
+      <c r="A111" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C111" s="8">
+        <v>0.61156606674194303</v>
+      </c>
       <c r="D111" s="8" t="s">
         <v>117</v>
       </c>
@@ -4301,9 +5700,15 @@
       </c>
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A112" s="10"/>
-      <c r="B112" s="11"/>
-      <c r="C112" s="11"/>
+      <c r="A112" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C112" s="11">
+        <v>0.164831638336181</v>
+      </c>
       <c r="D112" s="11" t="s">
         <v>118</v>
       </c>
@@ -4324,9 +5729,15 @@
       </c>
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A113" s="7"/>
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
+      <c r="A113" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C113" s="8">
+        <v>0.23129153251647899</v>
+      </c>
       <c r="D113" s="8" t="s">
         <v>119</v>
       </c>
@@ -4347,9 +5758,15 @@
       </c>
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A114" s="10"/>
-      <c r="B114" s="11"/>
-      <c r="C114" s="11"/>
+      <c r="A114" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C114" s="11">
+        <v>0.72992944717407204</v>
+      </c>
       <c r="D114" s="11" t="s">
         <v>120</v>
       </c>
@@ -4370,9 +5787,15 @@
       </c>
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A115" s="7"/>
-      <c r="B115" s="8"/>
-      <c r="C115" s="8"/>
+      <c r="A115" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C115" s="8">
+        <v>0.17205500602722101</v>
+      </c>
       <c r="D115" s="8" t="s">
         <v>121</v>
       </c>
@@ -4393,9 +5816,15 @@
       </c>
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A116" s="10"/>
-      <c r="B116" s="11"/>
-      <c r="C116" s="11"/>
+      <c r="A116" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C116" s="11">
+        <v>0.164976596832275</v>
+      </c>
       <c r="D116" s="11" t="s">
         <v>122</v>
       </c>
@@ -4416,9 +5845,15 @@
       </c>
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A117" s="7"/>
-      <c r="B117" s="8"/>
-      <c r="C117" s="8"/>
+      <c r="A117" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C117" s="8">
+        <v>0.16637229919433499</v>
+      </c>
       <c r="D117" s="8" t="s">
         <v>123</v>
       </c>
@@ -4439,9 +5874,15 @@
       </c>
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A118" s="10"/>
-      <c r="B118" s="11"/>
-      <c r="C118" s="11"/>
+      <c r="A118" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C118" s="11">
+        <v>0.67828106880187899</v>
+      </c>
       <c r="D118" s="11" t="s">
         <v>124</v>
       </c>
@@ -4462,9 +5903,15 @@
       </c>
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A119" s="7"/>
-      <c r="B119" s="8"/>
-      <c r="C119" s="8"/>
+      <c r="A119" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C119" s="8">
+        <v>0.179522514343261</v>
+      </c>
       <c r="D119" s="8" t="s">
         <v>125</v>
       </c>
@@ -4485,9 +5932,15 @@
       </c>
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A120" s="10"/>
-      <c r="B120" s="11"/>
-      <c r="C120" s="11"/>
+      <c r="A120" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C120" s="11">
+        <v>0.58964467048644997</v>
+      </c>
       <c r="D120" s="11" t="s">
         <v>126</v>
       </c>
@@ -4508,9 +5961,15 @@
       </c>
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A121" s="7"/>
-      <c r="B121" s="8"/>
-      <c r="C121" s="8"/>
+      <c r="A121" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C121" s="8">
+        <v>0.16510510444641099</v>
+      </c>
       <c r="D121" s="8" t="s">
         <v>127</v>
       </c>
@@ -4531,9 +5990,15 @@
       </c>
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A122" s="10"/>
-      <c r="B122" s="11"/>
-      <c r="C122" s="11"/>
+      <c r="A122" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="B122" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C122" s="11">
+        <v>0.837563276290893</v>
+      </c>
       <c r="D122" s="11" t="s">
         <v>128</v>
       </c>
@@ -4554,9 +6019,15 @@
       </c>
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A123" s="7"/>
-      <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
+      <c r="A123" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C123" s="8">
+        <v>0.75990319252014105</v>
+      </c>
       <c r="D123" s="8" t="s">
         <v>129</v>
       </c>
@@ -4577,9 +6048,15 @@
       </c>
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A124" s="10"/>
-      <c r="B124" s="11"/>
-      <c r="C124" s="11"/>
+      <c r="A124" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C124" s="11">
+        <v>0.61714816093444802</v>
+      </c>
       <c r="D124" s="11" t="s">
         <v>130</v>
       </c>
@@ -4600,9 +6077,15 @@
       </c>
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A125" s="7"/>
-      <c r="B125" s="8"/>
-      <c r="C125" s="8"/>
+      <c r="A125" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C125" s="8">
+        <v>1.32692170143127</v>
+      </c>
       <c r="D125" s="8" t="s">
         <v>131</v>
       </c>
@@ -4623,9 +6106,15 @@
       </c>
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A126" s="10"/>
-      <c r="B126" s="11"/>
-      <c r="C126" s="11"/>
+      <c r="A126" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="B126" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C126" s="11">
+        <v>0.66475510597229004</v>
+      </c>
       <c r="D126" s="11" t="s">
         <v>132</v>
       </c>
@@ -4646,9 +6135,15 @@
       </c>
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A127" s="7"/>
-      <c r="B127" s="8"/>
-      <c r="C127" s="8"/>
+      <c r="A127" s="7" t="s">
+        <v>377</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C127" s="8">
+        <v>0.56747746467590299</v>
+      </c>
       <c r="D127" s="8" t="s">
         <v>133</v>
       </c>
@@ -4669,9 +6164,15 @@
       </c>
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A128" s="10"/>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
+      <c r="A128" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="B128" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C128" s="11">
+        <v>0.821058750152587</v>
+      </c>
       <c r="D128" s="11" t="s">
         <v>134</v>
       </c>
@@ -4692,9 +6193,15 @@
       </c>
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A129" s="7"/>
-      <c r="B129" s="8"/>
-      <c r="C129" s="8"/>
+      <c r="A129" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C129" s="8">
+        <v>0.65578770637512196</v>
+      </c>
       <c r="D129" s="8" t="s">
         <v>135</v>
       </c>
@@ -4715,9 +6222,15 @@
       </c>
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A130" s="10"/>
-      <c r="B130" s="11"/>
-      <c r="C130" s="11"/>
+      <c r="A130" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="B130" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C130" s="11">
+        <v>0.79100561141967696</v>
+      </c>
       <c r="D130" s="11" t="s">
         <v>136</v>
       </c>
@@ -4738,9 +6251,15 @@
       </c>
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A131" s="7"/>
-      <c r="B131" s="8"/>
-      <c r="C131" s="8"/>
+      <c r="A131" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C131" s="8">
+        <v>0.667458295822143</v>
+      </c>
       <c r="D131" s="8" t="s">
         <v>137</v>
       </c>
@@ -4761,9 +6280,15 @@
       </c>
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A132" s="10"/>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
+      <c r="A132" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="B132" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C132" s="11">
+        <v>0.67611932754516602</v>
+      </c>
       <c r="D132" s="11" t="s">
         <v>138</v>
       </c>
@@ -4784,9 +6309,15 @@
       </c>
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A133" s="7"/>
-      <c r="B133" s="8"/>
-      <c r="C133" s="8"/>
+      <c r="A133" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="B133" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C133" s="8">
+        <v>0.670462846755981</v>
+      </c>
       <c r="D133" s="8" t="s">
         <v>139</v>
       </c>
@@ -4807,9 +6338,15 @@
       </c>
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A134" s="10"/>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
+      <c r="A134" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="B134" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C134" s="11">
+        <v>0.59122014045715299</v>
+      </c>
       <c r="D134" s="11" t="s">
         <v>140</v>
       </c>
@@ -4830,9 +6367,15 @@
       </c>
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A135" s="7"/>
-      <c r="B135" s="8"/>
-      <c r="C135" s="8"/>
+      <c r="A135" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="B135" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C135" s="8">
+        <v>0.16102409362792899</v>
+      </c>
       <c r="D135" s="8" t="s">
         <v>141</v>
       </c>
@@ -4853,9 +6396,15 @@
       </c>
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A136" s="10"/>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
+      <c r="A136" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="B136" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C136" s="11">
+        <v>0.968511343002319</v>
+      </c>
       <c r="D136" s="11" t="s">
         <v>142</v>
       </c>
@@ -4876,9 +6425,15 @@
       </c>
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A137" s="7"/>
-      <c r="B137" s="8"/>
-      <c r="C137" s="8"/>
+      <c r="A137" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="B137" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C137" s="8">
+        <v>0.85265851020812899</v>
+      </c>
       <c r="D137" s="8" t="s">
         <v>143</v>
       </c>
@@ -4899,9 +6454,15 @@
       </c>
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A138" s="10"/>
-      <c r="B138" s="11"/>
-      <c r="C138" s="11"/>
+      <c r="A138" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="B138" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C138" s="11">
+        <v>0.52807974815368597</v>
+      </c>
       <c r="D138" s="11" t="s">
         <v>144</v>
       </c>
@@ -4922,9 +6483,15 @@
       </c>
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A139" s="7"/>
-      <c r="B139" s="8"/>
-      <c r="C139" s="8"/>
+      <c r="A139" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="B139" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C139" s="8">
+        <v>0.93557095527648904</v>
+      </c>
       <c r="D139" s="8" t="s">
         <v>145</v>
       </c>
@@ -4945,9 +6512,15 @@
       </c>
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A140" s="10"/>
-      <c r="B140" s="11"/>
-      <c r="C140" s="11"/>
+      <c r="A140" s="10" t="s">
+        <v>390</v>
+      </c>
+      <c r="B140" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C140" s="11">
+        <v>0.76749587059020996</v>
+      </c>
       <c r="D140" s="11" t="s">
         <v>146</v>
       </c>
@@ -4968,9 +6541,15 @@
       </c>
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A141" s="7"/>
-      <c r="B141" s="8"/>
-      <c r="C141" s="8"/>
+      <c r="A141" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="B141" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C141" s="8">
+        <v>0.17059302330017001</v>
+      </c>
       <c r="D141" s="8" t="s">
         <v>147</v>
       </c>
@@ -4991,9 +6570,15 @@
       </c>
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A142" s="10"/>
-      <c r="B142" s="11"/>
-      <c r="C142" s="11"/>
+      <c r="A142" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="B142" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C142" s="11">
+        <v>0.16503524780273399</v>
+      </c>
       <c r="D142" s="11" t="s">
         <v>148</v>
       </c>
@@ -5014,9 +6599,15 @@
       </c>
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A143" s="7"/>
-      <c r="B143" s="8"/>
-      <c r="C143" s="8"/>
+      <c r="A143" s="7" t="s">
+        <v>393</v>
+      </c>
+      <c r="B143" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C143" s="8">
+        <v>0.40426158905029203</v>
+      </c>
       <c r="D143" s="8" t="s">
         <v>149</v>
       </c>
@@ -5037,9 +6628,15 @@
       </c>
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A144" s="10"/>
-      <c r="B144" s="11"/>
-      <c r="C144" s="11"/>
+      <c r="A144" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="B144" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C144" s="11">
+        <v>0.16589260101318301</v>
+      </c>
       <c r="D144" s="11" t="s">
         <v>150</v>
       </c>
@@ -5060,9 +6657,15 @@
       </c>
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A145" s="7"/>
-      <c r="B145" s="8"/>
-      <c r="C145" s="8"/>
+      <c r="A145" s="7" t="s">
+        <v>395</v>
+      </c>
+      <c r="B145" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C145" s="8">
+        <v>0.65723896026611295</v>
+      </c>
       <c r="D145" s="8" t="s">
         <v>151</v>
       </c>
@@ -5083,9 +6686,15 @@
       </c>
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A146" s="10"/>
-      <c r="B146" s="11"/>
-      <c r="C146" s="11"/>
+      <c r="A146" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B146" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C146" s="11">
+        <v>0.16569018363952601</v>
+      </c>
       <c r="D146" s="11" t="s">
         <v>152</v>
       </c>
@@ -5106,9 +6715,15 @@
       </c>
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A147" s="7"/>
-      <c r="B147" s="8"/>
-      <c r="C147" s="8"/>
+      <c r="A147" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="B147" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C147" s="8">
+        <v>0.38298416137695301</v>
+      </c>
       <c r="D147" s="8" t="s">
         <v>153</v>
       </c>
@@ -5129,9 +6744,15 @@
       </c>
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A148" s="10"/>
-      <c r="B148" s="11"/>
-      <c r="C148" s="11"/>
+      <c r="A148" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="B148" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C148" s="11">
+        <v>0.164352416992187</v>
+      </c>
       <c r="D148" s="11" t="s">
         <v>154</v>
       </c>
@@ -5152,9 +6773,15 @@
       </c>
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A149" s="7"/>
-      <c r="B149" s="8"/>
-      <c r="C149" s="8"/>
+      <c r="A149" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="B149" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C149" s="8">
+        <v>0.48286223411559998</v>
+      </c>
       <c r="D149" s="8" t="s">
         <v>155</v>
       </c>
@@ -5175,9 +6802,15 @@
       </c>
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A150" s="10"/>
-      <c r="B150" s="11"/>
-      <c r="C150" s="11"/>
+      <c r="A150" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="B150" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C150" s="11">
+        <v>0.53257179260253895</v>
+      </c>
       <c r="D150" s="11" t="s">
         <v>156</v>
       </c>
@@ -5198,9 +6831,15 @@
       </c>
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A151" s="7"/>
-      <c r="B151" s="8"/>
-      <c r="C151" s="8"/>
+      <c r="A151" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="B151" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C151" s="8">
+        <v>0.158925056457519</v>
+      </c>
       <c r="D151" s="8" t="s">
         <v>157</v>
       </c>
@@ -5221,9 +6860,15 @@
       </c>
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A152" s="10"/>
-      <c r="B152" s="11"/>
-      <c r="C152" s="11"/>
+      <c r="A152" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="B152" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C152" s="11">
+        <v>0.63991928100585904</v>
+      </c>
       <c r="D152" s="11" t="s">
         <v>158</v>
       </c>
@@ -5244,9 +6889,15 @@
       </c>
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A153" s="7"/>
-      <c r="B153" s="8"/>
-      <c r="C153" s="8"/>
+      <c r="A153" s="7" t="s">
+        <v>403</v>
+      </c>
+      <c r="B153" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C153" s="8">
+        <v>0.15931057929992601</v>
+      </c>
       <c r="D153" s="8" t="s">
         <v>159</v>
       </c>
@@ -5267,9 +6918,15 @@
       </c>
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A154" s="10"/>
-      <c r="B154" s="11"/>
-      <c r="C154" s="11"/>
+      <c r="A154" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="B154" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C154" s="11">
+        <v>0.68768620491027799</v>
+      </c>
       <c r="D154" s="11" t="s">
         <v>160</v>
       </c>
@@ -5290,9 +6947,15 @@
       </c>
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A155" s="7"/>
-      <c r="B155" s="8"/>
-      <c r="C155" s="8"/>
+      <c r="A155" s="7" t="s">
+        <v>405</v>
+      </c>
+      <c r="B155" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C155" s="8">
+        <v>0.16060185432433999</v>
+      </c>
       <c r="D155" s="8" t="s">
         <v>161</v>
       </c>
@@ -5313,9 +6976,15 @@
       </c>
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A156" s="10"/>
-      <c r="B156" s="11"/>
-      <c r="C156" s="11"/>
+      <c r="A156" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="B156" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C156" s="11">
+        <v>0.71055889129638605</v>
+      </c>
       <c r="D156" s="11" t="s">
         <v>162</v>
       </c>
@@ -5336,9 +7005,15 @@
       </c>
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A157" s="7"/>
-      <c r="B157" s="8"/>
-      <c r="C157" s="8"/>
+      <c r="A157" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="B157" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C157" s="8">
+        <v>0.77157068252563399</v>
+      </c>
       <c r="D157" s="8" t="s">
         <v>163</v>
       </c>
@@ -5359,9 +7034,15 @@
       </c>
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A158" s="10"/>
-      <c r="B158" s="11"/>
-      <c r="C158" s="11"/>
+      <c r="A158" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="B158" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C158" s="11">
+        <v>0.62589168548583896</v>
+      </c>
       <c r="D158" s="11" t="s">
         <v>164</v>
       </c>
@@ -5382,9 +7063,15 @@
       </c>
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A159" s="7"/>
-      <c r="B159" s="8"/>
-      <c r="C159" s="8"/>
+      <c r="A159" s="7" t="s">
+        <v>409</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C159" s="8">
+        <v>0.163355112075805</v>
+      </c>
       <c r="D159" s="8" t="s">
         <v>165</v>
       </c>
@@ -5405,9 +7092,15 @@
       </c>
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A160" s="10"/>
-      <c r="B160" s="11"/>
-      <c r="C160" s="11"/>
+      <c r="A160" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="B160" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C160" s="11">
+        <v>0.54885506629943803</v>
+      </c>
       <c r="D160" s="11" t="s">
         <v>166</v>
       </c>
@@ -5428,9 +7121,15 @@
       </c>
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A161" s="7"/>
-      <c r="B161" s="8"/>
-      <c r="C161" s="8"/>
+      <c r="A161" s="7" t="s">
+        <v>411</v>
+      </c>
+      <c r="B161" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C161" s="8">
+        <v>0.16453742980957001</v>
+      </c>
       <c r="D161" s="8" t="s">
         <v>167</v>
       </c>
@@ -5451,9 +7150,15 @@
       </c>
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A162" s="10"/>
-      <c r="B162" s="11"/>
-      <c r="C162" s="11"/>
+      <c r="A162" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="B162" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C162" s="11">
+        <v>0.81094694137573198</v>
+      </c>
       <c r="D162" s="11" t="s">
         <v>168</v>
       </c>
@@ -5474,9 +7179,15 @@
       </c>
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A163" s="7"/>
-      <c r="B163" s="8"/>
-      <c r="C163" s="8"/>
+      <c r="A163" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="B163" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C163" s="8">
+        <v>0.218562841415405</v>
+      </c>
       <c r="D163" s="8" t="s">
         <v>169</v>
       </c>
@@ -5497,9 +7208,15 @@
       </c>
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A164" s="10"/>
-      <c r="B164" s="11"/>
-      <c r="C164" s="11"/>
+      <c r="A164" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="B164" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C164" s="11">
+        <v>0.16717553138732899</v>
+      </c>
       <c r="D164" s="11" t="s">
         <v>170</v>
       </c>
@@ -5520,9 +7237,15 @@
       </c>
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A165" s="7"/>
-      <c r="B165" s="8"/>
-      <c r="C165" s="8"/>
+      <c r="A165" s="7" t="s">
+        <v>415</v>
+      </c>
+      <c r="B165" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C165" s="8">
+        <v>0.63217973709106401</v>
+      </c>
       <c r="D165" s="8" t="s">
         <v>171</v>
       </c>
@@ -5543,9 +7266,15 @@
       </c>
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A166" s="10"/>
-      <c r="B166" s="11"/>
-      <c r="C166" s="11"/>
+      <c r="A166" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="B166" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C166" s="11">
+        <v>9.6984953880310005</v>
+      </c>
       <c r="D166" s="11" t="s">
         <v>172</v>
       </c>
@@ -5566,9 +7295,15 @@
       </c>
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A167" s="7"/>
-      <c r="B167" s="8"/>
-      <c r="C167" s="8"/>
+      <c r="A167" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="B167" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C167" s="8">
+        <v>101.55069398880001</v>
+      </c>
       <c r="D167" s="8" t="s">
         <v>174</v>
       </c>
@@ -5589,9 +7324,15 @@
       </c>
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A168" s="10"/>
-      <c r="B168" s="11"/>
-      <c r="C168" s="11"/>
+      <c r="A168" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="B168" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C168" s="11">
+        <v>100.980442523956</v>
+      </c>
       <c r="D168" s="11" t="s">
         <v>175</v>
       </c>
@@ -5612,9 +7353,15 @@
       </c>
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A169" s="7"/>
-      <c r="B169" s="8"/>
-      <c r="C169" s="8"/>
+      <c r="A169" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="B169" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C169" s="8">
+        <v>100.540321350097</v>
+      </c>
       <c r="D169" s="8" t="s">
         <v>176</v>
       </c>
@@ -5635,9 +7382,15 @@
       </c>
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A170" s="10"/>
-      <c r="B170" s="11"/>
-      <c r="C170" s="11"/>
+      <c r="A170" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="B170" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C170" s="11">
+        <v>100.101659536361</v>
+      </c>
       <c r="D170" s="11" t="s">
         <v>177</v>
       </c>
@@ -5658,9 +7411,15 @@
       </c>
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A171" s="7"/>
-      <c r="B171" s="8"/>
-      <c r="C171" s="8"/>
+      <c r="A171" s="7" t="s">
+        <v>421</v>
+      </c>
+      <c r="B171" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C171" s="8">
+        <v>100.1033577919</v>
+      </c>
       <c r="D171" s="8" t="s">
         <v>178</v>
       </c>
@@ -5681,9 +7440,15 @@
       </c>
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A172" s="10"/>
-      <c r="B172" s="11"/>
-      <c r="C172" s="11"/>
+      <c r="A172" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="B172" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C172" s="11">
+        <v>100.103155136108</v>
+      </c>
       <c r="D172" s="11" t="s">
         <v>179</v>
       </c>
@@ -5704,9 +7469,15 @@
       </c>
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A173" s="7"/>
-      <c r="B173" s="8"/>
-      <c r="C173" s="8"/>
+      <c r="A173" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="B173" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C173" s="8">
+        <v>100.10395026206901</v>
+      </c>
       <c r="D173" s="8" t="s">
         <v>180</v>
       </c>
@@ -5727,9 +7498,15 @@
       </c>
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A174" s="10"/>
-      <c r="B174" s="11"/>
-      <c r="C174" s="11"/>
+      <c r="A174" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="B174" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C174" s="11">
+        <v>100.103672027587</v>
+      </c>
       <c r="D174" s="11" t="s">
         <v>181</v>
       </c>
@@ -5750,9 +7527,15 @@
       </c>
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A175" s="7"/>
-      <c r="B175" s="8"/>
-      <c r="C175" s="8"/>
+      <c r="A175" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="B175" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C175" s="8">
+        <v>100.104493379592</v>
+      </c>
       <c r="D175" s="8" t="s">
         <v>182</v>
       </c>
@@ -5773,9 +7556,15 @@
       </c>
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A176" s="10"/>
-      <c r="B176" s="11"/>
-      <c r="C176" s="11"/>
+      <c r="A176" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="B176" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C176" s="11">
+        <v>100.104610681533</v>
+      </c>
       <c r="D176" s="11" t="s">
         <v>183</v>
       </c>
@@ -5796,9 +7585,15 @@
       </c>
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A177" s="7"/>
-      <c r="B177" s="8"/>
-      <c r="C177" s="8"/>
+      <c r="A177" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="B177" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C177" s="8">
+        <v>2.8489601612090998</v>
+      </c>
       <c r="D177" s="8" t="s">
         <v>184</v>
       </c>
@@ -5819,9 +7614,15 @@
       </c>
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A178" s="10"/>
-      <c r="B178" s="11"/>
-      <c r="C178" s="11"/>
+      <c r="A178" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="B178" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C178" s="11">
+        <v>100.104613304138</v>
+      </c>
       <c r="D178" s="11" t="s">
         <v>185</v>
       </c>
@@ -5842,9 +7643,15 @@
       </c>
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A179" s="7"/>
-      <c r="B179" s="8"/>
-      <c r="C179" s="8"/>
+      <c r="A179" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="B179" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C179" s="8">
+        <v>0.24106359481811501</v>
+      </c>
       <c r="D179" s="8" t="s">
         <v>186</v>
       </c>
@@ -5865,9 +7672,15 @@
       </c>
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A180" s="10"/>
-      <c r="B180" s="11"/>
-      <c r="C180" s="11"/>
+      <c r="A180" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="B180" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C180" s="11">
+        <v>0.192982196807861</v>
+      </c>
       <c r="D180" s="11" t="s">
         <v>187</v>
       </c>
@@ -5888,9 +7701,15 @@
       </c>
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A181" s="7"/>
-      <c r="B181" s="8"/>
-      <c r="C181" s="8"/>
+      <c r="A181" s="7" t="s">
+        <v>431</v>
+      </c>
+      <c r="B181" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C181" s="8">
+        <v>5.3734707832336399</v>
+      </c>
       <c r="D181" s="8" t="s">
         <v>188</v>
       </c>
@@ -5911,9 +7730,15 @@
       </c>
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A182" s="10"/>
-      <c r="B182" s="11"/>
-      <c r="C182" s="11"/>
+      <c r="A182" s="10" t="s">
+        <v>432</v>
+      </c>
+      <c r="B182" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C182" s="11">
+        <v>100.10366749763401</v>
+      </c>
       <c r="D182" s="11" t="s">
         <v>189</v>
       </c>
@@ -5934,9 +7759,15 @@
       </c>
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A183" s="7"/>
-      <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
+      <c r="A183" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="B183" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C183" s="8">
+        <v>100.06978392601</v>
+      </c>
       <c r="D183" s="8" t="s">
         <v>190</v>
       </c>
@@ -5957,9 +7788,15 @@
       </c>
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A184" s="10"/>
-      <c r="B184" s="11"/>
-      <c r="C184" s="11"/>
+      <c r="A184" s="10" t="s">
+        <v>434</v>
+      </c>
+      <c r="B184" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C184" s="11">
+        <v>0.22595858573913499</v>
+      </c>
       <c r="D184" s="11" t="s">
         <v>191</v>
       </c>
@@ -5980,9 +7817,15 @@
       </c>
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A185" s="7"/>
-      <c r="B185" s="8"/>
-      <c r="C185" s="8"/>
+      <c r="A185" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="B185" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C185" s="8">
+        <v>0.18755245208740201</v>
+      </c>
       <c r="D185" s="8" t="s">
         <v>192</v>
       </c>
@@ -6003,9 +7846,15 @@
       </c>
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A186" s="10"/>
-      <c r="B186" s="11"/>
-      <c r="C186" s="11"/>
+      <c r="A186" s="10" t="s">
+        <v>436</v>
+      </c>
+      <c r="B186" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C186" s="11">
+        <v>100.096255540847</v>
+      </c>
       <c r="D186" s="11" t="s">
         <v>193</v>
       </c>
@@ -6026,9 +7875,15 @@
       </c>
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A187" s="7"/>
-      <c r="B187" s="8"/>
-      <c r="C187" s="8"/>
+      <c r="A187" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B187" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C187" s="8">
+        <v>4.08691334724426</v>
+      </c>
       <c r="D187" s="8" t="s">
         <v>194</v>
       </c>
@@ -6049,9 +7904,15 @@
       </c>
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A188" s="10"/>
-      <c r="B188" s="11"/>
-      <c r="C188" s="11"/>
+      <c r="A188" s="10" t="s">
+        <v>438</v>
+      </c>
+      <c r="B188" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C188" s="11">
+        <v>4.2244009971618599</v>
+      </c>
       <c r="D188" s="11" t="s">
         <v>195</v>
       </c>
@@ -6072,9 +7933,15 @@
       </c>
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A189" s="7"/>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
+      <c r="A189" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="B189" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C189" s="8">
+        <v>4.2180705070495597</v>
+      </c>
       <c r="D189" s="8" t="s">
         <v>196</v>
       </c>
@@ -6095,9 +7962,15 @@
       </c>
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A190" s="10"/>
-      <c r="B190" s="11"/>
-      <c r="C190" s="11"/>
+      <c r="A190" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="B190" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C190" s="11">
+        <v>100.104227542877</v>
+      </c>
       <c r="D190" s="11" t="s">
         <v>197</v>
       </c>
@@ -6118,9 +7991,15 @@
       </c>
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A191" s="7"/>
-      <c r="B191" s="8"/>
-      <c r="C191" s="8"/>
+      <c r="A191" s="7" t="s">
+        <v>441</v>
+      </c>
+      <c r="B191" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C191" s="8">
+        <v>100.104158639907</v>
+      </c>
       <c r="D191" s="8" t="s">
         <v>198</v>
       </c>
@@ -6141,9 +8020,15 @@
       </c>
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A192" s="10"/>
-      <c r="B192" s="11"/>
-      <c r="C192" s="11"/>
+      <c r="A192" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="B192" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C192" s="11">
+        <v>100.106792449951</v>
+      </c>
       <c r="D192" s="11" t="s">
         <v>199</v>
       </c>
@@ -6164,9 +8049,15 @@
       </c>
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A193" s="7"/>
-      <c r="B193" s="8"/>
-      <c r="C193" s="8"/>
+      <c r="A193" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="B193" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C193" s="8">
+        <v>100.103860378265</v>
+      </c>
       <c r="D193" s="8" t="s">
         <v>200</v>
       </c>
@@ -6187,9 +8078,15 @@
       </c>
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A194" s="10"/>
-      <c r="B194" s="11"/>
-      <c r="C194" s="11"/>
+      <c r="A194" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="B194" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C194" s="11">
+        <v>100.103489637374</v>
+      </c>
       <c r="D194" s="11" t="s">
         <v>201</v>
       </c>
@@ -6210,9 +8107,15 @@
       </c>
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A195" s="7"/>
-      <c r="B195" s="8"/>
-      <c r="C195" s="8"/>
+      <c r="A195" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="B195" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C195" s="8">
+        <v>3.3044857978820801</v>
+      </c>
       <c r="D195" s="8" t="s">
         <v>202</v>
       </c>
@@ -6233,9 +8136,15 @@
       </c>
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A196" s="10"/>
-      <c r="B196" s="11"/>
-      <c r="C196" s="11"/>
+      <c r="A196" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="B196" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C196" s="11">
+        <v>100.10417795181201</v>
+      </c>
       <c r="D196" s="11" t="s">
         <v>203</v>
       </c>
@@ -6256,9 +8165,15 @@
       </c>
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A197" s="7"/>
-      <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
+      <c r="A197" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="B197" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C197" s="8">
+        <v>100.104630231857</v>
+      </c>
       <c r="D197" s="8" t="s">
         <v>204</v>
       </c>
@@ -6279,9 +8194,15 @@
       </c>
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A198" s="10"/>
-      <c r="B198" s="11"/>
-      <c r="C198" s="11"/>
+      <c r="A198" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="B198" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C198" s="11">
+        <v>100.104633331298</v>
+      </c>
       <c r="D198" s="11" t="s">
         <v>205</v>
       </c>
@@ -6302,9 +8223,15 @@
       </c>
     </row>
     <row r="199" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A199" s="7"/>
-      <c r="B199" s="8"/>
-      <c r="C199" s="8"/>
+      <c r="A199" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="B199" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C199" s="8">
+        <v>100.017288923263</v>
+      </c>
       <c r="D199" s="8" t="s">
         <v>206</v>
       </c>
@@ -6325,9 +8252,15 @@
       </c>
     </row>
     <row r="200" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A200" s="10"/>
-      <c r="B200" s="11"/>
-      <c r="C200" s="11"/>
+      <c r="A200" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="B200" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C200" s="11">
+        <v>3.0213925838470401</v>
+      </c>
       <c r="D200" s="11" t="s">
         <v>207</v>
       </c>
@@ -6348,9 +8281,15 @@
       </c>
     </row>
     <row r="201" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A201" s="7"/>
-      <c r="B201" s="8"/>
-      <c r="C201" s="8"/>
+      <c r="A201" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="B201" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C201" s="8">
+        <v>8.4429767131805402</v>
+      </c>
       <c r="D201" s="8" t="s">
         <v>208</v>
       </c>
@@ -6371,9 +8310,15 @@
       </c>
     </row>
     <row r="202" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A202" s="10"/>
-      <c r="B202" s="11"/>
-      <c r="C202" s="11"/>
+      <c r="A202" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="B202" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C202" s="11">
+        <v>0.194552421569824</v>
+      </c>
       <c r="D202" s="11" t="s">
         <v>209</v>
       </c>
@@ -6394,9 +8339,15 @@
       </c>
     </row>
     <row r="203" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A203" s="7"/>
-      <c r="B203" s="8"/>
-      <c r="C203" s="8"/>
+      <c r="A203" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="B203" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C203" s="8">
+        <v>100.103674650192</v>
+      </c>
       <c r="D203" s="8" t="s">
         <v>210</v>
       </c>
@@ -6417,9 +8368,15 @@
       </c>
     </row>
     <row r="204" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A204" s="10"/>
-      <c r="B204" s="11"/>
-      <c r="C204" s="11"/>
+      <c r="A204" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="B204" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C204" s="11">
+        <v>100.10447359085001</v>
+      </c>
       <c r="D204" s="11" t="s">
         <v>211</v>
       </c>
@@ -6440,9 +8397,15 @@
       </c>
     </row>
     <row r="205" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A205" s="7"/>
-      <c r="B205" s="8"/>
-      <c r="C205" s="8"/>
+      <c r="A205" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="B205" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C205" s="8">
+        <v>100.0120139122</v>
+      </c>
       <c r="D205" s="8" t="s">
         <v>212</v>
       </c>
@@ -6463,9 +8426,15 @@
       </c>
     </row>
     <row r="206" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A206" s="10"/>
-      <c r="B206" s="11"/>
-      <c r="C206" s="11"/>
+      <c r="A206" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="B206" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C206" s="11">
+        <v>7.8902812004089302</v>
+      </c>
       <c r="D206" s="11" t="s">
         <v>213</v>
       </c>
@@ -6486,9 +8455,15 @@
       </c>
     </row>
     <row r="207" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A207" s="7"/>
-      <c r="B207" s="8"/>
-      <c r="C207" s="8"/>
+      <c r="A207" s="7" t="s">
+        <v>457</v>
+      </c>
+      <c r="B207" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C207" s="8">
+        <v>3.0788586139678902</v>
+      </c>
       <c r="D207" s="8" t="s">
         <v>214</v>
       </c>
@@ -6509,9 +8484,15 @@
       </c>
     </row>
     <row r="208" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A208" s="10"/>
-      <c r="B208" s="11"/>
-      <c r="C208" s="11"/>
+      <c r="A208" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="B208" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C208" s="11">
+        <v>100.103590726852</v>
+      </c>
       <c r="D208" s="11" t="s">
         <v>215</v>
       </c>
@@ -6532,9 +8513,15 @@
       </c>
     </row>
     <row r="209" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A209" s="7"/>
-      <c r="B209" s="8"/>
-      <c r="C209" s="8"/>
+      <c r="A209" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="B209" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C209" s="8">
+        <v>100.104437589645</v>
+      </c>
       <c r="D209" s="8" t="s">
         <v>216</v>
       </c>
@@ -6555,9 +8542,15 @@
       </c>
     </row>
     <row r="210" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A210" s="10"/>
-      <c r="B210" s="11"/>
-      <c r="C210" s="11"/>
+      <c r="A210" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="B210" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C210" s="11">
+        <v>100.10421276092499</v>
+      </c>
       <c r="D210" s="11" t="s">
         <v>217</v>
       </c>
@@ -6578,9 +8571,15 @@
       </c>
     </row>
     <row r="211" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A211" s="7"/>
-      <c r="B211" s="8"/>
-      <c r="C211" s="8"/>
+      <c r="A211" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="B211" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C211" s="8">
+        <v>7.5950124263763401</v>
+      </c>
       <c r="D211" s="8" t="s">
         <v>218</v>
       </c>
@@ -6601,9 +8600,15 @@
       </c>
     </row>
     <row r="212" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A212" s="10"/>
-      <c r="B212" s="11"/>
-      <c r="C212" s="11"/>
+      <c r="A212" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="B212" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C212" s="11">
+        <v>0.16583251953125</v>
+      </c>
       <c r="D212" s="11" t="s">
         <v>219</v>
       </c>
@@ -6624,9 +8629,15 @@
       </c>
     </row>
     <row r="213" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A213" s="7"/>
-      <c r="B213" s="8"/>
-      <c r="C213" s="8"/>
+      <c r="A213" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="B213" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C213" s="8">
+        <v>9.75142002105712</v>
+      </c>
       <c r="D213" s="8" t="s">
         <v>220</v>
       </c>
@@ -6647,9 +8658,15 @@
       </c>
     </row>
     <row r="214" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A214" s="10"/>
-      <c r="B214" s="11"/>
-      <c r="C214" s="11"/>
+      <c r="A214" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="B214" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C214" s="11">
+        <v>8.6685678958892805</v>
+      </c>
       <c r="D214" s="11" t="s">
         <v>221</v>
       </c>
@@ -6670,9 +8687,15 @@
       </c>
     </row>
     <row r="215" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A215" s="7"/>
-      <c r="B215" s="8"/>
-      <c r="C215" s="8"/>
+      <c r="A215" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="B215" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C215" s="8">
+        <v>2.2575731277465798</v>
+      </c>
       <c r="D215" s="8" t="s">
         <v>222</v>
       </c>
@@ -6693,9 +8716,15 @@
       </c>
     </row>
     <row r="216" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A216" s="10"/>
-      <c r="B216" s="11"/>
-      <c r="C216" s="11"/>
+      <c r="A216" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="B216" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C216" s="11">
+        <v>100.00971794128399</v>
+      </c>
       <c r="D216" s="11" t="s">
         <v>223</v>
       </c>
@@ -6716,9 +8745,15 @@
       </c>
     </row>
     <row r="217" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A217" s="7"/>
-      <c r="B217" s="8"/>
-      <c r="C217" s="8"/>
+      <c r="A217" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="B217" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C217" s="8">
+        <v>100.10463571548399</v>
+      </c>
       <c r="D217" s="8" t="s">
         <v>224</v>
       </c>
@@ -6739,9 +8774,15 @@
       </c>
     </row>
     <row r="218" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A218" s="10"/>
-      <c r="B218" s="11"/>
-      <c r="C218" s="11"/>
+      <c r="A218" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="B218" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C218" s="11">
+        <v>100.05347633361799</v>
+      </c>
       <c r="D218" s="11" t="s">
         <v>225</v>
       </c>
@@ -6762,9 +8803,15 @@
       </c>
     </row>
     <row r="219" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A219" s="7"/>
-      <c r="B219" s="8"/>
-      <c r="C219" s="8"/>
+      <c r="A219" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="B219" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C219" s="8">
+        <v>100.103863477706</v>
+      </c>
       <c r="D219" s="8" t="s">
         <v>226</v>
       </c>
@@ -6785,9 +8832,15 @@
       </c>
     </row>
     <row r="220" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A220" s="10"/>
-      <c r="B220" s="11"/>
-      <c r="C220" s="11"/>
+      <c r="A220" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="B220" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C220" s="11">
+        <v>100.10406970977699</v>
+      </c>
       <c r="D220" s="11" t="s">
         <v>227</v>
       </c>
@@ -6808,9 +8861,15 @@
       </c>
     </row>
     <row r="221" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A221" s="7"/>
-      <c r="B221" s="8"/>
-      <c r="C221" s="8"/>
+      <c r="A221" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="B221" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C221" s="8">
+        <v>100.104673624038</v>
+      </c>
       <c r="D221" s="8" t="s">
         <v>228</v>
       </c>
@@ -6831,9 +8890,15 @@
       </c>
     </row>
     <row r="222" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A222" s="10"/>
-      <c r="B222" s="11"/>
-      <c r="C222" s="11"/>
+      <c r="A222" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B222" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C222" s="11">
+        <v>100.10390734672499</v>
+      </c>
       <c r="D222" s="11" t="s">
         <v>229</v>
       </c>
@@ -6854,9 +8919,15 @@
       </c>
     </row>
     <row r="223" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A223" s="7"/>
-      <c r="B223" s="8"/>
-      <c r="C223" s="8"/>
+      <c r="A223" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="B223" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C223" s="8">
+        <v>100.103841304779</v>
+      </c>
       <c r="D223" s="8" t="s">
         <v>230</v>
       </c>
@@ -6877,9 +8948,15 @@
       </c>
     </row>
     <row r="224" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A224" s="10"/>
-      <c r="B224" s="11"/>
-      <c r="C224" s="11"/>
+      <c r="A224" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="B224" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C224" s="11">
+        <v>100.104554414749</v>
+      </c>
       <c r="D224" s="11" t="s">
         <v>231</v>
       </c>
@@ -6900,9 +8977,15 @@
       </c>
     </row>
     <row r="225" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A225" s="7"/>
-      <c r="B225" s="8"/>
-      <c r="C225" s="8"/>
+      <c r="A225" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="B225" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C225" s="8">
+        <v>100.104022979736</v>
+      </c>
       <c r="D225" s="8" t="s">
         <v>232</v>
       </c>
@@ -6923,9 +9006,15 @@
       </c>
     </row>
     <row r="226" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A226" s="10"/>
-      <c r="B226" s="11"/>
-      <c r="C226" s="11"/>
+      <c r="A226" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="B226" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C226" s="11">
+        <v>100.10406661033601</v>
+      </c>
       <c r="D226" s="11" t="s">
         <v>233</v>
       </c>
@@ -6946,9 +9035,15 @@
       </c>
     </row>
     <row r="227" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A227" s="7"/>
-      <c r="B227" s="8"/>
-      <c r="C227" s="8"/>
+      <c r="A227" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="B227" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C227" s="8">
+        <v>100.10658073425201</v>
+      </c>
       <c r="D227" s="8" t="s">
         <v>234</v>
       </c>
@@ -6969,9 +9064,15 @@
       </c>
     </row>
     <row r="228" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A228" s="10"/>
-      <c r="B228" s="11"/>
-      <c r="C228" s="11"/>
+      <c r="A228" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="B228" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C228" s="11">
+        <v>100.041407585144</v>
+      </c>
       <c r="D228" s="11" t="s">
         <v>235</v>
       </c>
@@ -6992,9 +9093,15 @@
       </c>
     </row>
     <row r="229" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A229" s="7"/>
-      <c r="B229" s="8"/>
-      <c r="C229" s="8"/>
+      <c r="A229" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="B229" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C229" s="8">
+        <v>3.02444076538085</v>
+      </c>
       <c r="D229" s="8" t="s">
         <v>236</v>
       </c>
@@ -7015,9 +9122,15 @@
       </c>
     </row>
     <row r="230" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A230" s="10"/>
-      <c r="B230" s="11"/>
-      <c r="C230" s="11"/>
+      <c r="A230" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="B230" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C230" s="11">
+        <v>100.104114770889</v>
+      </c>
       <c r="D230" s="11" t="s">
         <v>237</v>
       </c>
@@ -7038,9 +9151,15 @@
       </c>
     </row>
     <row r="231" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A231" s="7"/>
-      <c r="B231" s="8"/>
-      <c r="C231" s="8"/>
+      <c r="A231" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="B231" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C231" s="8">
+        <v>5.95265769958496</v>
+      </c>
       <c r="D231" s="8" t="s">
         <v>238</v>
       </c>
@@ -7061,9 +9180,15 @@
       </c>
     </row>
     <row r="232" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A232" s="10"/>
-      <c r="B232" s="11"/>
-      <c r="C232" s="11"/>
+      <c r="A232" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="B232" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C232" s="11">
+        <v>100.10374546051</v>
+      </c>
       <c r="D232" s="11" t="s">
         <v>239</v>
       </c>
@@ -7084,9 +9209,15 @@
       </c>
     </row>
     <row r="233" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A233" s="7"/>
-      <c r="B233" s="8"/>
-      <c r="C233" s="8"/>
+      <c r="A233" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="B233" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C233" s="8">
+        <v>100.10406088828999</v>
+      </c>
       <c r="D233" s="8" t="s">
         <v>240</v>
       </c>
@@ -7107,9 +9238,15 @@
       </c>
     </row>
     <row r="234" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A234" s="10"/>
-      <c r="B234" s="11"/>
-      <c r="C234" s="11"/>
+      <c r="A234" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="B234" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C234" s="11">
+        <v>100.1045088768</v>
+      </c>
       <c r="D234" s="11" t="s">
         <v>241</v>
       </c>
@@ -7130,9 +9267,15 @@
       </c>
     </row>
     <row r="235" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A235" s="7"/>
-      <c r="B235" s="8"/>
-      <c r="C235" s="8"/>
+      <c r="A235" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="B235" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C235" s="8">
+        <v>5.1349015235900799</v>
+      </c>
       <c r="D235" s="8" t="s">
         <v>242</v>
       </c>
@@ -7153,9 +9296,15 @@
       </c>
     </row>
     <row r="236" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A236" s="10"/>
-      <c r="B236" s="11"/>
-      <c r="C236" s="11"/>
+      <c r="A236" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="B236" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C236" s="11">
+        <v>100.103924036026</v>
+      </c>
       <c r="D236" s="11" t="s">
         <v>243</v>
       </c>
@@ -7176,9 +9325,15 @@
       </c>
     </row>
     <row r="237" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A237" s="7"/>
-      <c r="B237" s="8"/>
-      <c r="C237" s="8"/>
+      <c r="A237" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="B237" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C237" s="8">
+        <v>100.104396343231</v>
+      </c>
       <c r="D237" s="8" t="s">
         <v>244</v>
       </c>
@@ -7199,9 +9354,15 @@
       </c>
     </row>
     <row r="238" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A238" s="10"/>
-      <c r="B238" s="11"/>
-      <c r="C238" s="11"/>
+      <c r="A238" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="B238" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="C238" s="11">
+        <v>100.10398316383301</v>
+      </c>
       <c r="D238" s="11" t="s">
         <v>245</v>
       </c>
@@ -7222,9 +9383,15 @@
       </c>
     </row>
     <row r="239" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A239" s="7"/>
-      <c r="B239" s="8"/>
-      <c r="C239" s="8"/>
+      <c r="A239" s="7" t="s">
+        <v>489</v>
+      </c>
+      <c r="B239" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C239" s="8">
+        <v>100.104214668273</v>
+      </c>
       <c r="D239" s="8" t="s">
         <v>246</v>
       </c>
@@ -7245,9 +9412,15 @@
       </c>
     </row>
     <row r="240" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A240" s="1"/>
-      <c r="B240" s="2"/>
-      <c r="C240" s="2"/>
+      <c r="A240" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C240" s="2">
+        <v>6.4669952392578098</v>
+      </c>
       <c r="D240" s="2" t="s">
         <v>247</v>
       </c>
@@ -7267,7 +9440,16 @@
         <v>0.115933895111083</v>
       </c>
     </row>
-    <row r="241" spans="4:9" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A241" t="s">
+        <v>491</v>
+      </c>
+      <c r="B241" t="s">
+        <v>173</v>
+      </c>
+      <c r="C241">
+        <v>100.104124069213</v>
+      </c>
       <c r="D241" t="s">
         <v>248</v>
       </c>
@@ -7289,5 +9471,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/comparison_bapa.xlsx
+++ b/comparison_bapa.xlsx
@@ -8,19 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mudathir\all\sls-reachability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{378CF71F-99BD-425B-8CB2-5CA82FA7CEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D91AEEA-E528-4CF4-9497-BBDC8F7CF243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{43139118-C9B1-4C53-BA07-4D51B812E9BD}"/>
   </bookViews>
   <sheets>
-    <sheet name="comparison_bapa" sheetId="1" r:id="rId1"/>
+    <sheet name="pivot table" sheetId="2" r:id="rId1"/>
+    <sheet name="comparison_bapa" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId3"/>
+  </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="497">
   <si>
     <t>sls file</t>
   </si>
@@ -1496,6 +1500,21 @@
   </si>
   <si>
     <t>bapa/card/fol_0000120.smt2</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>Count of sls duration</t>
+  </si>
+  <si>
+    <t>sls</t>
+  </si>
+  <si>
+    <t>cvc5 lia</t>
+  </si>
+  <si>
+    <t>cvc5 lia normaliz</t>
   </si>
 </sst>
 </file>
@@ -2059,7 +2078,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -2073,6 +2092,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2129,6 +2153,2866 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Mudathir Mahgoub" refreshedDate="46114.463886805555" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="240" xr:uid="{83E52B08-862F-4C7F-9D9D-28C890578037}">
+  <cacheSource type="worksheet">
+    <worksheetSource name="Table1"/>
+  </cacheSource>
+  <cacheFields count="9">
+    <cacheField name="sls file" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="sls result" numFmtId="0">
+      <sharedItems count="3">
+        <s v="sat"/>
+        <s v="unsat"/>
+        <s v="timeout"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="sls duration" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0.152176618576049" maxValue="101.55069398880001"/>
+    </cacheField>
+    <cacheField name="cvc5 lia filename" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="cvc5 lia result" numFmtId="0">
+      <sharedItems count="3">
+        <s v="sat"/>
+        <s v="unsat"/>
+        <s v="timeout"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="cvc5 lia duration" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="9.0281963348388602E-3" maxValue="103.92190527915901"/>
+    </cacheField>
+    <cacheField name="lia normaliz filename" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="lia normaliz result" numFmtId="0">
+      <sharedItems count="3">
+        <s v="sat"/>
+        <s v="unsat"/>
+        <s v="timeout"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="lia normaliz duration" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7.9343318939208898E-3" maxValue="100.057497739791"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="240">
+  <r>
+    <s v="bapa/arith/fol_0000001.smt2"/>
+    <x v="0"/>
+    <n v="0.99435853958129805"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000001.smt2"/>
+    <x v="0"/>
+    <n v="1.3242959976196201E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000001.smt2"/>
+    <x v="0"/>
+    <n v="0.101495265960693"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000002.smt2"/>
+    <x v="0"/>
+    <n v="0.76033210754394498"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000002.smt2"/>
+    <x v="0"/>
+    <n v="1.3138532638549799E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000002.smt2"/>
+    <x v="0"/>
+    <n v="1.44908428192138E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000003.smt2"/>
+    <x v="0"/>
+    <n v="0.63649606704711903"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000003.smt2"/>
+    <x v="0"/>
+    <n v="1.40173435211181E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000003.smt2"/>
+    <x v="0"/>
+    <n v="2.0340681076049801E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000004.smt2"/>
+    <x v="0"/>
+    <n v="0.80373120307922297"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000004.smt2"/>
+    <x v="0"/>
+    <n v="6.3341617584228502E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000004.smt2"/>
+    <x v="0"/>
+    <n v="8.1681728363037095E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000005.smt2"/>
+    <x v="0"/>
+    <n v="0.63803029060363703"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000005.smt2"/>
+    <x v="0"/>
+    <n v="7.8626632690429604E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000005.smt2"/>
+    <x v="0"/>
+    <n v="4.7867774963378899E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000006.smt2"/>
+    <x v="0"/>
+    <n v="0.568917036056518"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000006.smt2"/>
+    <x v="0"/>
+    <n v="6.6159963607788003E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000006.smt2"/>
+    <x v="0"/>
+    <n v="5.0418615341186503E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000007.smt2"/>
+    <x v="0"/>
+    <n v="0.79503488540649403"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000007.smt2"/>
+    <x v="0"/>
+    <n v="5.9335947036743102E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000007.smt2"/>
+    <x v="0"/>
+    <n v="4.5779228210449198E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000008.smt2"/>
+    <x v="0"/>
+    <n v="0.63126659393310502"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000008.smt2"/>
+    <x v="0"/>
+    <n v="6.2076091766357401E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000008.smt2"/>
+    <x v="0"/>
+    <n v="4.58817481994628E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000009.smt2"/>
+    <x v="0"/>
+    <n v="0.79279041290283203"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000009.smt2"/>
+    <x v="0"/>
+    <n v="5.9259891510009703E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000009.smt2"/>
+    <x v="0"/>
+    <n v="4.4304609298705999E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000010.smt2"/>
+    <x v="0"/>
+    <n v="0.64874768257141102"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000010.smt2"/>
+    <x v="0"/>
+    <n v="5.7984352111816399E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000010.smt2"/>
+    <x v="0"/>
+    <n v="4.4718265533447203E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000011.smt2"/>
+    <x v="0"/>
+    <n v="0.65620541572570801"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000011.smt2"/>
+    <x v="0"/>
+    <n v="5.8189392089843701E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000011.smt2"/>
+    <x v="0"/>
+    <n v="4.4330596923828097E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000012.smt2"/>
+    <x v="0"/>
+    <n v="0.67011260986328103"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000012.smt2"/>
+    <x v="0"/>
+    <n v="5.8893680572509703E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000012.smt2"/>
+    <x v="0"/>
+    <n v="4.4733524322509703E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000013.smt2"/>
+    <x v="0"/>
+    <n v="0.61955571174621504"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000013.smt2"/>
+    <x v="0"/>
+    <n v="5.8380126953125E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000013.smt2"/>
+    <x v="0"/>
+    <n v="4.4816970825195299E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000014.smt2"/>
+    <x v="0"/>
+    <n v="0.167417287826538"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000014.smt2"/>
+    <x v="0"/>
+    <n v="5.8025836944580002E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000014.smt2"/>
+    <x v="0"/>
+    <n v="4.4156074523925698E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000015.smt2"/>
+    <x v="0"/>
+    <n v="1.01652908325195"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000015.smt2"/>
+    <x v="0"/>
+    <n v="5.8545112609863198E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000015.smt2"/>
+    <x v="0"/>
+    <n v="4.3086290359497001E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000016.smt2"/>
+    <x v="0"/>
+    <n v="0.84496617317199696"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000016.smt2"/>
+    <x v="0"/>
+    <n v="5.7845830917358398E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000016.smt2"/>
+    <x v="0"/>
+    <n v="4.6988010406494099E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000017.smt2"/>
+    <x v="0"/>
+    <n v="0.53039336204528797"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000017.smt2"/>
+    <x v="0"/>
+    <n v="5.9258222579955999E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000017.smt2"/>
+    <x v="0"/>
+    <n v="4.3082714080810498E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000018.smt2"/>
+    <x v="0"/>
+    <n v="0.93049621582031194"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000018.smt2"/>
+    <x v="0"/>
+    <n v="6.0906648635864202E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000018.smt2"/>
+    <x v="0"/>
+    <n v="4.4025659561157199E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000019.smt2"/>
+    <x v="0"/>
+    <n v="0.74736404418945301"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000019.smt2"/>
+    <x v="0"/>
+    <n v="6.7611217498779297E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000019.smt2"/>
+    <x v="0"/>
+    <n v="4.9208641052245997E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000020.smt2"/>
+    <x v="0"/>
+    <n v="0.171578884124755"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000020.smt2"/>
+    <x v="0"/>
+    <n v="7.1949005126953097E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000020.smt2"/>
+    <x v="0"/>
+    <n v="4.9638271331787102E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000021.smt2"/>
+    <x v="1"/>
+    <n v="0.16096591949462799"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000021.smt2"/>
+    <x v="1"/>
+    <n v="1.3502120971679601E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000021.smt2"/>
+    <x v="1"/>
+    <n v="1.1879682540893499E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000022.smt2"/>
+    <x v="0"/>
+    <n v="0.40941166877746499"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000022.smt2"/>
+    <x v="0"/>
+    <n v="6.5932512283325195E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000022.smt2"/>
+    <x v="0"/>
+    <n v="4.5344114303588798E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000023.smt2"/>
+    <x v="1"/>
+    <n v="0.16520500183105399"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000023.smt2"/>
+    <x v="1"/>
+    <n v="1.06856822967529E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000023.smt2"/>
+    <x v="1"/>
+    <n v="1.0849714279174799E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000024.smt2"/>
+    <x v="0"/>
+    <n v="0.65459823608398404"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000024.smt2"/>
+    <x v="0"/>
+    <n v="6.5405845642089802E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000024.smt2"/>
+    <x v="0"/>
+    <n v="4.9724578857421799E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000025.smt2"/>
+    <x v="0"/>
+    <n v="0.162420749664306"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000025.smt2"/>
+    <x v="0"/>
+    <n v="1.18811130523681E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000025.smt2"/>
+    <x v="0"/>
+    <n v="1.3100862503051701E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000026.smt2"/>
+    <x v="0"/>
+    <n v="0.37980604171752902"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000026.smt2"/>
+    <x v="0"/>
+    <n v="1.3247728347778299E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000026.smt2"/>
+    <x v="0"/>
+    <n v="1.2727499008178701E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000027.smt2"/>
+    <x v="0"/>
+    <n v="0.163376569747924"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000027.smt2"/>
+    <x v="0"/>
+    <n v="1.41315460205078E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000027.smt2"/>
+    <x v="0"/>
+    <n v="1.29928588867187E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000028.smt2"/>
+    <x v="1"/>
+    <n v="0.47155237197875899"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000028.smt2"/>
+    <x v="1"/>
+    <n v="0.119706630706787"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000028.smt2"/>
+    <x v="2"/>
+    <n v="6.2685966491699205E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000029.smt2"/>
+    <x v="0"/>
+    <n v="0.53534078598022405"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000029.smt2"/>
+    <x v="0"/>
+    <n v="0.117452144622802"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000029.smt2"/>
+    <x v="2"/>
+    <n v="0.122227668762207"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000030.smt2"/>
+    <x v="1"/>
+    <n v="0.16627836227416901"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000030.smt2"/>
+    <x v="1"/>
+    <n v="9.6716880798339792E-3"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000030.smt2"/>
+    <x v="1"/>
+    <n v="1.16009712219238E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000031.smt2"/>
+    <x v="0"/>
+    <n v="0.62550663948059004"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000031.smt2"/>
+    <x v="0"/>
+    <n v="6.1882734298705999E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000031.smt2"/>
+    <x v="0"/>
+    <n v="4.8797607421875E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000032.smt2"/>
+    <x v="1"/>
+    <n v="0.16071510314941401"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000032.smt2"/>
+    <x v="1"/>
+    <n v="1.04312896728515E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000032.smt2"/>
+    <x v="1"/>
+    <n v="9.9892616271972604E-3"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000033.smt2"/>
+    <x v="0"/>
+    <n v="0.686598300933837"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000033.smt2"/>
+    <x v="0"/>
+    <n v="6.0556411743164E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000033.smt2"/>
+    <x v="0"/>
+    <n v="4.4088840484619099E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000034.smt2"/>
+    <x v="1"/>
+    <n v="0.15680384635925201"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000034.smt2"/>
+    <x v="1"/>
+    <n v="1.03905200958251E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000034.smt2"/>
+    <x v="1"/>
+    <n v="9.7904205322265608E-3"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000035.smt2"/>
+    <x v="0"/>
+    <n v="0.71952629089355402"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000035.smt2"/>
+    <x v="0"/>
+    <n v="6.3884258270263602E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000035.smt2"/>
+    <x v="0"/>
+    <n v="4.8144340515136698E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000036.smt2"/>
+    <x v="0"/>
+    <n v="0.76075839996337802"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000036.smt2"/>
+    <x v="0"/>
+    <n v="1.15578174591064E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000036.smt2"/>
+    <x v="0"/>
+    <n v="1.2047529220580999E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000037.smt2"/>
+    <x v="0"/>
+    <n v="0.61400890350341797"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000037.smt2"/>
+    <x v="0"/>
+    <n v="6.2669038772582994E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000037.smt2"/>
+    <x v="0"/>
+    <n v="4.31671142578125E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000038.smt2"/>
+    <x v="1"/>
+    <n v="0.15881991386413499"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000038.smt2"/>
+    <x v="1"/>
+    <n v="1.04796886444091E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000038.smt2"/>
+    <x v="1"/>
+    <n v="9.9687576293945295E-3"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000039.smt2"/>
+    <x v="0"/>
+    <n v="0.55142021179199197"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000039.smt2"/>
+    <x v="0"/>
+    <n v="6.2346696853637598E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000039.smt2"/>
+    <x v="0"/>
+    <n v="4.4043779373168897E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000040.smt2"/>
+    <x v="1"/>
+    <n v="0.159366369247436"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000040.smt2"/>
+    <x v="1"/>
+    <n v="1.0697841644287101E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000040.smt2"/>
+    <x v="1"/>
+    <n v="9.9987983703613195E-3"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000041.smt2"/>
+    <x v="0"/>
+    <n v="0.79223847389221103"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000041.smt2"/>
+    <x v="0"/>
+    <n v="6.2450408935546799E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000041.smt2"/>
+    <x v="0"/>
+    <n v="4.6099662780761698E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000042.smt2"/>
+    <x v="0"/>
+    <n v="0.211480617523193"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000042.smt2"/>
+    <x v="0"/>
+    <n v="1.18279457092285E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000042.smt2"/>
+    <x v="0"/>
+    <n v="1.2178897857666E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000043.smt2"/>
+    <x v="0"/>
+    <n v="0.16698408126830999"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000043.smt2"/>
+    <x v="0"/>
+    <n v="0.119373083114624"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000043.smt2"/>
+    <x v="2"/>
+    <n v="4.4809579849243102E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000044.smt2"/>
+    <x v="0"/>
+    <n v="0.618000268936157"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000044.smt2"/>
+    <x v="0"/>
+    <n v="5.8284521102905197E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000044.smt2"/>
+    <x v="0"/>
+    <n v="4.4211626052856397E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000045.smt2"/>
+    <x v="1"/>
+    <n v="0.22474837303161599"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000045.smt2"/>
+    <x v="1"/>
+    <n v="0.113115072250366"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000045.smt2"/>
+    <x v="2"/>
+    <n v="4.9978256225585903E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000046.smt2"/>
+    <x v="0"/>
+    <n v="0.17848396301269501"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000046.smt2"/>
+    <x v="0"/>
+    <n v="0.121005296707153"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000046.smt2"/>
+    <x v="2"/>
+    <n v="4.6791315078735303E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000047.smt2"/>
+    <x v="1"/>
+    <n v="0.219141244888305"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000047.smt2"/>
+    <x v="1"/>
+    <n v="0.115952968597412"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000047.smt2"/>
+    <x v="2"/>
+    <n v="9.0545415878295898E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000048.smt2"/>
+    <x v="0"/>
+    <n v="0.42846250534057601"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000048.smt2"/>
+    <x v="0"/>
+    <n v="0.13345503807067799"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000048.smt2"/>
+    <x v="2"/>
+    <n v="4.6838283538818297E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000049.smt2"/>
+    <x v="0"/>
+    <n v="0.52458643913268999"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000049.smt2"/>
+    <x v="0"/>
+    <n v="0.15679931640625"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000049.smt2"/>
+    <x v="2"/>
+    <n v="5.4154872894287102E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000050.smt2"/>
+    <x v="0"/>
+    <n v="1.5994741916656401"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000050.smt2"/>
+    <x v="0"/>
+    <n v="1.8458127975463801E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000050.smt2"/>
+    <x v="0"/>
+    <n v="1.9216775894165001E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000051.smt2"/>
+    <x v="0"/>
+    <n v="0.57938766479492099"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000051.smt2"/>
+    <x v="0"/>
+    <n v="0.119428157806396"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000051.smt2"/>
+    <x v="2"/>
+    <n v="5.2750825881958001E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000052.smt2"/>
+    <x v="0"/>
+    <n v="0.54706501960754395"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000052.smt2"/>
+    <x v="0"/>
+    <n v="0.13226437568664501"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000052.smt2"/>
+    <x v="2"/>
+    <n v="0.161716699600219"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000053.smt2"/>
+    <x v="0"/>
+    <n v="0.43974351882934498"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000053.smt2"/>
+    <x v="0"/>
+    <n v="0.12703251838683999"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000053.smt2"/>
+    <x v="2"/>
+    <n v="5.3837537765502902E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000054.smt2"/>
+    <x v="0"/>
+    <n v="0.18849515914916901"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000054.smt2"/>
+    <x v="0"/>
+    <n v="0.13518643379211401"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000054.smt2"/>
+    <x v="2"/>
+    <n v="6.1524391174316399E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000055.smt2"/>
+    <x v="1"/>
+    <n v="0.17217445373535101"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000055.smt2"/>
+    <x v="1"/>
+    <n v="1.07979774475097E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000055.smt2"/>
+    <x v="1"/>
+    <n v="1.1770963668823201E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000056.smt2"/>
+    <x v="0"/>
+    <n v="0.72484612464904696"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000056.smt2"/>
+    <x v="0"/>
+    <n v="6.3684225082397405E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000056.smt2"/>
+    <x v="0"/>
+    <n v="4.50634956359863E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000057.smt2"/>
+    <x v="0"/>
+    <n v="0.39650130271911599"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000057.smt2"/>
+    <x v="0"/>
+    <n v="0.116705894470214"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000057.smt2"/>
+    <x v="2"/>
+    <n v="4.7250747680664E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000058.smt2"/>
+    <x v="1"/>
+    <n v="0.47390007972717202"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000058.smt2"/>
+    <x v="1"/>
+    <n v="0.114969491958618"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000058.smt2"/>
+    <x v="2"/>
+    <n v="5.5867433547973598E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000059.smt2"/>
+    <x v="1"/>
+    <n v="0.15601181983947701"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000059.smt2"/>
+    <x v="1"/>
+    <n v="1.04565620422363E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000059.smt2"/>
+    <x v="1"/>
+    <n v="9.9360942840576102E-3"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000060.smt2"/>
+    <x v="1"/>
+    <n v="0.234406948089599"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000060.smt2"/>
+    <x v="1"/>
+    <n v="0.11656832695007301"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000060.smt2"/>
+    <x v="2"/>
+    <n v="5.0779104232788003E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000061.smt2"/>
+    <x v="1"/>
+    <n v="0.47082734107971103"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000061.smt2"/>
+    <x v="1"/>
+    <n v="0.11485242843627901"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000061.smt2"/>
+    <x v="2"/>
+    <n v="4.8722743988037102E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000062.smt2"/>
+    <x v="0"/>
+    <n v="0.42225170135498002"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000062.smt2"/>
+    <x v="0"/>
+    <n v="0.127403974533081"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000062.smt2"/>
+    <x v="2"/>
+    <n v="4.6223640441894497E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000063.smt2"/>
+    <x v="1"/>
+    <n v="0.233814477920532"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000063.smt2"/>
+    <x v="1"/>
+    <n v="0.113116979598999"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000063.smt2"/>
+    <x v="2"/>
+    <n v="4.4949531555175698E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000064.smt2"/>
+    <x v="1"/>
+    <n v="0.152176618576049"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000064.smt2"/>
+    <x v="1"/>
+    <n v="1.2086153030395499E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000064.smt2"/>
+    <x v="1"/>
+    <n v="1.0486602783203101E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000065.smt2"/>
+    <x v="1"/>
+    <n v="0.48354673385620101"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000065.smt2"/>
+    <x v="1"/>
+    <n v="0.115830898284912"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000065.smt2"/>
+    <x v="2"/>
+    <n v="4.6811819076538003E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000066.smt2"/>
+    <x v="1"/>
+    <n v="0.59694933891296298"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000066.smt2"/>
+    <x v="1"/>
+    <n v="0.116195917129516"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000066.smt2"/>
+    <x v="2"/>
+    <n v="4.4660806655883699E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000067.smt2"/>
+    <x v="1"/>
+    <n v="0.60850429534912098"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000067.smt2"/>
+    <x v="1"/>
+    <n v="0.114636182785034"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000067.smt2"/>
+    <x v="2"/>
+    <n v="0.122978687286376"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000068.smt2"/>
+    <x v="1"/>
+    <n v="0.22384619712829501"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000068.smt2"/>
+    <x v="1"/>
+    <n v="0.114525318145751"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000068.smt2"/>
+    <x v="2"/>
+    <n v="7.0685386657714802E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000069.smt2"/>
+    <x v="0"/>
+    <n v="0.55266261100768999"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000069.smt2"/>
+    <x v="0"/>
+    <n v="0.11901354789733801"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000069.smt2"/>
+    <x v="2"/>
+    <n v="4.7506093978881801E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000070.smt2"/>
+    <x v="1"/>
+    <n v="0.22388839721679599"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000070.smt2"/>
+    <x v="1"/>
+    <n v="0.115196943283081"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000070.smt2"/>
+    <x v="2"/>
+    <n v="5.5344104766845703E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000071.smt2"/>
+    <x v="0"/>
+    <n v="0.51312685012817305"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000071.smt2"/>
+    <x v="0"/>
+    <n v="0.120176553726196"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000071.smt2"/>
+    <x v="2"/>
+    <n v="5.0118207931518499E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000072.smt2"/>
+    <x v="0"/>
+    <n v="0.19146013259887601"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000072.smt2"/>
+    <x v="0"/>
+    <n v="0.119714260101318"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000072.smt2"/>
+    <x v="2"/>
+    <n v="5.0841093063354402E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000073.smt2"/>
+    <x v="0"/>
+    <n v="0.58962893486022905"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000073.smt2"/>
+    <x v="0"/>
+    <n v="1.7429113388061499E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000073.smt2"/>
+    <x v="0"/>
+    <n v="1.72088146209716E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000074.smt2"/>
+    <x v="0"/>
+    <n v="0.42420721054077098"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000074.smt2"/>
+    <x v="0"/>
+    <n v="0.12500524520874001"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000074.smt2"/>
+    <x v="2"/>
+    <n v="4.8106908798217697E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000075.smt2"/>
+    <x v="0"/>
+    <n v="0.56092762947082497"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000075.smt2"/>
+    <x v="0"/>
+    <n v="0.122902154922485"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000075.smt2"/>
+    <x v="2"/>
+    <n v="4.7061443328857401E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000076.smt2"/>
+    <x v="0"/>
+    <n v="0.18892359733581501"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000076.smt2"/>
+    <x v="0"/>
+    <n v="0.123332738876342"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000076.smt2"/>
+    <x v="2"/>
+    <n v="0.14733719825744601"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000077.smt2"/>
+    <x v="0"/>
+    <n v="0.52262091636657704"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000077.smt2"/>
+    <x v="0"/>
+    <n v="0.13582348823547299"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000077.smt2"/>
+    <x v="2"/>
+    <n v="5.1762580871581997E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000078.smt2"/>
+    <x v="1"/>
+    <n v="0.17058753967285101"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000078.smt2"/>
+    <x v="1"/>
+    <n v="1.4173269271850499E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000078.smt2"/>
+    <x v="1"/>
+    <n v="1.2853860855102499E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000079.smt2"/>
+    <x v="0"/>
+    <n v="0.89729022979736295"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000079.smt2"/>
+    <x v="0"/>
+    <n v="7.1373939514160101E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000079.smt2"/>
+    <x v="0"/>
+    <n v="5.3411960601806599E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000080.smt2"/>
+    <x v="0"/>
+    <n v="0.17688155174255299"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000080.smt2"/>
+    <x v="0"/>
+    <n v="6.1158657073974602E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000080.smt2"/>
+    <x v="0"/>
+    <n v="4.4915676116943297E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000081.smt2"/>
+    <x v="1"/>
+    <n v="0.15490198135375899"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000081.smt2"/>
+    <x v="1"/>
+    <n v="1.03394985198974E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000081.smt2"/>
+    <x v="1"/>
+    <n v="9.6285343170165998E-3"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000082.smt2"/>
+    <x v="0"/>
+    <n v="0.66412115097045898"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000082.smt2"/>
+    <x v="0"/>
+    <n v="6.1781644821166902E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000082.smt2"/>
+    <x v="0"/>
+    <n v="4.5893430709838798E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000083.smt2"/>
+    <x v="1"/>
+    <n v="0.16417956352233801"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000083.smt2"/>
+    <x v="1"/>
+    <n v="1.054048538208E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000083.smt2"/>
+    <x v="1"/>
+    <n v="1.0493993759155201E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000084.smt2"/>
+    <x v="0"/>
+    <n v="0.17815995216369601"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000084.smt2"/>
+    <x v="0"/>
+    <n v="0.1182541847229"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000084.smt2"/>
+    <x v="2"/>
+    <n v="4.95438575744628E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000085.smt2"/>
+    <x v="1"/>
+    <n v="0.47321844100952098"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000085.smt2"/>
+    <x v="1"/>
+    <n v="0.117470741271972"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000085.smt2"/>
+    <x v="2"/>
+    <n v="4.7630786895751898E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000086.smt2"/>
+    <x v="1"/>
+    <n v="0.20443201065063399"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000086.smt2"/>
+    <x v="1"/>
+    <n v="0.11285448074340799"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000086.smt2"/>
+    <x v="2"/>
+    <n v="4.96673583984375E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000087.smt2"/>
+    <x v="1"/>
+    <n v="0.16650128364562899"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000087.smt2"/>
+    <x v="1"/>
+    <n v="1.03604793548583E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000087.smt2"/>
+    <x v="1"/>
+    <n v="1.1652946472167899E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000088.smt2"/>
+    <x v="1"/>
+    <n v="0.46969437599182101"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000088.smt2"/>
+    <x v="1"/>
+    <n v="0.11802053451538"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000088.smt2"/>
+    <x v="2"/>
+    <n v="5.0182104110717697E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000089.smt2"/>
+    <x v="1"/>
+    <n v="0.60850167274475098"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000089.smt2"/>
+    <x v="1"/>
+    <n v="0.115944623947143"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000089.smt2"/>
+    <x v="2"/>
+    <n v="5.2581310272216797E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000090.smt2"/>
+    <x v="0"/>
+    <n v="0.69072961807250899"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000090.smt2"/>
+    <x v="0"/>
+    <n v="5.9777259826660101E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000090.smt2"/>
+    <x v="0"/>
+    <n v="4.3616771697997998E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000091.smt2"/>
+    <x v="1"/>
+    <n v="0.16004705429077101"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000091.smt2"/>
+    <x v="1"/>
+    <n v="1.01652145385742E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000091.smt2"/>
+    <x v="1"/>
+    <n v="9.5777511596679601E-3"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000092.smt2"/>
+    <x v="1"/>
+    <n v="0.166557312011718"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000092.smt2"/>
+    <x v="1"/>
+    <n v="1.2187719345092701E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000092.smt2"/>
+    <x v="1"/>
+    <n v="1.09376907348632E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000093.smt2"/>
+    <x v="1"/>
+    <n v="0.17809796333312899"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000093.smt2"/>
+    <x v="1"/>
+    <n v="1.1828899383544899E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000093.smt2"/>
+    <x v="1"/>
+    <n v="1.01594924926757E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000094.smt2"/>
+    <x v="1"/>
+    <n v="0.22989678382873499"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000094.smt2"/>
+    <x v="1"/>
+    <n v="0.116023302078247"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000094.smt2"/>
+    <x v="2"/>
+    <n v="4.7819852828979402E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000095.smt2"/>
+    <x v="1"/>
+    <n v="0.59611082077026301"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000095.smt2"/>
+    <x v="1"/>
+    <n v="0.11651730537414499"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000095.smt2"/>
+    <x v="2"/>
+    <n v="4.8085451126098598E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000096.smt2"/>
+    <x v="0"/>
+    <n v="0.41368675231933499"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000096.smt2"/>
+    <x v="0"/>
+    <n v="0.118608951568603"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000096.smt2"/>
+    <x v="2"/>
+    <n v="4.7187328338622998E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000097.smt2"/>
+    <x v="1"/>
+    <n v="0.468215942382812"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000097.smt2"/>
+    <x v="1"/>
+    <n v="0.115262508392333"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000097.smt2"/>
+    <x v="2"/>
+    <n v="4.77674007415771E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000098.smt2"/>
+    <x v="1"/>
+    <n v="0.47069001197814903"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000098.smt2"/>
+    <x v="1"/>
+    <n v="0.118569374084472"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000098.smt2"/>
+    <x v="2"/>
+    <n v="4.6757459640502902E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000099.smt2"/>
+    <x v="0"/>
+    <n v="0.45036292076110801"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000099.smt2"/>
+    <x v="0"/>
+    <n v="0.121697187423706"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000099.smt2"/>
+    <x v="2"/>
+    <n v="4.6641349792480399E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000100.smt2"/>
+    <x v="0"/>
+    <n v="0.45693588256835899"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000100.smt2"/>
+    <x v="0"/>
+    <n v="0.124733209609985"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000100.smt2"/>
+    <x v="2"/>
+    <n v="4.5722961425781201E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000101.smt2"/>
+    <x v="0"/>
+    <n v="1.283203125"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000101.smt2"/>
+    <x v="0"/>
+    <n v="1.7717361450195299E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000101.smt2"/>
+    <x v="0"/>
+    <n v="1.7483234405517498E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000102.smt2"/>
+    <x v="0"/>
+    <n v="0.593713998794555"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000102.smt2"/>
+    <x v="0"/>
+    <n v="0.12615013122558499"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000102.smt2"/>
+    <x v="2"/>
+    <n v="5.6472063064575098E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000103.smt2"/>
+    <x v="0"/>
+    <n v="0.57118177413940396"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000103.smt2"/>
+    <x v="0"/>
+    <n v="0.119795799255371"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000103.smt2"/>
+    <x v="2"/>
+    <n v="8.8441848754882799E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000104.smt2"/>
+    <x v="0"/>
+    <n v="0.20302200317382799"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000104.smt2"/>
+    <x v="0"/>
+    <n v="0.120328664779663"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000104.smt2"/>
+    <x v="2"/>
+    <n v="8.3253383636474595E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000105.smt2"/>
+    <x v="0"/>
+    <n v="0.1976318359375"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000105.smt2"/>
+    <x v="0"/>
+    <n v="0.124726772308349"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000105.smt2"/>
+    <x v="2"/>
+    <n v="0.130986928939819"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000106.smt2"/>
+    <x v="0"/>
+    <n v="0.44295406341552701"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000106.smt2"/>
+    <x v="0"/>
+    <n v="0.12280392646789499"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000106.smt2"/>
+    <x v="2"/>
+    <n v="0.205983877182006"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000107.smt2"/>
+    <x v="1"/>
+    <n v="0.172296047210693"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000107.smt2"/>
+    <x v="1"/>
+    <n v="0.83991265296936002"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000107.smt2"/>
+    <x v="1"/>
+    <n v="1.12090110778808E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000108.smt2"/>
+    <x v="0"/>
+    <n v="0.98990082740783603"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000108.smt2"/>
+    <x v="0"/>
+    <n v="6.7646265029907199E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000108.smt2"/>
+    <x v="0"/>
+    <n v="5.10697364807128E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000109.smt2"/>
+    <x v="0"/>
+    <n v="0.423665761947631"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000109.smt2"/>
+    <x v="0"/>
+    <n v="0.119143724441528"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000109.smt2"/>
+    <x v="2"/>
+    <n v="4.6656370162963798E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000110.smt2"/>
+    <x v="1"/>
+    <n v="0.61156606674194303"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000110.smt2"/>
+    <x v="1"/>
+    <n v="0.118505239486694"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000110.smt2"/>
+    <x v="2"/>
+    <n v="4.4392347335815402E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000111.smt2"/>
+    <x v="1"/>
+    <n v="0.164831638336181"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000111.smt2"/>
+    <x v="1"/>
+    <n v="1.12555027008056E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000111.smt2"/>
+    <x v="1"/>
+    <n v="1.0449886322021399E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000112.smt2"/>
+    <x v="1"/>
+    <n v="0.23129153251647899"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000112.smt2"/>
+    <x v="1"/>
+    <n v="0.116581916809082"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000112.smt2"/>
+    <x v="2"/>
+    <n v="4.7589778900146401E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000113.smt2"/>
+    <x v="0"/>
+    <n v="0.72992944717407204"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000113.smt2"/>
+    <x v="0"/>
+    <n v="6.33366107940673E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000113.smt2"/>
+    <x v="0"/>
+    <n v="4.43463325500488E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000114.smt2"/>
+    <x v="1"/>
+    <n v="0.17205500602722101"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000114.smt2"/>
+    <x v="1"/>
+    <n v="1.15253925323486E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000114.smt2"/>
+    <x v="1"/>
+    <n v="1.0713100433349601E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000115.smt2"/>
+    <x v="1"/>
+    <n v="0.164976596832275"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000115.smt2"/>
+    <x v="1"/>
+    <n v="1.1500358581542899E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000115.smt2"/>
+    <x v="1"/>
+    <n v="1.0607957839965799E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000116.smt2"/>
+    <x v="1"/>
+    <n v="0.16637229919433499"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000116.smt2"/>
+    <x v="1"/>
+    <n v="1.17039680480957E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000116.smt2"/>
+    <x v="1"/>
+    <n v="1.08428001403808E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000117.smt2"/>
+    <x v="0"/>
+    <n v="0.67828106880187899"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000117.smt2"/>
+    <x v="0"/>
+    <n v="6.0166597366333001E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000117.smt2"/>
+    <x v="0"/>
+    <n v="4.5263528823852497E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000118.smt2"/>
+    <x v="0"/>
+    <n v="0.179522514343261"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000118.smt2"/>
+    <x v="0"/>
+    <n v="0.119395971298217"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000118.smt2"/>
+    <x v="2"/>
+    <n v="4.5195817947387598E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000119.smt2"/>
+    <x v="1"/>
+    <n v="0.58964467048644997"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000119.smt2"/>
+    <x v="1"/>
+    <n v="0.116992950439453"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000119.smt2"/>
+    <x v="2"/>
+    <n v="6.0981273651122998E-2"/>
+  </r>
+  <r>
+    <s v="bapa/arith/fol_0000120.smt2"/>
+    <x v="1"/>
+    <n v="0.16510510444641099"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000120.smt2"/>
+    <x v="1"/>
+    <n v="1.1287212371826101E-2"/>
+    <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000120.smt2"/>
+    <x v="1"/>
+    <n v="1.0813713073730399E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000001.smt2"/>
+    <x v="0"/>
+    <n v="0.837563276290893"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000001.smt2"/>
+    <x v="0"/>
+    <n v="1.34451389312744E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000001.smt2"/>
+    <x v="0"/>
+    <n v="1.2289762496948201E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000002.smt2"/>
+    <x v="0"/>
+    <n v="0.75990319252014105"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000002.smt2"/>
+    <x v="0"/>
+    <n v="1.3576030731201101E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000002.smt2"/>
+    <x v="0"/>
+    <n v="1.30712985992431E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000003.smt2"/>
+    <x v="0"/>
+    <n v="0.61714816093444802"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000003.smt2"/>
+    <x v="0"/>
+    <n v="1.2915134429931601E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000003.smt2"/>
+    <x v="0"/>
+    <n v="1.15993022918701E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000004.smt2"/>
+    <x v="0"/>
+    <n v="1.32692170143127"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000004.smt2"/>
+    <x v="0"/>
+    <n v="6.03528022766113E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000004.smt2"/>
+    <x v="0"/>
+    <n v="4.4612407684326102E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000005.smt2"/>
+    <x v="0"/>
+    <n v="0.66475510597229004"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000005.smt2"/>
+    <x v="0"/>
+    <n v="5.9652328491210903E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000005.smt2"/>
+    <x v="0"/>
+    <n v="4.2409181594848598E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000006.smt2"/>
+    <x v="0"/>
+    <n v="0.56747746467590299"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000006.smt2"/>
+    <x v="0"/>
+    <n v="6.0105085372924798E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000006.smt2"/>
+    <x v="0"/>
+    <n v="5.1395416259765597E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000007.smt2"/>
+    <x v="0"/>
+    <n v="0.821058750152587"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000007.smt2"/>
+    <x v="0"/>
+    <n v="5.8335542678833001E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000007.smt2"/>
+    <x v="0"/>
+    <n v="4.1522502899169901E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000008.smt2"/>
+    <x v="0"/>
+    <n v="0.65578770637512196"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000008.smt2"/>
+    <x v="0"/>
+    <n v="5.9497356414794901E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000008.smt2"/>
+    <x v="0"/>
+    <n v="4.2270660400390597E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000009.smt2"/>
+    <x v="0"/>
+    <n v="0.79100561141967696"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000009.smt2"/>
+    <x v="0"/>
+    <n v="5.7343482971191399E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000009.smt2"/>
+    <x v="0"/>
+    <n v="4.2980194091796799E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000010.smt2"/>
+    <x v="0"/>
+    <n v="0.667458295822143"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000010.smt2"/>
+    <x v="0"/>
+    <n v="6.3792228698730399E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000010.smt2"/>
+    <x v="0"/>
+    <n v="4.241943359375E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000011.smt2"/>
+    <x v="0"/>
+    <n v="0.67611932754516602"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000011.smt2"/>
+    <x v="0"/>
+    <n v="6.1859846115112298E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000011.smt2"/>
+    <x v="0"/>
+    <n v="4.29434776306152E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000012.smt2"/>
+    <x v="0"/>
+    <n v="0.670462846755981"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000012.smt2"/>
+    <x v="0"/>
+    <n v="6.04727268218994E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000012.smt2"/>
+    <x v="0"/>
+    <n v="4.2688608169555602E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000013.smt2"/>
+    <x v="0"/>
+    <n v="0.59122014045715299"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000013.smt2"/>
+    <x v="0"/>
+    <n v="6.0076475143432603E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000013.smt2"/>
+    <x v="0"/>
+    <n v="4.3863058090209898E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000014.smt2"/>
+    <x v="0"/>
+    <n v="0.16102409362792899"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000014.smt2"/>
+    <x v="0"/>
+    <n v="5.9150218963622998E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000014.smt2"/>
+    <x v="0"/>
+    <n v="4.3490171432495103E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000015.smt2"/>
+    <x v="0"/>
+    <n v="0.968511343002319"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000015.smt2"/>
+    <x v="0"/>
+    <n v="6.3306808471679604E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000015.smt2"/>
+    <x v="0"/>
+    <n v="4.2840003967285101E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000016.smt2"/>
+    <x v="0"/>
+    <n v="0.85265851020812899"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000016.smt2"/>
+    <x v="0"/>
+    <n v="5.8362960815429597E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000016.smt2"/>
+    <x v="0"/>
+    <n v="4.4537067413330002E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000017.smt2"/>
+    <x v="0"/>
+    <n v="0.52807974815368597"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000017.smt2"/>
+    <x v="0"/>
+    <n v="6.2740325927734306E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000017.smt2"/>
+    <x v="0"/>
+    <n v="4.21948432922363E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000018.smt2"/>
+    <x v="0"/>
+    <n v="0.93557095527648904"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000018.smt2"/>
+    <x v="0"/>
+    <n v="6.1152219772338798E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000018.smt2"/>
+    <x v="0"/>
+    <n v="4.2753458023071199E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000019.smt2"/>
+    <x v="0"/>
+    <n v="0.76749587059020996"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000019.smt2"/>
+    <x v="0"/>
+    <n v="6.3507795333862305E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000019.smt2"/>
+    <x v="0"/>
+    <n v="4.7303676605224602E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000020.smt2"/>
+    <x v="0"/>
+    <n v="0.17059302330017001"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000020.smt2"/>
+    <x v="0"/>
+    <n v="5.9348344802856397E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000020.smt2"/>
+    <x v="0"/>
+    <n v="4.15787696838378E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000021.smt2"/>
+    <x v="1"/>
+    <n v="0.16503524780273399"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000021.smt2"/>
+    <x v="1"/>
+    <n v="1.0775089263916E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000021.smt2"/>
+    <x v="1"/>
+    <n v="1.1081695556640601E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000022.smt2"/>
+    <x v="0"/>
+    <n v="0.40426158905029203"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000022.smt2"/>
+    <x v="0"/>
+    <n v="6.0818195343017502E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000022.smt2"/>
+    <x v="0"/>
+    <n v="4.22806739807128E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000023.smt2"/>
+    <x v="1"/>
+    <n v="0.16589260101318301"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000023.smt2"/>
+    <x v="1"/>
+    <n v="1.10418796539306E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000023.smt2"/>
+    <x v="1"/>
+    <n v="1.03745460510253E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000024.smt2"/>
+    <x v="0"/>
+    <n v="0.65723896026611295"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000024.smt2"/>
+    <x v="0"/>
+    <n v="6.5743923187255804E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000024.smt2"/>
+    <x v="0"/>
+    <n v="4.9272060394287102E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000025.smt2"/>
+    <x v="0"/>
+    <n v="0.16569018363952601"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000025.smt2"/>
+    <x v="0"/>
+    <n v="1.1778116226196201E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000025.smt2"/>
+    <x v="0"/>
+    <n v="1.22833251953125E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000026.smt2"/>
+    <x v="0"/>
+    <n v="0.38298416137695301"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000026.smt2"/>
+    <x v="0"/>
+    <n v="1.33535861968994E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000026.smt2"/>
+    <x v="0"/>
+    <n v="1.35400295257568E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000027.smt2"/>
+    <x v="0"/>
+    <n v="0.164352416992187"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000027.smt2"/>
+    <x v="0"/>
+    <n v="1.46529674530029E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000027.smt2"/>
+    <x v="0"/>
+    <n v="1.2335538864135701E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000028.smt2"/>
+    <x v="1"/>
+    <n v="0.48286223411559998"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000028.smt2"/>
+    <x v="1"/>
+    <n v="0.115192651748657"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000028.smt2"/>
+    <x v="2"/>
+    <n v="4.6390533447265597E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000029.smt2"/>
+    <x v="0"/>
+    <n v="0.53257179260253895"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000029.smt2"/>
+    <x v="0"/>
+    <n v="0.12024188041687001"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000029.smt2"/>
+    <x v="2"/>
+    <n v="4.5660257339477497E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000030.smt2"/>
+    <x v="1"/>
+    <n v="0.158925056457519"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000030.smt2"/>
+    <x v="1"/>
+    <n v="1.09891891479492E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000030.smt2"/>
+    <x v="1"/>
+    <n v="1.0617733001708899E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000031.smt2"/>
+    <x v="0"/>
+    <n v="0.63991928100585904"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000031.smt2"/>
+    <x v="0"/>
+    <n v="6.2046289443969699E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000031.smt2"/>
+    <x v="0"/>
+    <n v="4.3722391128539997E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000032.smt2"/>
+    <x v="1"/>
+    <n v="0.15931057929992601"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000032.smt2"/>
+    <x v="1"/>
+    <n v="1.1416912078857399E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000032.smt2"/>
+    <x v="1"/>
+    <n v="9.7038745880126901E-3"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000033.smt2"/>
+    <x v="0"/>
+    <n v="0.68768620491027799"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000033.smt2"/>
+    <x v="0"/>
+    <n v="6.1464071273803697E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000033.smt2"/>
+    <x v="0"/>
+    <n v="4.3673753738403299E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000034.smt2"/>
+    <x v="1"/>
+    <n v="0.16060185432433999"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000034.smt2"/>
+    <x v="1"/>
+    <n v="1.1688232421875E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000034.smt2"/>
+    <x v="1"/>
+    <n v="9.2990398406982405E-3"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000035.smt2"/>
+    <x v="0"/>
+    <n v="0.71055889129638605"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000035.smt2"/>
+    <x v="0"/>
+    <n v="6.4224004745483398E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000035.smt2"/>
+    <x v="0"/>
+    <n v="4.8962116241455002E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000036.smt2"/>
+    <x v="0"/>
+    <n v="0.77157068252563399"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000036.smt2"/>
+    <x v="0"/>
+    <n v="1.2276649475097601E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000036.smt2"/>
+    <x v="0"/>
+    <n v="1.2424468994140601E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000037.smt2"/>
+    <x v="0"/>
+    <n v="0.62589168548583896"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000037.smt2"/>
+    <x v="0"/>
+    <n v="5.96060752868652E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000037.smt2"/>
+    <x v="0"/>
+    <n v="4.4213056564330999E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000038.smt2"/>
+    <x v="1"/>
+    <n v="0.163355112075805"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000038.smt2"/>
+    <x v="1"/>
+    <n v="1.00221633911132E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000038.smt2"/>
+    <x v="1"/>
+    <n v="1.1805772781371999E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000039.smt2"/>
+    <x v="0"/>
+    <n v="0.54885506629943803"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000039.smt2"/>
+    <x v="0"/>
+    <n v="6.1365842819213798E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000039.smt2"/>
+    <x v="0"/>
+    <n v="4.2194366455078097E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000040.smt2"/>
+    <x v="1"/>
+    <n v="0.16453742980957001"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000040.smt2"/>
+    <x v="1"/>
+    <n v="1.09097957611083E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000040.smt2"/>
+    <x v="1"/>
+    <n v="9.7630023956298793E-3"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000041.smt2"/>
+    <x v="0"/>
+    <n v="0.81094694137573198"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000041.smt2"/>
+    <x v="0"/>
+    <n v="5.8904409408569301E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000041.smt2"/>
+    <x v="0"/>
+    <n v="4.3220043182372998E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000042.smt2"/>
+    <x v="0"/>
+    <n v="0.218562841415405"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000042.smt2"/>
+    <x v="0"/>
+    <n v="1.30558013916015E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000042.smt2"/>
+    <x v="0"/>
+    <n v="1.1343717575073201E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000043.smt2"/>
+    <x v="0"/>
+    <n v="0.16717553138732899"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000043.smt2"/>
+    <x v="0"/>
+    <n v="0.117285251617431"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000043.smt2"/>
+    <x v="2"/>
+    <n v="4.6789646148681599E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000044.smt2"/>
+    <x v="0"/>
+    <n v="0.63217973709106401"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000044.smt2"/>
+    <x v="0"/>
+    <n v="6.06284141540527E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000044.smt2"/>
+    <x v="0"/>
+    <n v="4.3131351470947203E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000045.smt2"/>
+    <x v="1"/>
+    <n v="9.6984953880310005"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000045.smt2"/>
+    <x v="1"/>
+    <n v="0.45752215385437001"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000045.smt2"/>
+    <x v="2"/>
+    <n v="5.8704376220703097E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000046.smt2"/>
+    <x v="2"/>
+    <n v="101.55069398880001"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000046.smt2"/>
+    <x v="0"/>
+    <n v="55.186328172683702"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000046.smt2"/>
+    <x v="2"/>
+    <n v="0.116800069808959"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000047.smt2"/>
+    <x v="2"/>
+    <n v="100.980442523956"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000047.smt2"/>
+    <x v="1"/>
+    <n v="11.0270683765411"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000047.smt2"/>
+    <x v="2"/>
+    <n v="0.12814307212829501"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000048.smt2"/>
+    <x v="2"/>
+    <n v="100.540321350097"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000048.smt2"/>
+    <x v="2"/>
+    <n v="102.904328346252"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000048.smt2"/>
+    <x v="2"/>
+    <n v="8.0286900997161794"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000049.smt2"/>
+    <x v="2"/>
+    <n v="100.101659536361"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000049.smt2"/>
+    <x v="2"/>
+    <n v="102.762780904769"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000049.smt2"/>
+    <x v="2"/>
+    <n v="7.9743127822875897"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000050.smt2"/>
+    <x v="2"/>
+    <n v="100.1033577919"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000050.smt2"/>
+    <x v="0"/>
+    <n v="2.2781610488891602E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000050.smt2"/>
+    <x v="0"/>
+    <n v="2.15697288513183E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000051.smt2"/>
+    <x v="2"/>
+    <n v="100.103155136108"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000051.smt2"/>
+    <x v="0"/>
+    <n v="10.8118269443511"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000051.smt2"/>
+    <x v="2"/>
+    <n v="0.13244318962097101"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000052.smt2"/>
+    <x v="2"/>
+    <n v="100.10395026206901"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000052.smt2"/>
+    <x v="0"/>
+    <n v="11.7932810783386"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000052.smt2"/>
+    <x v="2"/>
+    <n v="0.113091468811035"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000053.smt2"/>
+    <x v="2"/>
+    <n v="100.103672027587"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000053.smt2"/>
+    <x v="0"/>
+    <n v="10.684314250946001"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000053.smt2"/>
+    <x v="2"/>
+    <n v="0.11482834815979"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000054.smt2"/>
+    <x v="2"/>
+    <n v="100.104493379592"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000054.smt2"/>
+    <x v="0"/>
+    <n v="10.6366739273071"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000054.smt2"/>
+    <x v="2"/>
+    <n v="0.113204717636108"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000055.smt2"/>
+    <x v="2"/>
+    <n v="100.104610681533"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000055.smt2"/>
+    <x v="1"/>
+    <n v="9.2768096923828107"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000055.smt2"/>
+    <x v="1"/>
+    <n v="10.3423652648925"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000056.smt2"/>
+    <x v="0"/>
+    <n v="2.8489601612090998"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000056.smt2"/>
+    <x v="0"/>
+    <n v="2.33149528503417E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000056.smt2"/>
+    <x v="0"/>
+    <n v="2.2301673889160101E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000057.smt2"/>
+    <x v="2"/>
+    <n v="100.104613304138"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000057.smt2"/>
+    <x v="0"/>
+    <n v="0.464864492416381"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000057.smt2"/>
+    <x v="2"/>
+    <n v="6.3155651092529297E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000058.smt2"/>
+    <x v="1"/>
+    <n v="0.24106359481811501"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000058.smt2"/>
+    <x v="1"/>
+    <n v="0.115168571472167"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000058.smt2"/>
+    <x v="2"/>
+    <n v="4.9031496047973598E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000059.smt2"/>
+    <x v="1"/>
+    <n v="0.192982196807861"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000059.smt2"/>
+    <x v="1"/>
+    <n v="9.1369152069091797E-3"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000059.smt2"/>
+    <x v="1"/>
+    <n v="7.9343318939208898E-3"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000060.smt2"/>
+    <x v="1"/>
+    <n v="5.3734707832336399"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000060.smt2"/>
+    <x v="1"/>
+    <n v="0.45754480361938399"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000060.smt2"/>
+    <x v="2"/>
+    <n v="7.5896024703979395E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000061.smt2"/>
+    <x v="2"/>
+    <n v="100.10366749763401"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000061.smt2"/>
+    <x v="1"/>
+    <n v="1.3182189464569001"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000061.smt2"/>
+    <x v="2"/>
+    <n v="6.6768407821655204E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000062.smt2"/>
+    <x v="2"/>
+    <n v="100.06978392601"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000062.smt2"/>
+    <x v="0"/>
+    <n v="0.572218418121337"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000062.smt2"/>
+    <x v="2"/>
+    <n v="6.4674854278564398E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000063.smt2"/>
+    <x v="1"/>
+    <n v="0.22595858573913499"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000063.smt2"/>
+    <x v="1"/>
+    <n v="0.120316982269287"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000063.smt2"/>
+    <x v="2"/>
+    <n v="0.140614509582519"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000064.smt2"/>
+    <x v="1"/>
+    <n v="0.18755245208740201"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000064.smt2"/>
+    <x v="1"/>
+    <n v="9.0727806091308594E-3"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000064.smt2"/>
+    <x v="1"/>
+    <n v="9.9568367004394497E-3"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000065.smt2"/>
+    <x v="2"/>
+    <n v="100.096255540847"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000065.smt2"/>
+    <x v="1"/>
+    <n v="0.463155508041381"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000065.smt2"/>
+    <x v="2"/>
+    <n v="6.7728042602538993E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000066.smt2"/>
+    <x v="1"/>
+    <n v="4.08691334724426"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000066.smt2"/>
+    <x v="1"/>
+    <n v="0.45934391021728499"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000066.smt2"/>
+    <x v="2"/>
+    <n v="7.1146249771118095E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000067.smt2"/>
+    <x v="1"/>
+    <n v="4.2244009971618599"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000067.smt2"/>
+    <x v="1"/>
+    <n v="0.46430850028991699"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000067.smt2"/>
+    <x v="2"/>
+    <n v="6.0230970382690402E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000068.smt2"/>
+    <x v="1"/>
+    <n v="4.2180705070495597"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000068.smt2"/>
+    <x v="1"/>
+    <n v="0.48046779632568298"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000068.smt2"/>
+    <x v="2"/>
+    <n v="6.1934709548950098E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000069.smt2"/>
+    <x v="2"/>
+    <n v="100.104227542877"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000069.smt2"/>
+    <x v="0"/>
+    <n v="10.550202369689901"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000069.smt2"/>
+    <x v="2"/>
+    <n v="0.116948127746582"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000070.smt2"/>
+    <x v="2"/>
+    <n v="100.104158639907"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000070.smt2"/>
+    <x v="1"/>
+    <n v="9.6964647769927907"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000070.smt2"/>
+    <x v="2"/>
+    <n v="0.119216680526733"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000071.smt2"/>
+    <x v="2"/>
+    <n v="100.106792449951"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000071.smt2"/>
+    <x v="2"/>
+    <n v="102.830458164215"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000071.smt2"/>
+    <x v="2"/>
+    <n v="8.1073417663574201"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000072.smt2"/>
+    <x v="2"/>
+    <n v="100.103860378265"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000072.smt2"/>
+    <x v="2"/>
+    <n v="103.01978445053101"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000072.smt2"/>
+    <x v="2"/>
+    <n v="8.0363807678222603"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000073.smt2"/>
+    <x v="2"/>
+    <n v="100.103489637374"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000073.smt2"/>
+    <x v="0"/>
+    <n v="2.2176980972290001E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000073.smt2"/>
+    <x v="0"/>
+    <n v="2.2228240966796799E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000074.smt2"/>
+    <x v="0"/>
+    <n v="3.3044857978820801"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000074.smt2"/>
+    <x v="0"/>
+    <n v="11.8450262546539"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000074.smt2"/>
+    <x v="2"/>
+    <n v="0.113598823547363"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000075.smt2"/>
+    <x v="2"/>
+    <n v="100.10417795181201"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000075.smt2"/>
+    <x v="0"/>
+    <n v="10.561582326889001"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000075.smt2"/>
+    <x v="2"/>
+    <n v="0.116568088531494"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000076.smt2"/>
+    <x v="2"/>
+    <n v="100.104630231857"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000076.smt2"/>
+    <x v="0"/>
+    <n v="10.7870483398437"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000076.smt2"/>
+    <x v="2"/>
+    <n v="0.11711072921752901"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000077.smt2"/>
+    <x v="2"/>
+    <n v="100.104633331298"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000077.smt2"/>
+    <x v="0"/>
+    <n v="11.829340457916199"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000077.smt2"/>
+    <x v="2"/>
+    <n v="0.116960048675537"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000078.smt2"/>
+    <x v="2"/>
+    <n v="100.017288923263"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000078.smt2"/>
+    <x v="1"/>
+    <n v="9.2319128513336093"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000078.smt2"/>
+    <x v="1"/>
+    <n v="10.3725688457489"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000079.smt2"/>
+    <x v="0"/>
+    <n v="3.0213925838470401"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000079.smt2"/>
+    <x v="0"/>
+    <n v="2.41920948028564E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000079.smt2"/>
+    <x v="0"/>
+    <n v="2.2059679031372001E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000080.smt2"/>
+    <x v="0"/>
+    <n v="8.4429767131805402"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000080.smt2"/>
+    <x v="0"/>
+    <n v="0.857588291168212"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000080.smt2"/>
+    <x v="0"/>
+    <n v="0.75850510597229004"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000081.smt2"/>
+    <x v="1"/>
+    <n v="0.194552421569824"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000081.smt2"/>
+    <x v="1"/>
+    <n v="9.0281963348388602E-3"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000081.smt2"/>
+    <x v="1"/>
+    <n v="8.6221694946288993E-3"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000082.smt2"/>
+    <x v="2"/>
+    <n v="100.103674650192"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000082.smt2"/>
+    <x v="0"/>
+    <n v="1.3803586959838801"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000082.smt2"/>
+    <x v="0"/>
+    <n v="1.3046307563781701"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000083.smt2"/>
+    <x v="2"/>
+    <n v="100.10447359085001"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000083.smt2"/>
+    <x v="1"/>
+    <n v="0.814053535461425"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000083.smt2"/>
+    <x v="1"/>
+    <n v="0.75070405006408603"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000084.smt2"/>
+    <x v="2"/>
+    <n v="100.0120139122"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000084.smt2"/>
+    <x v="0"/>
+    <n v="10.5684700012207"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000084.smt2"/>
+    <x v="2"/>
+    <n v="0.122172594070434"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000085.smt2"/>
+    <x v="1"/>
+    <n v="7.8902812004089302"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000085.smt2"/>
+    <x v="1"/>
+    <n v="0.444107055664062"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000085.smt2"/>
+    <x v="2"/>
+    <n v="6.2417268753051702E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000086.smt2"/>
+    <x v="1"/>
+    <n v="3.0788586139678902"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000086.smt2"/>
+    <x v="1"/>
+    <n v="1.2973814010620099"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000086.smt2"/>
+    <x v="2"/>
+    <n v="5.80039024353027E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000087.smt2"/>
+    <x v="2"/>
+    <n v="100.103590726852"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000087.smt2"/>
+    <x v="1"/>
+    <n v="0.80474185943603505"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000087.smt2"/>
+    <x v="1"/>
+    <n v="0.74081039428710904"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000088.smt2"/>
+    <x v="2"/>
+    <n v="100.104437589645"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000088.smt2"/>
+    <x v="1"/>
+    <n v="9.7817196846008301"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000088.smt2"/>
+    <x v="2"/>
+    <n v="0.11642408370971601"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000089.smt2"/>
+    <x v="2"/>
+    <n v="100.10421276092499"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000089.smt2"/>
+    <x v="1"/>
+    <n v="9.9216971397399902"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000089.smt2"/>
+    <x v="2"/>
+    <n v="0.119226694107055"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000090.smt2"/>
+    <x v="0"/>
+    <n v="7.5950124263763401"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000090.smt2"/>
+    <x v="0"/>
+    <n v="0.83846354484558105"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000090.smt2"/>
+    <x v="0"/>
+    <n v="0.77145075798034601"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000091.smt2"/>
+    <x v="1"/>
+    <n v="0.16583251953125"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000091.smt2"/>
+    <x v="1"/>
+    <n v="1.1050462722778299E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000091.smt2"/>
+    <x v="1"/>
+    <n v="1.2113094329833899E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000092.smt2"/>
+    <x v="1"/>
+    <n v="9.75142002105712"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000092.smt2"/>
+    <x v="1"/>
+    <n v="0.81234431266784601"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000092.smt2"/>
+    <x v="1"/>
+    <n v="0.736497402191162"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000093.smt2"/>
+    <x v="1"/>
+    <n v="8.6685678958892805"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000093.smt2"/>
+    <x v="1"/>
+    <n v="0.81416773796081499"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000093.smt2"/>
+    <x v="1"/>
+    <n v="0.73891758918762196"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000094.smt2"/>
+    <x v="1"/>
+    <n v="2.2575731277465798"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000094.smt2"/>
+    <x v="1"/>
+    <n v="0.44502305984496998"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000094.smt2"/>
+    <x v="2"/>
+    <n v="6.00049495697021E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000095.smt2"/>
+    <x v="2"/>
+    <n v="100.00971794128399"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000095.smt2"/>
+    <x v="1"/>
+    <n v="10.694043159484799"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000095.smt2"/>
+    <x v="2"/>
+    <n v="0.13203740119933999"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000096.smt2"/>
+    <x v="2"/>
+    <n v="100.10463571548399"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000096.smt2"/>
+    <x v="2"/>
+    <n v="102.83106851577701"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000096.smt2"/>
+    <x v="2"/>
+    <n v="8.0429515838622994"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000097.smt2"/>
+    <x v="2"/>
+    <n v="100.05347633361799"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000097.smt2"/>
+    <x v="2"/>
+    <n v="102.789240837097"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000097.smt2"/>
+    <x v="2"/>
+    <n v="7.9874482154846103"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000098.smt2"/>
+    <x v="2"/>
+    <n v="100.103863477706"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000098.smt2"/>
+    <x v="2"/>
+    <n v="102.743310451507"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000098.smt2"/>
+    <x v="2"/>
+    <n v="100.045338630676"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000099.smt2"/>
+    <x v="2"/>
+    <n v="100.10406970977699"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000099.smt2"/>
+    <x v="2"/>
+    <n v="102.753546953201"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000099.smt2"/>
+    <x v="2"/>
+    <n v="100.057497739791"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000100.smt2"/>
+    <x v="2"/>
+    <n v="100.104673624038"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000100.smt2"/>
+    <x v="2"/>
+    <n v="102.78602147102301"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000100.smt2"/>
+    <x v="2"/>
+    <n v="100.041392326354"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000101.smt2"/>
+    <x v="2"/>
+    <n v="100.10390734672499"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000101.smt2"/>
+    <x v="0"/>
+    <n v="2.8036355972290001E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000101.smt2"/>
+    <x v="0"/>
+    <n v="2.8535127639770501E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000102.smt2"/>
+    <x v="2"/>
+    <n v="100.103841304779"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000102.smt2"/>
+    <x v="2"/>
+    <n v="102.79785966873099"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000102.smt2"/>
+    <x v="2"/>
+    <n v="100.053363323211"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000103.smt2"/>
+    <x v="2"/>
+    <n v="100.104554414749"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000103.smt2"/>
+    <x v="2"/>
+    <n v="102.897040367126"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000103.smt2"/>
+    <x v="2"/>
+    <n v="100.045784235"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000104.smt2"/>
+    <x v="2"/>
+    <n v="100.104022979736"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000104.smt2"/>
+    <x v="2"/>
+    <n v="102.905977487564"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000104.smt2"/>
+    <x v="2"/>
+    <n v="100.048868894577"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000105.smt2"/>
+    <x v="2"/>
+    <n v="100.10406661033601"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000105.smt2"/>
+    <x v="2"/>
+    <n v="103.92190527915901"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000105.smt2"/>
+    <x v="2"/>
+    <n v="100.044727563858"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000106.smt2"/>
+    <x v="2"/>
+    <n v="100.10658073425201"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000106.smt2"/>
+    <x v="2"/>
+    <n v="102.944362401962"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000106.smt2"/>
+    <x v="2"/>
+    <n v="100.039130210876"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000107.smt2"/>
+    <x v="2"/>
+    <n v="100.041407585144"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000107.smt2"/>
+    <x v="2"/>
+    <n v="102.807678699493"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000107.smt2"/>
+    <x v="2"/>
+    <n v="100.04731726646401"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000108.smt2"/>
+    <x v="0"/>
+    <n v="3.02444076538085"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000108.smt2"/>
+    <x v="0"/>
+    <n v="2.8664827346801699E-2"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000108.smt2"/>
+    <x v="0"/>
+    <n v="2.94163227081298E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000109.smt2"/>
+    <x v="2"/>
+    <n v="100.104114770889"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000109.smt2"/>
+    <x v="0"/>
+    <n v="55.589154243469203"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000109.smt2"/>
+    <x v="2"/>
+    <n v="0.119300603866577"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000110.smt2"/>
+    <x v="1"/>
+    <n v="5.95265769958496"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000110.smt2"/>
+    <x v="1"/>
+    <n v="0.45155262947082497"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000110.smt2"/>
+    <x v="2"/>
+    <n v="6.1893463134765597E-2"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000111.smt2"/>
+    <x v="2"/>
+    <n v="100.10374546051"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000111.smt2"/>
+    <x v="1"/>
+    <n v="0.837837934494018"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000111.smt2"/>
+    <x v="1"/>
+    <n v="0.72359490394592196"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000112.smt2"/>
+    <x v="2"/>
+    <n v="100.10406088828999"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000112.smt2"/>
+    <x v="1"/>
+    <n v="10.837009906768699"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000112.smt2"/>
+    <x v="2"/>
+    <n v="0.11482429504394499"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000113.smt2"/>
+    <x v="2"/>
+    <n v="100.1045088768"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000113.smt2"/>
+    <x v="0"/>
+    <n v="10.6599640846252"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000113.smt2"/>
+    <x v="0"/>
+    <n v="11.814095258712699"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000114.smt2"/>
+    <x v="1"/>
+    <n v="5.1349015235900799"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000114.smt2"/>
+    <x v="1"/>
+    <n v="0.80120897293090798"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000114.smt2"/>
+    <x v="1"/>
+    <n v="0.71333432197570801"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000115.smt2"/>
+    <x v="2"/>
+    <n v="100.103924036026"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000115.smt2"/>
+    <x v="1"/>
+    <n v="0.80271553993225098"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000115.smt2"/>
+    <x v="1"/>
+    <n v="0.72495794296264604"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000116.smt2"/>
+    <x v="2"/>
+    <n v="100.104396343231"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000116.smt2"/>
+    <x v="1"/>
+    <n v="9.27725958824157"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000116.smt2"/>
+    <x v="1"/>
+    <n v="10.506611585617"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000117.smt2"/>
+    <x v="2"/>
+    <n v="100.10398316383301"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000117.smt2"/>
+    <x v="0"/>
+    <n v="11.553208351135201"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000117.smt2"/>
+    <x v="0"/>
+    <n v="11.802000522613501"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000118.smt2"/>
+    <x v="2"/>
+    <n v="100.104214668273"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000118.smt2"/>
+    <x v="2"/>
+    <n v="102.59962272644"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000118.smt2"/>
+    <x v="2"/>
+    <n v="7.9867048263549796"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000119.smt2"/>
+    <x v="1"/>
+    <n v="6.4669952392578098"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000119.smt2"/>
+    <x v="1"/>
+    <n v="9.8084259033203107"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000119.smt2"/>
+    <x v="2"/>
+    <n v="0.115933895111083"/>
+  </r>
+  <r>
+    <s v="bapa/card/fol_0000120.smt2"/>
+    <x v="2"/>
+    <n v="100.104124069213"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000120.smt2"/>
+    <x v="1"/>
+    <n v="9.2373118400573695"/>
+    <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000120.smt2"/>
+    <x v="1"/>
+    <n v="10.4824538230896"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7D55DB8C-C0D9-48E6-9B9F-FBA125C11914}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls" colHeaderCaption="cvc5 lia normaliz">
+  <location ref="A12:E17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="7"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4778405-FE92-45D5-9093-FA0E28569C7B}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls" colHeaderCaption="cvc5 lia">
+  <location ref="A3:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2465,6 +5349,202 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C7BCC34-B16B-45C0-B141-FAD55AFF40F3}">
+  <dimension ref="A3:E17"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="15">
+        <v>116</v>
+      </c>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A6" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="15">
+        <v>19</v>
+      </c>
+      <c r="C6" s="15">
+        <v>16</v>
+      </c>
+      <c r="D6" s="15">
+        <v>16</v>
+      </c>
+      <c r="E6" s="15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="15"/>
+      <c r="C7" s="15"/>
+      <c r="D7" s="15">
+        <v>73</v>
+      </c>
+      <c r="E7" s="15">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="B8" s="15">
+        <v>135</v>
+      </c>
+      <c r="C8" s="15">
+        <v>16</v>
+      </c>
+      <c r="D8" s="15">
+        <v>89</v>
+      </c>
+      <c r="E8" s="15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A12" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A13" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="15">
+        <v>84</v>
+      </c>
+      <c r="C14" s="15">
+        <v>32</v>
+      </c>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A15" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="B15" s="15">
+        <v>6</v>
+      </c>
+      <c r="C15" s="15">
+        <v>37</v>
+      </c>
+      <c r="D15" s="15">
+        <v>8</v>
+      </c>
+      <c r="E15" s="15">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A16" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15">
+        <v>36</v>
+      </c>
+      <c r="D16" s="15">
+        <v>37</v>
+      </c>
+      <c r="E16" s="15">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="B17" s="15">
+        <v>90</v>
+      </c>
+      <c r="C17" s="15">
+        <v>105</v>
+      </c>
+      <c r="D17" s="15">
+        <v>45</v>
+      </c>
+      <c r="E17" s="15">
+        <v>240</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEEC5DD9-14C3-4C18-9355-6C6BFA91C6D6}">
   <dimension ref="A1:I241"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/comparison_bapa.xlsx
+++ b/comparison_bapa.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mudathir\all\sls-reachability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D91AEEA-E528-4CF4-9497-BBDC8F7CF243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6C9570F-84A0-445A-94AE-5D7775087996}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{43139118-C9B1-4C53-BA07-4D51B812E9BD}"/>
   </bookViews>
   <sheets>
-    <sheet name="pivot table" sheetId="2" r:id="rId1"/>
-    <sheet name="comparison_bapa" sheetId="1" r:id="rId2"/>
+    <sheet name="Detail1" sheetId="4" r:id="rId1"/>
+    <sheet name="pivot table" sheetId="2" r:id="rId2"/>
+    <sheet name="comparison_bapa" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="5" r:id="rId3"/>
+    <pivotCache cacheId="20" r:id="rId4"/>
   </pivotCaches>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1471" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2010" uniqueCount="743">
   <si>
     <t>sls file</t>
   </si>
@@ -1515,6 +1516,744 @@
   </si>
   <si>
     <t>cvc5 lia normaliz</t>
+  </si>
+  <si>
+    <t>SAT</t>
+  </si>
+  <si>
+    <t>UNSAT</t>
+  </si>
+  <si>
+    <t>sqlsolver filename</t>
+  </si>
+  <si>
+    <t>sqlsolver result</t>
+  </si>
+  <si>
+    <t>sqlsolver duration</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000001.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000002.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000003.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000004.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000005.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000006.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000007.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000008.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000009.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000010.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000011.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000012.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000013.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000014.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000015.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000016.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000017.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000018.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000019.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000020.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000021.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000022.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000023.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000024.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000025.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000026.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000027.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000028.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000029.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000030.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000031.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000032.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000033.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000034.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000035.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000036.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000037.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000038.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000039.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000040.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000041.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000042.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000043.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000044.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000045.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000046.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000047.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000048.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000049.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000050.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000051.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000052.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000053.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000054.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000055.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000056.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000057.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000058.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000059.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000060.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000061.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000062.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000063.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000064.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000065.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000066.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000067.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000068.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000069.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000070.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000071.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000072.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000073.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000074.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000075.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000076.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000077.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000078.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000079.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000080.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000081.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000082.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000083.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000084.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000085.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000086.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000087.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000088.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000089.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000090.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000091.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000092.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000093.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000094.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000095.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000096.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000097.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000098.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000099.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000100.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000101.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000102.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000103.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000104.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000105.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000106.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000107.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000108.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000109.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000110.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000111.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000112.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000113.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000114.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000115.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000116.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000117.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000118.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000119.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000120.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000001.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000002.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000003.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000004.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000005.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000006.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000007.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000008.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000009.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000010.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000011.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000012.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000013.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000014.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000015.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000016.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000017.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000018.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000019.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000020.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000021.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000022.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000023.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000024.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000025.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000026.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000027.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000028.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000029.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000030.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000031.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000032.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000033.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000034.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000035.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000036.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000037.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000038.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000039.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000040.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000041.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000042.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000043.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000044.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000045.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000046.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000047.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000048.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000049.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000050.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000051.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000052.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000053.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000054.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000055.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000056.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000057.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000058.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000059.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000060.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000061.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000062.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000063.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000064.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000065.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000066.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000067.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000068.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000069.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000070.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000071.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000072.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000073.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000074.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000075.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000076.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000077.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000078.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000079.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000080.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000081.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000082.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000083.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000084.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000085.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000086.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000087.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000088.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000089.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000090.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000091.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000092.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000093.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000094.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000095.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000096.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000097.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000098.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000099.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000100.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000101.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000102.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000103.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000104.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000105.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000106.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000107.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000108.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000109.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000110.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000111.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000112.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000113.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000114.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000115.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000116.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000117.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000118.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000119.smt2</t>
+  </si>
+  <si>
+    <t>/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000120.smt2</t>
+  </si>
+  <si>
+    <t>Details for Count of sls duration - sqlsolver result: SAT, cvc5 lia result: unsat</t>
   </si>
 </sst>
 </file>
@@ -2078,7 +2817,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
@@ -2097,6 +2836,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2156,11 +2896,11 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Mudathir Mahgoub" refreshedDate="46114.463886805555" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="240" xr:uid="{83E52B08-862F-4C7F-9D9D-28C890578037}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Mudathir Mahgoub" refreshedDate="46137.74307326389" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="240" xr:uid="{83E52B08-862F-4C7F-9D9D-28C890578037}">
   <cacheSource type="worksheet">
     <worksheetSource name="Table1"/>
   </cacheSource>
-  <cacheFields count="9">
+  <cacheFields count="12">
     <cacheField name="sls file" numFmtId="0">
       <sharedItems/>
     </cacheField>
@@ -2200,6 +2940,19 @@
     <cacheField name="lia normaliz duration" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="7.9343318939208898E-3" maxValue="100.057497739791"/>
     </cacheField>
+    <cacheField name="sqlsolver filename" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="sqlsolver result" numFmtId="0">
+      <sharedItems count="3">
+        <s v="SAT"/>
+        <s v="UNSAT"/>
+        <s v="timeout"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="sqlsolver duration" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="8.9999999999999993E-3" maxValue="100"/>
+    </cacheField>
   </cacheFields>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
@@ -2221,6 +2974,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000001.smt2"/>
     <x v="0"/>
     <n v="0.101495265960693"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000001.smt2"/>
+    <x v="0"/>
+    <n v="0.20499999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000002.smt2"/>
@@ -2232,6 +2988,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000002.smt2"/>
     <x v="0"/>
     <n v="1.44908428192138E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000002.smt2"/>
+    <x v="0"/>
+    <n v="1.7000000000000001E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000003.smt2"/>
@@ -2243,6 +3002,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000003.smt2"/>
     <x v="0"/>
     <n v="2.0340681076049801E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000003.smt2"/>
+    <x v="0"/>
+    <n v="1.6E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000004.smt2"/>
@@ -2254,6 +3016,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000004.smt2"/>
     <x v="0"/>
     <n v="8.1681728363037095E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000004.smt2"/>
+    <x v="0"/>
+    <n v="1.4E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000005.smt2"/>
@@ -2265,6 +3030,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000005.smt2"/>
     <x v="0"/>
     <n v="4.7867774963378899E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000005.smt2"/>
+    <x v="0"/>
+    <n v="1.2E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000006.smt2"/>
@@ -2276,6 +3044,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000006.smt2"/>
     <x v="0"/>
     <n v="5.0418615341186503E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000006.smt2"/>
+    <x v="0"/>
+    <n v="1.2999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000007.smt2"/>
@@ -2287,6 +3058,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000007.smt2"/>
     <x v="0"/>
     <n v="4.5779228210449198E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000007.smt2"/>
+    <x v="0"/>
+    <n v="0.28000000000000003"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000008.smt2"/>
@@ -2298,6 +3072,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000008.smt2"/>
     <x v="0"/>
     <n v="4.58817481994628E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000008.smt2"/>
+    <x v="0"/>
+    <n v="1.4E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000009.smt2"/>
@@ -2309,6 +3086,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000009.smt2"/>
     <x v="0"/>
     <n v="4.4304609298705999E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000009.smt2"/>
+    <x v="0"/>
+    <n v="0.23"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000010.smt2"/>
@@ -2320,6 +3100,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000010.smt2"/>
     <x v="0"/>
     <n v="4.4718265533447203E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000010.smt2"/>
+    <x v="0"/>
+    <n v="0.20399999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000011.smt2"/>
@@ -2331,6 +3114,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000011.smt2"/>
     <x v="0"/>
     <n v="4.4330596923828097E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000011.smt2"/>
+    <x v="0"/>
+    <n v="0.21099999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000012.smt2"/>
@@ -2342,6 +3128,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000012.smt2"/>
     <x v="0"/>
     <n v="4.4733524322509703E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000012.smt2"/>
+    <x v="0"/>
+    <n v="0.192"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000013.smt2"/>
@@ -2353,6 +3142,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000013.smt2"/>
     <x v="0"/>
     <n v="4.4816970825195299E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000013.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000014.smt2"/>
@@ -2364,6 +3156,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000014.smt2"/>
     <x v="0"/>
     <n v="4.4156074523925698E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000014.smt2"/>
+    <x v="0"/>
+    <n v="0.01"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000015.smt2"/>
@@ -2375,6 +3170,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000015.smt2"/>
     <x v="0"/>
     <n v="4.3086290359497001E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000015.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000016.smt2"/>
@@ -2386,6 +3184,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000016.smt2"/>
     <x v="0"/>
     <n v="4.6988010406494099E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000016.smt2"/>
+    <x v="0"/>
+    <n v="1.2E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000017.smt2"/>
@@ -2397,6 +3198,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000017.smt2"/>
     <x v="0"/>
     <n v="4.3082714080810498E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000017.smt2"/>
+    <x v="0"/>
+    <n v="1.2E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000018.smt2"/>
@@ -2408,6 +3212,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000018.smt2"/>
     <x v="0"/>
     <n v="4.4025659561157199E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000018.smt2"/>
+    <x v="0"/>
+    <n v="1.4E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000019.smt2"/>
@@ -2419,6 +3226,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000019.smt2"/>
     <x v="0"/>
     <n v="4.9208641052245997E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000019.smt2"/>
+    <x v="0"/>
+    <n v="0.215"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000020.smt2"/>
@@ -2430,6 +3240,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000020.smt2"/>
     <x v="0"/>
     <n v="4.9638271331787102E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000020.smt2"/>
+    <x v="0"/>
+    <n v="0.20200000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000021.smt2"/>
@@ -2441,6 +3254,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000021.smt2"/>
     <x v="1"/>
     <n v="1.1879682540893499E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000021.smt2"/>
+    <x v="1"/>
+    <n v="2.3E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000022.smt2"/>
@@ -2452,6 +3268,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000022.smt2"/>
     <x v="0"/>
     <n v="4.5344114303588798E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000022.smt2"/>
+    <x v="0"/>
+    <n v="0.20100000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000023.smt2"/>
@@ -2463,6 +3282,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000023.smt2"/>
     <x v="1"/>
     <n v="1.0849714279174799E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000023.smt2"/>
+    <x v="1"/>
+    <n v="2.4E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000024.smt2"/>
@@ -2474,6 +3296,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000024.smt2"/>
     <x v="0"/>
     <n v="4.9724578857421799E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000024.smt2"/>
+    <x v="0"/>
+    <n v="0.19900000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000025.smt2"/>
@@ -2485,6 +3310,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000025.smt2"/>
     <x v="0"/>
     <n v="1.3100862503051701E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000025.smt2"/>
+    <x v="0"/>
+    <n v="1.4999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000026.smt2"/>
@@ -2496,6 +3324,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000026.smt2"/>
     <x v="0"/>
     <n v="1.2727499008178701E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000026.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000027.smt2"/>
@@ -2507,6 +3338,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000027.smt2"/>
     <x v="0"/>
     <n v="1.29928588867187E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000027.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000028.smt2"/>
@@ -2518,6 +3352,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000028.smt2"/>
     <x v="2"/>
     <n v="6.2685966491699205E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000028.smt2"/>
+    <x v="1"/>
+    <n v="0.22900000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000029.smt2"/>
@@ -2529,6 +3366,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000029.smt2"/>
     <x v="2"/>
     <n v="0.122227668762207"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000029.smt2"/>
+    <x v="0"/>
+    <n v="0.22600000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000030.smt2"/>
@@ -2540,6 +3380,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000030.smt2"/>
     <x v="1"/>
     <n v="1.16009712219238E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000030.smt2"/>
+    <x v="1"/>
+    <n v="1.9E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000031.smt2"/>
@@ -2551,6 +3394,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000031.smt2"/>
     <x v="0"/>
     <n v="4.8797607421875E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000031.smt2"/>
+    <x v="0"/>
+    <n v="0.01"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000032.smt2"/>
@@ -2562,6 +3408,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000032.smt2"/>
     <x v="1"/>
     <n v="9.9892616271972604E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000032.smt2"/>
+    <x v="1"/>
+    <n v="1.9E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000033.smt2"/>
@@ -2573,6 +3422,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000033.smt2"/>
     <x v="0"/>
     <n v="4.4088840484619099E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000033.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000034.smt2"/>
@@ -2584,6 +3436,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000034.smt2"/>
     <x v="1"/>
     <n v="9.7904205322265608E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000034.smt2"/>
+    <x v="1"/>
+    <n v="1.9E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000035.smt2"/>
@@ -2595,6 +3450,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000035.smt2"/>
     <x v="0"/>
     <n v="4.8144340515136698E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000035.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000036.smt2"/>
@@ -2606,6 +3464,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000036.smt2"/>
     <x v="0"/>
     <n v="1.2047529220580999E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000036.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000037.smt2"/>
@@ -2617,6 +3478,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000037.smt2"/>
     <x v="0"/>
     <n v="4.31671142578125E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000037.smt2"/>
+    <x v="0"/>
+    <n v="0.189"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000038.smt2"/>
@@ -2628,6 +3492,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000038.smt2"/>
     <x v="1"/>
     <n v="9.9687576293945295E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000038.smt2"/>
+    <x v="1"/>
+    <n v="1.7999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000039.smt2"/>
@@ -2639,6 +3506,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000039.smt2"/>
     <x v="0"/>
     <n v="4.4043779373168897E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000039.smt2"/>
+    <x v="0"/>
+    <n v="0.193"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000040.smt2"/>
@@ -2650,6 +3520,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000040.smt2"/>
     <x v="1"/>
     <n v="9.9987983703613195E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000040.smt2"/>
+    <x v="1"/>
+    <n v="1.9E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000041.smt2"/>
@@ -2661,6 +3534,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000041.smt2"/>
     <x v="0"/>
     <n v="4.6099662780761698E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000041.smt2"/>
+    <x v="0"/>
+    <n v="0.191"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000042.smt2"/>
@@ -2672,6 +3548,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000042.smt2"/>
     <x v="0"/>
     <n v="1.2178897857666E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000042.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000043.smt2"/>
@@ -2683,6 +3562,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000043.smt2"/>
     <x v="2"/>
     <n v="4.4809579849243102E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000043.smt2"/>
+    <x v="0"/>
+    <n v="0.223"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000044.smt2"/>
@@ -2694,6 +3576,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000044.smt2"/>
     <x v="0"/>
     <n v="4.4211626052856397E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000044.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000045.smt2"/>
@@ -2705,6 +3590,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000045.smt2"/>
     <x v="2"/>
     <n v="4.9978256225585903E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000045.smt2"/>
+    <x v="1"/>
+    <n v="0.22900000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000046.smt2"/>
@@ -2716,6 +3604,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000046.smt2"/>
     <x v="2"/>
     <n v="4.6791315078735303E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000046.smt2"/>
+    <x v="0"/>
+    <n v="0.24099999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000047.smt2"/>
@@ -2727,6 +3618,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000047.smt2"/>
     <x v="2"/>
     <n v="9.0545415878295898E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000047.smt2"/>
+    <x v="1"/>
+    <n v="0.222"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000048.smt2"/>
@@ -2738,6 +3632,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000048.smt2"/>
     <x v="2"/>
     <n v="4.6838283538818297E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000048.smt2"/>
+    <x v="0"/>
+    <n v="0.215"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000049.smt2"/>
@@ -2749,6 +3646,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000049.smt2"/>
     <x v="2"/>
     <n v="5.4154872894287102E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000049.smt2"/>
+    <x v="0"/>
+    <n v="0.22600000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000050.smt2"/>
@@ -2760,6 +3660,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000050.smt2"/>
     <x v="0"/>
     <n v="1.9216775894165001E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000050.smt2"/>
+    <x v="0"/>
+    <n v="1.2E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000051.smt2"/>
@@ -2771,6 +3674,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000051.smt2"/>
     <x v="2"/>
     <n v="5.2750825881958001E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000051.smt2"/>
+    <x v="0"/>
+    <n v="0.23"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000052.smt2"/>
@@ -2782,6 +3688,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000052.smt2"/>
     <x v="2"/>
     <n v="0.161716699600219"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000052.smt2"/>
+    <x v="0"/>
+    <n v="0.23499999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000053.smt2"/>
@@ -2793,6 +3702,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000053.smt2"/>
     <x v="2"/>
     <n v="5.3837537765502902E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000053.smt2"/>
+    <x v="0"/>
+    <n v="0.22600000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000054.smt2"/>
@@ -2804,6 +3716,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000054.smt2"/>
     <x v="2"/>
     <n v="6.1524391174316399E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000054.smt2"/>
+    <x v="0"/>
+    <n v="0.22500000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000055.smt2"/>
@@ -2815,6 +3730,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000055.smt2"/>
     <x v="1"/>
     <n v="1.1770963668823201E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000055.smt2"/>
+    <x v="1"/>
+    <n v="3.4000000000000002E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000056.smt2"/>
@@ -2826,6 +3744,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000056.smt2"/>
     <x v="0"/>
     <n v="4.50634956359863E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000056.smt2"/>
+    <x v="0"/>
+    <n v="0.501"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000057.smt2"/>
@@ -2837,6 +3758,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000057.smt2"/>
     <x v="2"/>
     <n v="4.7250747680664E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000057.smt2"/>
+    <x v="0"/>
+    <n v="0.28100000000000003"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000058.smt2"/>
@@ -2848,6 +3772,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000058.smt2"/>
     <x v="2"/>
     <n v="5.5867433547973598E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000058.smt2"/>
+    <x v="1"/>
+    <n v="0.23300000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000059.smt2"/>
@@ -2859,6 +3786,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000059.smt2"/>
     <x v="1"/>
     <n v="9.9360942840576102E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000059.smt2"/>
+    <x v="1"/>
+    <n v="1.7000000000000001E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000060.smt2"/>
@@ -2870,6 +3800,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000060.smt2"/>
     <x v="2"/>
     <n v="5.0779104232788003E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000060.smt2"/>
+    <x v="1"/>
+    <n v="0.223"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000061.smt2"/>
@@ -2881,6 +3814,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000061.smt2"/>
     <x v="2"/>
     <n v="4.8722743988037102E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000061.smt2"/>
+    <x v="1"/>
+    <n v="0.22700000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000062.smt2"/>
@@ -2892,6 +3828,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000062.smt2"/>
     <x v="2"/>
     <n v="4.6223640441894497E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000062.smt2"/>
+    <x v="0"/>
+    <n v="0.23400000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000063.smt2"/>
@@ -2903,6 +3842,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000063.smt2"/>
     <x v="2"/>
     <n v="4.4949531555175698E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000063.smt2"/>
+    <x v="1"/>
+    <n v="0.224"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000064.smt2"/>
@@ -2914,6 +3856,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000064.smt2"/>
     <x v="1"/>
     <n v="1.0486602783203101E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000064.smt2"/>
+    <x v="1"/>
+    <n v="1.7999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000065.smt2"/>
@@ -2925,6 +3870,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000065.smt2"/>
     <x v="2"/>
     <n v="4.6811819076538003E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000065.smt2"/>
+    <x v="1"/>
+    <n v="0.224"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000066.smt2"/>
@@ -2936,6 +3884,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000066.smt2"/>
     <x v="2"/>
     <n v="4.4660806655883699E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000066.smt2"/>
+    <x v="1"/>
+    <n v="0.23799999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000067.smt2"/>
@@ -2947,6 +3898,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000067.smt2"/>
     <x v="2"/>
     <n v="0.122978687286376"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000067.smt2"/>
+    <x v="1"/>
+    <n v="0.23699999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000068.smt2"/>
@@ -2958,6 +3912,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000068.smt2"/>
     <x v="2"/>
     <n v="7.0685386657714802E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000068.smt2"/>
+    <x v="1"/>
+    <n v="0.22500000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000069.smt2"/>
@@ -2969,6 +3926,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000069.smt2"/>
     <x v="2"/>
     <n v="4.7506093978881801E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000069.smt2"/>
+    <x v="0"/>
+    <n v="0.23"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000070.smt2"/>
@@ -2980,6 +3940,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000070.smt2"/>
     <x v="2"/>
     <n v="5.5344104766845703E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000070.smt2"/>
+    <x v="1"/>
+    <n v="0.24299999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000071.smt2"/>
@@ -2991,6 +3954,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000071.smt2"/>
     <x v="2"/>
     <n v="5.0118207931518499E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000071.smt2"/>
+    <x v="0"/>
+    <n v="0.224"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000072.smt2"/>
@@ -3002,6 +3968,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000072.smt2"/>
     <x v="2"/>
     <n v="5.0841093063354402E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000072.smt2"/>
+    <x v="0"/>
+    <n v="0.23899999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000073.smt2"/>
@@ -3013,6 +3982,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000073.smt2"/>
     <x v="0"/>
     <n v="1.72088146209716E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000073.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000074.smt2"/>
@@ -3024,6 +3996,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000074.smt2"/>
     <x v="2"/>
     <n v="4.8106908798217697E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000074.smt2"/>
+    <x v="0"/>
+    <n v="0.39400000000000002"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000075.smt2"/>
@@ -3035,6 +4010,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000075.smt2"/>
     <x v="2"/>
     <n v="4.7061443328857401E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000075.smt2"/>
+    <x v="0"/>
+    <n v="0.55100000000000005"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000076.smt2"/>
@@ -3046,6 +4024,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000076.smt2"/>
     <x v="2"/>
     <n v="0.14733719825744601"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000076.smt2"/>
+    <x v="0"/>
+    <n v="0.23200000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000077.smt2"/>
@@ -3057,6 +4038,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000077.smt2"/>
     <x v="2"/>
     <n v="5.1762580871581997E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000077.smt2"/>
+    <x v="0"/>
+    <n v="0.223"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000078.smt2"/>
@@ -3068,6 +4052,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000078.smt2"/>
     <x v="1"/>
     <n v="1.2853860855102499E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000078.smt2"/>
+    <x v="1"/>
+    <n v="0.02"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000079.smt2"/>
@@ -3079,6 +4066,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000079.smt2"/>
     <x v="0"/>
     <n v="5.3411960601806599E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000079.smt2"/>
+    <x v="0"/>
+    <n v="0.20599999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000080.smt2"/>
@@ -3090,6 +4080,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000080.smt2"/>
     <x v="0"/>
     <n v="4.4915676116943297E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000080.smt2"/>
+    <x v="0"/>
+    <n v="0.186"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000081.smt2"/>
@@ -3101,6 +4094,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000081.smt2"/>
     <x v="1"/>
     <n v="9.6285343170165998E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000081.smt2"/>
+    <x v="1"/>
+    <n v="1.6E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000082.smt2"/>
@@ -3112,6 +4108,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000082.smt2"/>
     <x v="0"/>
     <n v="4.5893430709838798E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000082.smt2"/>
+    <x v="0"/>
+    <n v="0.20599999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000083.smt2"/>
@@ -3123,6 +4122,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000083.smt2"/>
     <x v="1"/>
     <n v="1.0493993759155201E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000083.smt2"/>
+    <x v="1"/>
+    <n v="2.7E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000084.smt2"/>
@@ -3134,6 +4136,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000084.smt2"/>
     <x v="2"/>
     <n v="4.95438575744628E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000084.smt2"/>
+    <x v="0"/>
+    <n v="0.54700000000000004"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000085.smt2"/>
@@ -3145,6 +4150,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000085.smt2"/>
     <x v="2"/>
     <n v="4.7630786895751898E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000085.smt2"/>
+    <x v="1"/>
+    <n v="0.24"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000086.smt2"/>
@@ -3156,6 +4164,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000086.smt2"/>
     <x v="2"/>
     <n v="4.96673583984375E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000086.smt2"/>
+    <x v="1"/>
+    <n v="0.224"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000087.smt2"/>
@@ -3167,6 +4178,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000087.smt2"/>
     <x v="1"/>
     <n v="1.1652946472167899E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000087.smt2"/>
+    <x v="1"/>
+    <n v="1.9E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000088.smt2"/>
@@ -3178,6 +4192,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000088.smt2"/>
     <x v="2"/>
     <n v="5.0182104110717697E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000088.smt2"/>
+    <x v="1"/>
+    <n v="0.223"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000089.smt2"/>
@@ -3189,6 +4206,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000089.smt2"/>
     <x v="2"/>
     <n v="5.2581310272216797E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000089.smt2"/>
+    <x v="1"/>
+    <n v="0.223"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000090.smt2"/>
@@ -3200,6 +4220,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000090.smt2"/>
     <x v="0"/>
     <n v="4.3616771697997998E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000090.smt2"/>
+    <x v="0"/>
+    <n v="0.193"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000091.smt2"/>
@@ -3211,6 +4234,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000091.smt2"/>
     <x v="1"/>
     <n v="9.5777511596679601E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000091.smt2"/>
+    <x v="1"/>
+    <n v="1.9E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000092.smt2"/>
@@ -3222,6 +4248,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000092.smt2"/>
     <x v="1"/>
     <n v="1.09376907348632E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000092.smt2"/>
+    <x v="1"/>
+    <n v="2.5999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000093.smt2"/>
@@ -3233,6 +4262,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000093.smt2"/>
     <x v="1"/>
     <n v="1.01594924926757E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000093.smt2"/>
+    <x v="1"/>
+    <n v="3.5000000000000003E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000094.smt2"/>
@@ -3244,6 +4276,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000094.smt2"/>
     <x v="2"/>
     <n v="4.7819852828979402E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000094.smt2"/>
+    <x v="1"/>
+    <n v="0.223"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000095.smt2"/>
@@ -3255,6 +4290,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000095.smt2"/>
     <x v="2"/>
     <n v="4.8085451126098598E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000095.smt2"/>
+    <x v="1"/>
+    <n v="0.24"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000096.smt2"/>
@@ -3266,6 +4304,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000096.smt2"/>
     <x v="2"/>
     <n v="4.7187328338622998E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000096.smt2"/>
+    <x v="0"/>
+    <n v="0.22800000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000097.smt2"/>
@@ -3277,6 +4318,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000097.smt2"/>
     <x v="2"/>
     <n v="4.77674007415771E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000097.smt2"/>
+    <x v="1"/>
+    <n v="0.23"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000098.smt2"/>
@@ -3288,6 +4332,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000098.smt2"/>
     <x v="2"/>
     <n v="4.6757459640502902E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000098.smt2"/>
+    <x v="1"/>
+    <n v="0.24299999999999999"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000099.smt2"/>
@@ -3299,6 +4346,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000099.smt2"/>
     <x v="2"/>
     <n v="4.6641349792480399E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000099.smt2"/>
+    <x v="0"/>
+    <n v="0.23"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000100.smt2"/>
@@ -3310,6 +4360,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000100.smt2"/>
     <x v="2"/>
     <n v="4.5722961425781201E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000100.smt2"/>
+    <x v="0"/>
+    <n v="0.223"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000101.smt2"/>
@@ -3321,6 +4374,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000101.smt2"/>
     <x v="0"/>
     <n v="1.7483234405517498E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000101.smt2"/>
+    <x v="0"/>
+    <n v="8.9999999999999993E-3"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000102.smt2"/>
@@ -3332,6 +4388,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000102.smt2"/>
     <x v="2"/>
     <n v="5.6472063064575098E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000102.smt2"/>
+    <x v="0"/>
+    <n v="0.22900000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000103.smt2"/>
@@ -3343,6 +4402,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000103.smt2"/>
     <x v="2"/>
     <n v="8.8441848754882799E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000103.smt2"/>
+    <x v="0"/>
+    <n v="0.22600000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000104.smt2"/>
@@ -3354,6 +4416,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000104.smt2"/>
     <x v="2"/>
     <n v="8.3253383636474595E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000104.smt2"/>
+    <x v="0"/>
+    <n v="0.222"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000105.smt2"/>
@@ -3365,6 +4430,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000105.smt2"/>
     <x v="2"/>
     <n v="0.130986928939819"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000105.smt2"/>
+    <x v="0"/>
+    <n v="0.22800000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000106.smt2"/>
@@ -3376,6 +4444,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000106.smt2"/>
     <x v="2"/>
     <n v="0.205983877182006"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000106.smt2"/>
+    <x v="0"/>
+    <n v="0.23100000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000107.smt2"/>
@@ -3387,6 +4458,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000107.smt2"/>
     <x v="1"/>
     <n v="1.12090110778808E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000107.smt2"/>
+    <x v="1"/>
+    <n v="0.02"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000108.smt2"/>
@@ -3398,6 +4472,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000108.smt2"/>
     <x v="0"/>
     <n v="5.10697364807128E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000108.smt2"/>
+    <x v="0"/>
+    <n v="0.187"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000109.smt2"/>
@@ -3409,6 +4486,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000109.smt2"/>
     <x v="2"/>
     <n v="4.6656370162963798E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000109.smt2"/>
+    <x v="0"/>
+    <n v="0.22800000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000110.smt2"/>
@@ -3420,6 +4500,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000110.smt2"/>
     <x v="2"/>
     <n v="4.4392347335815402E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000110.smt2"/>
+    <x v="1"/>
+    <n v="0.216"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000111.smt2"/>
@@ -3431,6 +4514,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000111.smt2"/>
     <x v="1"/>
     <n v="1.0449886322021399E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000111.smt2"/>
+    <x v="1"/>
+    <n v="1.6E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000112.smt2"/>
@@ -3442,6 +4528,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000112.smt2"/>
     <x v="2"/>
     <n v="4.7589778900146401E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000112.smt2"/>
+    <x v="1"/>
+    <n v="0.54200000000000004"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000113.smt2"/>
@@ -3453,6 +4542,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000113.smt2"/>
     <x v="0"/>
     <n v="4.43463325500488E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000113.smt2"/>
+    <x v="0"/>
+    <n v="0.47499999999999998"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000114.smt2"/>
@@ -3464,6 +4556,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000114.smt2"/>
     <x v="1"/>
     <n v="1.0713100433349601E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000114.smt2"/>
+    <x v="1"/>
+    <n v="1.7999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000115.smt2"/>
@@ -3475,6 +4570,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000115.smt2"/>
     <x v="1"/>
     <n v="1.0607957839965799E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000115.smt2"/>
+    <x v="1"/>
+    <n v="1.7000000000000001E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000116.smt2"/>
@@ -3486,6 +4584,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000116.smt2"/>
     <x v="1"/>
     <n v="1.08428001403808E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000116.smt2"/>
+    <x v="1"/>
+    <n v="2.3E-2"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000117.smt2"/>
@@ -3497,6 +4598,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000117.smt2"/>
     <x v="0"/>
     <n v="4.5263528823852497E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000117.smt2"/>
+    <x v="0"/>
+    <n v="0.188"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000118.smt2"/>
@@ -3508,6 +4612,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000118.smt2"/>
     <x v="2"/>
     <n v="4.5195817947387598E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000118.smt2"/>
+    <x v="0"/>
+    <n v="0.216"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000119.smt2"/>
@@ -3519,6 +4626,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000119.smt2"/>
     <x v="2"/>
     <n v="6.0981273651122998E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000119.smt2"/>
+    <x v="1"/>
+    <n v="0.22700000000000001"/>
   </r>
   <r>
     <s v="bapa/arith/fol_0000120.smt2"/>
@@ -3530,6 +4640,9 @@
     <s v="benchmarks/bapa/arith/cvc5_bapa/fol_0000120.smt2"/>
     <x v="1"/>
     <n v="1.0813713073730399E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/arith/cvc5_bapa/fol_0000120.smt2"/>
+    <x v="1"/>
+    <n v="1.7999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000001.smt2"/>
@@ -3541,6 +4654,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000001.smt2"/>
     <x v="0"/>
     <n v="1.2289762496948201E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000001.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000002.smt2"/>
@@ -3552,6 +4668,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000002.smt2"/>
     <x v="0"/>
     <n v="1.30712985992431E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000002.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000003.smt2"/>
@@ -3563,6 +4682,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000003.smt2"/>
     <x v="0"/>
     <n v="1.15993022918701E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000003.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000004.smt2"/>
@@ -3574,6 +4696,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000004.smt2"/>
     <x v="0"/>
     <n v="4.4612407684326102E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000004.smt2"/>
+    <x v="0"/>
+    <n v="0.01"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000005.smt2"/>
@@ -3585,6 +4710,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000005.smt2"/>
     <x v="0"/>
     <n v="4.2409181594848598E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000005.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000006.smt2"/>
@@ -3596,6 +4724,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000006.smt2"/>
     <x v="0"/>
     <n v="5.1395416259765597E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000006.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000007.smt2"/>
@@ -3607,6 +4738,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000007.smt2"/>
     <x v="0"/>
     <n v="4.1522502899169901E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000007.smt2"/>
+    <x v="0"/>
+    <n v="0.184"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000008.smt2"/>
@@ -3618,6 +4752,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000008.smt2"/>
     <x v="0"/>
     <n v="4.2270660400390597E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000008.smt2"/>
+    <x v="0"/>
+    <n v="0.01"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000009.smt2"/>
@@ -3629,6 +4766,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000009.smt2"/>
     <x v="0"/>
     <n v="4.2980194091796799E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000009.smt2"/>
+    <x v="0"/>
+    <n v="0.18"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000010.smt2"/>
@@ -3640,6 +4780,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000010.smt2"/>
     <x v="0"/>
     <n v="4.241943359375E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000010.smt2"/>
+    <x v="0"/>
+    <n v="0.18099999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000011.smt2"/>
@@ -3651,6 +4794,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000011.smt2"/>
     <x v="0"/>
     <n v="4.29434776306152E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000011.smt2"/>
+    <x v="0"/>
+    <n v="0.32600000000000001"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000012.smt2"/>
@@ -3662,6 +4808,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000012.smt2"/>
     <x v="0"/>
     <n v="4.2688608169555602E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000012.smt2"/>
+    <x v="0"/>
+    <n v="0.47499999999999998"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000013.smt2"/>
@@ -3673,6 +4822,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000013.smt2"/>
     <x v="0"/>
     <n v="4.3863058090209898E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000013.smt2"/>
+    <x v="0"/>
+    <n v="1.2E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000014.smt2"/>
@@ -3684,6 +4836,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000014.smt2"/>
     <x v="0"/>
     <n v="4.3490171432495103E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000014.smt2"/>
+    <x v="0"/>
+    <n v="0.01"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000015.smt2"/>
@@ -3695,6 +4850,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000015.smt2"/>
     <x v="0"/>
     <n v="4.2840003967285101E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000015.smt2"/>
+    <x v="0"/>
+    <n v="1.4E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000016.smt2"/>
@@ -3706,6 +4864,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000016.smt2"/>
     <x v="0"/>
     <n v="4.4537067413330002E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000016.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000017.smt2"/>
@@ -3717,6 +4878,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000017.smt2"/>
     <x v="0"/>
     <n v="4.21948432922363E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000017.smt2"/>
+    <x v="0"/>
+    <n v="8.9999999999999993E-3"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000018.smt2"/>
@@ -3728,6 +4892,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000018.smt2"/>
     <x v="0"/>
     <n v="4.2753458023071199E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000018.smt2"/>
+    <x v="0"/>
+    <n v="0.01"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000019.smt2"/>
@@ -3739,6 +4906,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000019.smt2"/>
     <x v="0"/>
     <n v="4.7303676605224602E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000019.smt2"/>
+    <x v="0"/>
+    <n v="0.185"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000020.smt2"/>
@@ -3750,6 +4920,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000020.smt2"/>
     <x v="0"/>
     <n v="4.15787696838378E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000020.smt2"/>
+    <x v="0"/>
+    <n v="0.33600000000000002"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000021.smt2"/>
@@ -3761,6 +4934,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000021.smt2"/>
     <x v="1"/>
     <n v="1.1081695556640601E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000021.smt2"/>
+    <x v="1"/>
+    <n v="3.6999999999999998E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000022.smt2"/>
@@ -3772,6 +4948,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000022.smt2"/>
     <x v="0"/>
     <n v="4.22806739807128E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000022.smt2"/>
+    <x v="0"/>
+    <n v="0.183"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000023.smt2"/>
@@ -3783,6 +4962,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000023.smt2"/>
     <x v="1"/>
     <n v="1.03745460510253E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000023.smt2"/>
+    <x v="1"/>
+    <n v="1.7000000000000001E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000024.smt2"/>
@@ -3794,6 +4976,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000024.smt2"/>
     <x v="0"/>
     <n v="4.9272060394287102E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000024.smt2"/>
+    <x v="0"/>
+    <n v="0.183"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000025.smt2"/>
@@ -3805,6 +4990,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000025.smt2"/>
     <x v="0"/>
     <n v="1.22833251953125E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000025.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000026.smt2"/>
@@ -3816,6 +5004,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000026.smt2"/>
     <x v="0"/>
     <n v="1.35400295257568E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000026.smt2"/>
+    <x v="0"/>
+    <n v="8.9999999999999993E-3"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000027.smt2"/>
@@ -3827,6 +5018,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000027.smt2"/>
     <x v="0"/>
     <n v="1.2335538864135701E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000027.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000028.smt2"/>
@@ -3838,6 +5032,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000028.smt2"/>
     <x v="2"/>
     <n v="4.6390533447265597E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000028.smt2"/>
+    <x v="1"/>
+    <n v="0.215"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000029.smt2"/>
@@ -3849,6 +5046,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000029.smt2"/>
     <x v="2"/>
     <n v="4.5660257339477497E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000029.smt2"/>
+    <x v="0"/>
+    <n v="0.22"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000030.smt2"/>
@@ -3860,6 +5060,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000030.smt2"/>
     <x v="1"/>
     <n v="1.0617733001708899E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000030.smt2"/>
+    <x v="1"/>
+    <n v="0.02"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000031.smt2"/>
@@ -3871,6 +5074,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000031.smt2"/>
     <x v="0"/>
     <n v="4.3722391128539997E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000031.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000032.smt2"/>
@@ -3882,6 +5088,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000032.smt2"/>
     <x v="1"/>
     <n v="9.7038745880126901E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000032.smt2"/>
+    <x v="1"/>
+    <n v="1.7999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000033.smt2"/>
@@ -3893,6 +5102,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000033.smt2"/>
     <x v="0"/>
     <n v="4.3673753738403299E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000033.smt2"/>
+    <x v="0"/>
+    <n v="0.01"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000034.smt2"/>
@@ -3904,6 +5116,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000034.smt2"/>
     <x v="1"/>
     <n v="9.2990398406982405E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000034.smt2"/>
+    <x v="1"/>
+    <n v="1.7999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000035.smt2"/>
@@ -3915,6 +5130,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000035.smt2"/>
     <x v="0"/>
     <n v="4.8962116241455002E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000035.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000036.smt2"/>
@@ -3926,6 +5144,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000036.smt2"/>
     <x v="0"/>
     <n v="1.2424468994140601E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000036.smt2"/>
+    <x v="0"/>
+    <n v="8.9999999999999993E-3"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000037.smt2"/>
@@ -3937,6 +5158,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000037.smt2"/>
     <x v="0"/>
     <n v="4.4213056564330999E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000037.smt2"/>
+    <x v="0"/>
+    <n v="0.184"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000038.smt2"/>
@@ -3948,6 +5172,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000038.smt2"/>
     <x v="1"/>
     <n v="1.1805772781371999E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000038.smt2"/>
+    <x v="1"/>
+    <n v="2.5999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000039.smt2"/>
@@ -3959,6 +5186,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000039.smt2"/>
     <x v="0"/>
     <n v="4.2194366455078097E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000039.smt2"/>
+    <x v="0"/>
+    <n v="0.49199999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000040.smt2"/>
@@ -3970,6 +5200,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000040.smt2"/>
     <x v="1"/>
     <n v="9.7630023956298793E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000040.smt2"/>
+    <x v="1"/>
+    <n v="3.3000000000000002E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000041.smt2"/>
@@ -3981,6 +5214,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000041.smt2"/>
     <x v="0"/>
     <n v="4.3220043182372998E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000041.smt2"/>
+    <x v="0"/>
+    <n v="0.187"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000042.smt2"/>
@@ -3992,6 +5228,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000042.smt2"/>
     <x v="0"/>
     <n v="1.1343717575073201E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000042.smt2"/>
+    <x v="0"/>
+    <n v="1.0999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000043.smt2"/>
@@ -4003,6 +5242,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000043.smt2"/>
     <x v="2"/>
     <n v="4.6789646148681599E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000043.smt2"/>
+    <x v="0"/>
+    <n v="0.24199999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000044.smt2"/>
@@ -4014,6 +5256,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000044.smt2"/>
     <x v="0"/>
     <n v="4.3131351470947203E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000044.smt2"/>
+    <x v="0"/>
+    <n v="8.9999999999999993E-3"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000045.smt2"/>
@@ -4025,6 +5270,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000045.smt2"/>
     <x v="2"/>
     <n v="5.8704376220703097E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000045.smt2"/>
+    <x v="1"/>
+    <n v="1.63"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000046.smt2"/>
@@ -4036,6 +5284,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000046.smt2"/>
     <x v="2"/>
     <n v="0.116800069808959"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000046.smt2"/>
+    <x v="0"/>
+    <n v="16.096"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000047.smt2"/>
@@ -4047,6 +5298,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000047.smt2"/>
     <x v="2"/>
     <n v="0.12814307212829501"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000047.smt2"/>
+    <x v="1"/>
+    <n v="23.457999999999998"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000048.smt2"/>
@@ -4058,6 +5312,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000048.smt2"/>
     <x v="2"/>
     <n v="8.0286900997161794"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000048.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000049.smt2"/>
@@ -4069,6 +5326,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000049.smt2"/>
     <x v="2"/>
     <n v="7.9743127822875897"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000049.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000050.smt2"/>
@@ -4080,6 +5340,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000050.smt2"/>
     <x v="0"/>
     <n v="2.15697288513183E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000050.smt2"/>
+    <x v="0"/>
+    <n v="0.32500000000000001"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000051.smt2"/>
@@ -4091,6 +5354,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000051.smt2"/>
     <x v="2"/>
     <n v="0.13244318962097101"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000051.smt2"/>
+    <x v="0"/>
+    <n v="15.702999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000052.smt2"/>
@@ -4102,6 +5368,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000052.smt2"/>
     <x v="2"/>
     <n v="0.113091468811035"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000052.smt2"/>
+    <x v="0"/>
+    <n v="15.803000000000001"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000053.smt2"/>
@@ -4113,6 +5382,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000053.smt2"/>
     <x v="2"/>
     <n v="0.11482834815979"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000053.smt2"/>
+    <x v="0"/>
+    <n v="15.404"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000054.smt2"/>
@@ -4124,6 +5396,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000054.smt2"/>
     <x v="2"/>
     <n v="0.113204717636108"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000054.smt2"/>
+    <x v="0"/>
+    <n v="15.613"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000055.smt2"/>
@@ -4135,6 +5410,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000055.smt2"/>
     <x v="1"/>
     <n v="10.3423652648925"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000055.smt2"/>
+    <x v="0"/>
+    <n v="63.076999999999998"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000056.smt2"/>
@@ -4146,6 +5424,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000056.smt2"/>
     <x v="0"/>
     <n v="2.2301673889160101E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000056.smt2"/>
+    <x v="0"/>
+    <n v="1.4999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000057.smt2"/>
@@ -4157,6 +5438,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000057.smt2"/>
     <x v="2"/>
     <n v="6.3155651092529297E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000057.smt2"/>
+    <x v="0"/>
+    <n v="1.696"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000058.smt2"/>
@@ -4168,6 +5452,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000058.smt2"/>
     <x v="2"/>
     <n v="4.9031496047973598E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000058.smt2"/>
+    <x v="1"/>
+    <n v="0.248"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000059.smt2"/>
@@ -4179,6 +5466,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000059.smt2"/>
     <x v="1"/>
     <n v="7.9343318939208898E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000059.smt2"/>
+    <x v="1"/>
+    <n v="1.4E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000060.smt2"/>
@@ -4190,6 +5480,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000060.smt2"/>
     <x v="2"/>
     <n v="7.5896024703979395E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000060.smt2"/>
+    <x v="1"/>
+    <n v="1.64"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000061.smt2"/>
@@ -4201,6 +5494,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000061.smt2"/>
     <x v="2"/>
     <n v="6.6768407821655204E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000061.smt2"/>
+    <x v="1"/>
+    <n v="1.6819999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000062.smt2"/>
@@ -4212,6 +5508,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000062.smt2"/>
     <x v="2"/>
     <n v="6.4674854278564398E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000062.smt2"/>
+    <x v="0"/>
+    <n v="1.76"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000063.smt2"/>
@@ -4223,6 +5522,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000063.smt2"/>
     <x v="2"/>
     <n v="0.140614509582519"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000063.smt2"/>
+    <x v="1"/>
+    <n v="0.224"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000064.smt2"/>
@@ -4234,6 +5536,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000064.smt2"/>
     <x v="1"/>
     <n v="9.9568367004394497E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000064.smt2"/>
+    <x v="1"/>
+    <n v="1.4999999999999999E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000065.smt2"/>
@@ -4245,6 +5550,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000065.smt2"/>
     <x v="2"/>
     <n v="6.7728042602538993E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000065.smt2"/>
+    <x v="1"/>
+    <n v="1.728"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000066.smt2"/>
@@ -4256,6 +5564,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000066.smt2"/>
     <x v="2"/>
     <n v="7.1146249771118095E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000066.smt2"/>
+    <x v="1"/>
+    <n v="1.7050000000000001"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000067.smt2"/>
@@ -4267,6 +5578,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000067.smt2"/>
     <x v="2"/>
     <n v="6.0230970382690402E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000067.smt2"/>
+    <x v="1"/>
+    <n v="3.915"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000068.smt2"/>
@@ -4278,6 +5592,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000068.smt2"/>
     <x v="2"/>
     <n v="6.1934709548950098E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000068.smt2"/>
+    <x v="1"/>
+    <n v="3.83"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000069.smt2"/>
@@ -4289,6 +5606,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000069.smt2"/>
     <x v="2"/>
     <n v="0.116948127746582"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000069.smt2"/>
+    <x v="0"/>
+    <n v="16.097999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000070.smt2"/>
@@ -4300,6 +5620,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000070.smt2"/>
     <x v="2"/>
     <n v="0.119216680526733"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000070.smt2"/>
+    <x v="1"/>
+    <n v="15.481"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000071.smt2"/>
@@ -4311,6 +5634,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000071.smt2"/>
     <x v="2"/>
     <n v="8.1073417663574201"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000071.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000072.smt2"/>
@@ -4322,6 +5648,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000072.smt2"/>
     <x v="2"/>
     <n v="8.0363807678222603"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000072.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000073.smt2"/>
@@ -4333,6 +5662,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000073.smt2"/>
     <x v="0"/>
     <n v="2.2228240966796799E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000073.smt2"/>
+    <x v="0"/>
+    <n v="0.128"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000074.smt2"/>
@@ -4344,6 +5676,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000074.smt2"/>
     <x v="2"/>
     <n v="0.113598823547363"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000074.smt2"/>
+    <x v="0"/>
+    <n v="15.534000000000001"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000075.smt2"/>
@@ -4355,6 +5690,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000075.smt2"/>
     <x v="2"/>
     <n v="0.116568088531494"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000075.smt2"/>
+    <x v="0"/>
+    <n v="15.747999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000076.smt2"/>
@@ -4366,6 +5704,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000076.smt2"/>
     <x v="2"/>
     <n v="0.11711072921752901"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000076.smt2"/>
+    <x v="0"/>
+    <n v="60.073999999999998"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000077.smt2"/>
@@ -4377,6 +5718,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000077.smt2"/>
     <x v="2"/>
     <n v="0.116960048675537"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000077.smt2"/>
+    <x v="0"/>
+    <n v="15.144"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000078.smt2"/>
@@ -4388,6 +5732,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000078.smt2"/>
     <x v="1"/>
     <n v="10.3725688457489"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000078.smt2"/>
+    <x v="0"/>
+    <n v="67.650999999999996"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000079.smt2"/>
@@ -4399,6 +5746,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000079.smt2"/>
     <x v="0"/>
     <n v="2.2059679031372001E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000079.smt2"/>
+    <x v="0"/>
+    <n v="1.6E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000080.smt2"/>
@@ -4410,6 +5760,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000080.smt2"/>
     <x v="0"/>
     <n v="0.75850510597229004"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000080.smt2"/>
+    <x v="0"/>
+    <n v="9.3689999999999998"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000081.smt2"/>
@@ -4421,6 +5774,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000081.smt2"/>
     <x v="1"/>
     <n v="8.6221694946288993E-3"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000081.smt2"/>
+    <x v="1"/>
+    <n v="1.6E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000082.smt2"/>
@@ -4432,6 +5788,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000082.smt2"/>
     <x v="0"/>
     <n v="1.3046307563781701"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000082.smt2"/>
+    <x v="0"/>
+    <n v="9.0129999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000083.smt2"/>
@@ -4443,6 +5802,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000083.smt2"/>
     <x v="1"/>
     <n v="0.75070405006408603"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000083.smt2"/>
+    <x v="1"/>
+    <n v="9.2249999999999996"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000084.smt2"/>
@@ -4454,6 +5816,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000084.smt2"/>
     <x v="2"/>
     <n v="0.122172594070434"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000084.smt2"/>
+    <x v="0"/>
+    <n v="15.917"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000085.smt2"/>
@@ -4465,6 +5830,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000085.smt2"/>
     <x v="2"/>
     <n v="6.2417268753051702E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000085.smt2"/>
+    <x v="1"/>
+    <n v="2.0960000000000001"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000086.smt2"/>
@@ -4476,6 +5844,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000086.smt2"/>
     <x v="2"/>
     <n v="5.80039024353027E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000086.smt2"/>
+    <x v="1"/>
+    <n v="1.6639999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000087.smt2"/>
@@ -4487,6 +5858,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000087.smt2"/>
     <x v="1"/>
     <n v="0.74081039428710904"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000087.smt2"/>
+    <x v="1"/>
+    <n v="21.257000000000001"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000088.smt2"/>
@@ -4498,6 +5872,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000088.smt2"/>
     <x v="2"/>
     <n v="0.11642408370971601"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000088.smt2"/>
+    <x v="1"/>
+    <n v="31.742999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000089.smt2"/>
@@ -4509,6 +5886,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000089.smt2"/>
     <x v="2"/>
     <n v="0.119226694107055"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000089.smt2"/>
+    <x v="1"/>
+    <n v="18.033999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000090.smt2"/>
@@ -4520,6 +5900,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000090.smt2"/>
     <x v="0"/>
     <n v="0.77145075798034601"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000090.smt2"/>
+    <x v="0"/>
+    <n v="9.3960000000000008"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000091.smt2"/>
@@ -4531,6 +5914,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000091.smt2"/>
     <x v="1"/>
     <n v="1.2113094329833899E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000091.smt2"/>
+    <x v="1"/>
+    <n v="0.02"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000092.smt2"/>
@@ -4542,6 +5928,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000092.smt2"/>
     <x v="1"/>
     <n v="0.736497402191162"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000092.smt2"/>
+    <x v="1"/>
+    <n v="8.9459999999999997"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000093.smt2"/>
@@ -4553,6 +5942,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000093.smt2"/>
     <x v="1"/>
     <n v="0.73891758918762196"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000093.smt2"/>
+    <x v="1"/>
+    <n v="11.537000000000001"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000094.smt2"/>
@@ -4564,6 +5956,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000094.smt2"/>
     <x v="2"/>
     <n v="6.00049495697021E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000094.smt2"/>
+    <x v="1"/>
+    <n v="1.708"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000095.smt2"/>
@@ -4575,6 +5970,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000095.smt2"/>
     <x v="2"/>
     <n v="0.13203740119933999"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000095.smt2"/>
+    <x v="1"/>
+    <n v="15.978999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000096.smt2"/>
@@ -4586,6 +5984,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000096.smt2"/>
     <x v="2"/>
     <n v="8.0429515838622994"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000096.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000097.smt2"/>
@@ -4597,6 +5998,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000097.smt2"/>
     <x v="2"/>
     <n v="7.9874482154846103"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000097.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000098.smt2"/>
@@ -4608,6 +6012,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000098.smt2"/>
     <x v="2"/>
     <n v="100.045338630676"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000098.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000099.smt2"/>
@@ -4619,6 +6026,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000099.smt2"/>
     <x v="2"/>
     <n v="100.057497739791"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000099.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000100.smt2"/>
@@ -4630,6 +6040,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000100.smt2"/>
     <x v="2"/>
     <n v="100.041392326354"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000100.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000101.smt2"/>
@@ -4641,6 +6054,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000101.smt2"/>
     <x v="0"/>
     <n v="2.8535127639770501E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000101.smt2"/>
+    <x v="0"/>
+    <n v="0.33400000000000002"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000102.smt2"/>
@@ -4652,6 +6068,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000102.smt2"/>
     <x v="2"/>
     <n v="100.053363323211"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000102.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000103.smt2"/>
@@ -4663,6 +6082,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000103.smt2"/>
     <x v="2"/>
     <n v="100.045784235"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000103.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000104.smt2"/>
@@ -4674,6 +6096,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000104.smt2"/>
     <x v="2"/>
     <n v="100.048868894577"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000104.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000105.smt2"/>
@@ -4685,6 +6110,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000105.smt2"/>
     <x v="2"/>
     <n v="100.044727563858"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000105.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000106.smt2"/>
@@ -4696,6 +6124,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000106.smt2"/>
     <x v="2"/>
     <n v="100.039130210876"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000106.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000107.smt2"/>
@@ -4707,6 +6138,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000107.smt2"/>
     <x v="2"/>
     <n v="100.04731726646401"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000107.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000108.smt2"/>
@@ -4718,6 +6152,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000108.smt2"/>
     <x v="0"/>
     <n v="2.94163227081298E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000108.smt2"/>
+    <x v="0"/>
+    <n v="8.6999999999999994E-2"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000109.smt2"/>
@@ -4729,6 +6166,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000109.smt2"/>
     <x v="2"/>
     <n v="0.119300603866577"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000109.smt2"/>
+    <x v="0"/>
+    <n v="58.322000000000003"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000110.smt2"/>
@@ -4740,6 +6180,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000110.smt2"/>
     <x v="2"/>
     <n v="6.1893463134765597E-2"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000110.smt2"/>
+    <x v="1"/>
+    <n v="1.742"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000111.smt2"/>
@@ -4751,6 +6194,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000111.smt2"/>
     <x v="1"/>
     <n v="0.72359490394592196"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000111.smt2"/>
+    <x v="1"/>
+    <n v="9.4939999999999998"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000112.smt2"/>
@@ -4762,6 +6208,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000112.smt2"/>
     <x v="2"/>
     <n v="0.11482429504394499"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000112.smt2"/>
+    <x v="1"/>
+    <n v="15.724"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000113.smt2"/>
@@ -4773,6 +6222,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000113.smt2"/>
     <x v="0"/>
     <n v="11.814095258712699"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000113.smt2"/>
+    <x v="0"/>
+    <n v="83.8"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000114.smt2"/>
@@ -4784,6 +6236,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000114.smt2"/>
     <x v="1"/>
     <n v="0.71333432197570801"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000114.smt2"/>
+    <x v="1"/>
+    <n v="22.172999999999998"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000115.smt2"/>
@@ -4795,6 +6250,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000115.smt2"/>
     <x v="1"/>
     <n v="0.72495794296264604"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000115.smt2"/>
+    <x v="1"/>
+    <n v="21.673999999999999"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000116.smt2"/>
@@ -4806,6 +6264,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000116.smt2"/>
     <x v="1"/>
     <n v="10.506611585617"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000116.smt2"/>
+    <x v="0"/>
+    <n v="49.466000000000001"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000117.smt2"/>
@@ -4817,6 +6278,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000117.smt2"/>
     <x v="0"/>
     <n v="11.802000522613501"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000117.smt2"/>
+    <x v="0"/>
+    <n v="55.52"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000118.smt2"/>
@@ -4828,6 +6292,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000118.smt2"/>
     <x v="2"/>
     <n v="7.9867048263549796"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000118.smt2"/>
+    <x v="2"/>
+    <n v="100"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000119.smt2"/>
@@ -4839,6 +6306,9 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000119.smt2"/>
     <x v="2"/>
     <n v="0.115933895111083"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000119.smt2"/>
+    <x v="1"/>
+    <n v="16.396000000000001"/>
   </r>
   <r>
     <s v="bapa/card/fol_0000120.smt2"/>
@@ -4850,34 +6320,20 @@
     <s v="benchmarks/bapa/card/cvc5_bapa/fol_0000120.smt2"/>
     <x v="1"/>
     <n v="10.4824538230896"/>
+    <s v="/home/mudathir/all/sls-reachability/benchmarks/bapa/card/cvc5_bapa/fol_0000120.smt2"/>
+    <x v="0"/>
+    <n v="61.933999999999997"/>
   </r>
 </pivotCacheRecords>
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7D55DB8C-C0D9-48E6-9B9F-FBA125C11914}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls" colHeaderCaption="cvc5 lia normaliz">
-  <location ref="A12:E17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C38C6786-35D4-430E-AA4F-5A1E6BB67DCD}" name="PivotTable3" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls" colHeaderCaption="cvc5 lia">
+  <location ref="G3:K8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
     <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField axis="axisCol" showAll="0">
       <items count="4">
@@ -4888,9 +6344,22 @@
       </items>
     </pivotField>
     <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
   </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="10"/>
   </rowFields>
   <rowItems count="4">
     <i>
@@ -4907,7 +6376,7 @@
     </i>
   </rowItems>
   <colFields count="1">
-    <field x="7"/>
+    <field x="4"/>
   </colFields>
   <colItems count="4">
     <i>
@@ -4939,9 +6408,9 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4778405-FE92-45D5-9093-FA0E28569C7B}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls" colHeaderCaption="cvc5 lia">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D4778405-FE92-45D5-9093-FA0E28569C7B}" name="PivotTable1" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls" colHeaderCaption="cvc5 lia">
   <location ref="A3:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
+  <pivotFields count="12">
     <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="4">
@@ -4961,6 +6430,9 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
     <pivotField showAll="0"/>
@@ -5015,10 +6487,111 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7D55DB8C-C0D9-48E6-9B9F-FBA125C11914}" name="PivotTable2" cacheId="20" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls" colHeaderCaption="cvc5 lia normaliz">
+  <location ref="A12:E17" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="12">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="7"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E729566-643F-4C03-A5FC-1C062252F9B9}" name="Table1" displayName="Table1" ref="A1:I241" totalsRowShown="0">
-  <autoFilter ref="A1:I241" xr:uid="{1E729566-643F-4C03-A5FC-1C062252F9B9}"/>
-  <tableColumns count="9">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{712121DC-2227-47D7-8AD0-DD0D844A8D5D}" name="Table2" displayName="Table2" ref="A3:L7" totalsRowShown="0">
+  <autoFilter ref="A3:L7" xr:uid="{712121DC-2227-47D7-8AD0-DD0D844A8D5D}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{DF3DADE7-85D2-4D8F-9514-A05BCD590E67}" name="sls file"/>
+    <tableColumn id="2" xr3:uid="{682B3F0F-163C-47C4-ACB2-5F6EC33B0F85}" name="sls result"/>
+    <tableColumn id="3" xr3:uid="{8A078B57-A553-4B0F-96BA-57E6987CBB1A}" name="sls duration"/>
+    <tableColumn id="4" xr3:uid="{2CC7569B-EAD2-4B98-A3E3-483B685115D1}" name="cvc5 lia filename"/>
+    <tableColumn id="5" xr3:uid="{2313994D-5085-4AB6-B7CA-7863694A3245}" name="cvc5 lia result"/>
+    <tableColumn id="6" xr3:uid="{16521941-D04F-48AC-A66B-736D313BCD68}" name="cvc5 lia duration"/>
+    <tableColumn id="7" xr3:uid="{095ACE9E-F22C-4E0C-ABA4-2F572F45FBB7}" name="lia normaliz filename"/>
+    <tableColumn id="8" xr3:uid="{00EF8A30-9369-4FF3-B64E-C890B98A79BD}" name="lia normaliz result"/>
+    <tableColumn id="9" xr3:uid="{EED5C26A-8F5C-456D-A4D4-62CEF6BA5F68}" name="lia normaliz duration"/>
+    <tableColumn id="10" xr3:uid="{EA09C9F5-034C-4DFD-9FA6-C40DED8E92B2}" name="sqlsolver filename"/>
+    <tableColumn id="11" xr3:uid="{0BDB98C9-135A-414D-981C-6A3F988FFA4A}" name="sqlsolver result"/>
+    <tableColumn id="12" xr3:uid="{A656FC6C-ABB7-4480-8E41-98EC4D520644}" name="sqlsolver duration"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E729566-643F-4C03-A5FC-1C062252F9B9}" name="Table1" displayName="Table1" ref="A1:L241" totalsRowShown="0">
+  <autoFilter ref="A1:L241" xr:uid="{1E729566-643F-4C03-A5FC-1C062252F9B9}"/>
+  <tableColumns count="12">
     <tableColumn id="1" xr3:uid="{E3805889-3FE1-402D-BB6D-F7B17E3DEA31}" name="sls file"/>
     <tableColumn id="2" xr3:uid="{90A6288E-50A4-4863-AF83-0088DD98FE4D}" name="sls result"/>
     <tableColumn id="3" xr3:uid="{A267AAC5-40E4-4F1B-86EC-9C8AA546ADF6}" name="sls duration"/>
@@ -5028,6 +6601,9 @@
     <tableColumn id="7" xr3:uid="{EC93C786-0848-4FCD-8041-AFBB16DD425B}" name="lia normaliz filename"/>
     <tableColumn id="8" xr3:uid="{C1192E6F-5378-47BD-878E-BE1FBFF24DF0}" name="lia normaliz result"/>
     <tableColumn id="9" xr3:uid="{0F440ABC-08B3-464F-9622-2B4B82B9535E}" name="lia normaliz duration"/>
+    <tableColumn id="10" xr3:uid="{0348EA82-0DDF-42A8-BA05-B64EBCF86BD5}" name="sqlsolver filename"/>
+    <tableColumn id="11" xr3:uid="{0403120A-2E85-4A9A-B144-96388619EF2D}" name="sqlsolver result"/>
+    <tableColumn id="12" xr3:uid="{6EA5388B-D877-4D92-9692-FDE4008B05D5}" name="sqlsolver duration"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -5349,8 +6925,231 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C30B8097-7BCC-4ED3-938A-29A9AD4E50FD}">
+  <dimension ref="A1:L7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="24.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="44.81640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.08984375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="74.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="18.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" t="s">
+        <v>249</v>
+      </c>
+      <c r="H3" t="s">
+        <v>250</v>
+      </c>
+      <c r="I3" t="s">
+        <v>251</v>
+      </c>
+      <c r="J3" t="s">
+        <v>499</v>
+      </c>
+      <c r="K3" t="s">
+        <v>500</v>
+      </c>
+      <c r="L3" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>491</v>
+      </c>
+      <c r="B4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C4">
+        <v>100.104124069213</v>
+      </c>
+      <c r="D4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4">
+        <v>9.2373118400573695</v>
+      </c>
+      <c r="G4" t="s">
+        <v>248</v>
+      </c>
+      <c r="H4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4">
+        <v>10.4824538230896</v>
+      </c>
+      <c r="J4" t="s">
+        <v>741</v>
+      </c>
+      <c r="K4" t="s">
+        <v>497</v>
+      </c>
+      <c r="L4">
+        <v>61.933999999999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>487</v>
+      </c>
+      <c r="B5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C5">
+        <v>100.104396343231</v>
+      </c>
+      <c r="D5" t="s">
+        <v>244</v>
+      </c>
+      <c r="E5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5">
+        <v>9.27725958824157</v>
+      </c>
+      <c r="G5" t="s">
+        <v>244</v>
+      </c>
+      <c r="H5" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5">
+        <v>10.506611585617</v>
+      </c>
+      <c r="J5" t="s">
+        <v>737</v>
+      </c>
+      <c r="K5" t="s">
+        <v>497</v>
+      </c>
+      <c r="L5">
+        <v>49.466000000000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>449</v>
+      </c>
+      <c r="B6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6">
+        <v>100.017288923263</v>
+      </c>
+      <c r="D6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F6">
+        <v>9.2319128513336093</v>
+      </c>
+      <c r="G6" t="s">
+        <v>206</v>
+      </c>
+      <c r="H6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6">
+        <v>10.3725688457489</v>
+      </c>
+      <c r="J6" t="s">
+        <v>699</v>
+      </c>
+      <c r="K6" t="s">
+        <v>497</v>
+      </c>
+      <c r="L6">
+        <v>67.650999999999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>426</v>
+      </c>
+      <c r="B7" t="s">
+        <v>173</v>
+      </c>
+      <c r="C7">
+        <v>100.104610681533</v>
+      </c>
+      <c r="D7" t="s">
+        <v>183</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7">
+        <v>9.2768096923828107</v>
+      </c>
+      <c r="G7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H7" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7">
+        <v>10.3423652648925</v>
+      </c>
+      <c r="J7" t="s">
+        <v>676</v>
+      </c>
+      <c r="K7" t="s">
+        <v>497</v>
+      </c>
+      <c r="L7">
+        <v>63.076999999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C7BCC34-B16B-45C0-B141-FAD55AFF40F3}">
-  <dimension ref="A3:E17"/>
+  <dimension ref="A3:K17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.26953125" bestFit="1" customWidth="1"/>
@@ -5359,21 +7158,28 @@
     <col min="4" max="4" width="5.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.54296875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="7.36328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="13" t="s">
         <v>493</v>
       </c>
       <c r="B3" s="13" t="s">
         <v>495</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G3" s="13" t="s">
+        <v>493</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>494</v>
       </c>
@@ -5389,8 +7195,23 @@
       <c r="E4" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G4" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="H4" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" t="s">
+        <v>173</v>
+      </c>
+      <c r="J4" t="s">
+        <v>27</v>
+      </c>
+      <c r="K4" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
@@ -5402,8 +7223,21 @@
       <c r="E5" s="15">
         <v>116</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G5" s="14" t="s">
+        <v>497</v>
+      </c>
+      <c r="H5" s="15">
+        <v>135</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15">
+        <v>4</v>
+      </c>
+      <c r="K5" s="15">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="14" t="s">
         <v>173</v>
       </c>
@@ -5419,8 +7253,19 @@
       <c r="E6" s="15">
         <v>51</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G6" s="14" t="s">
+        <v>173</v>
+      </c>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15">
+        <v>16</v>
+      </c>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>27</v>
       </c>
@@ -5432,8 +7277,19 @@
       <c r="E7" s="15">
         <v>73</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G7" s="14" t="s">
+        <v>498</v>
+      </c>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15">
+        <v>85</v>
+      </c>
+      <c r="K7" s="15">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="14" t="s">
         <v>492</v>
       </c>
@@ -5449,8 +7305,23 @@
       <c r="E8" s="15">
         <v>240</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G8" s="14" t="s">
+        <v>492</v>
+      </c>
+      <c r="H8" s="15">
+        <v>135</v>
+      </c>
+      <c r="I8" s="15">
+        <v>16</v>
+      </c>
+      <c r="J8" s="15">
+        <v>89</v>
+      </c>
+      <c r="K8" s="15">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
         <v>493</v>
       </c>
@@ -5458,7 +7329,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="13" t="s">
         <v>494</v>
       </c>
@@ -5475,7 +7346,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="14" t="s">
         <v>6</v>
       </c>
@@ -5490,7 +7361,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>173</v>
       </c>
@@ -5507,7 +7378,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="14" t="s">
         <v>27</v>
       </c>
@@ -5544,9 +7415,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEEC5DD9-14C3-4C18-9355-6C6BFA91C6D6}">
-  <dimension ref="A1:I241"/>
+  <dimension ref="A1:L241"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.54296875" bestFit="1" customWidth="1"/>
@@ -5558,9 +7429,11 @@
     <col min="7" max="7" width="44.90625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="17.7265625" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
+    <col min="10" max="10" width="75.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -5588,8 +7461,17 @@
       <c r="I1" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J1" t="s">
+        <v>499</v>
+      </c>
+      <c r="K1" t="s">
+        <v>500</v>
+      </c>
+      <c r="L1" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="10" t="s">
         <v>252</v>
       </c>
@@ -5617,8 +7499,17 @@
       <c r="I2">
         <v>0.101495265960693</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J2" t="s">
+        <v>502</v>
+      </c>
+      <c r="K2" t="s">
+        <v>497</v>
+      </c>
+      <c r="L2">
+        <v>0.20499999999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
         <v>253</v>
       </c>
@@ -5646,8 +7537,17 @@
       <c r="I3">
         <v>1.44908428192138E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J3" t="s">
+        <v>503</v>
+      </c>
+      <c r="K3" t="s">
+        <v>497</v>
+      </c>
+      <c r="L3">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="10" t="s">
         <v>254</v>
       </c>
@@ -5675,8 +7575,17 @@
       <c r="I4">
         <v>2.0340681076049801E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J4" t="s">
+        <v>504</v>
+      </c>
+      <c r="K4" t="s">
+        <v>497</v>
+      </c>
+      <c r="L4">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
         <v>255</v>
       </c>
@@ -5704,8 +7613,17 @@
       <c r="I5">
         <v>8.1681728363037095E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5" t="s">
+        <v>505</v>
+      </c>
+      <c r="K5" t="s">
+        <v>497</v>
+      </c>
+      <c r="L5">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="10" t="s">
         <v>256</v>
       </c>
@@ -5733,8 +7651,17 @@
       <c r="I6">
         <v>4.7867774963378899E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6" t="s">
+        <v>506</v>
+      </c>
+      <c r="K6" t="s">
+        <v>497</v>
+      </c>
+      <c r="L6">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
         <v>257</v>
       </c>
@@ -5762,8 +7689,17 @@
       <c r="I7">
         <v>5.0418615341186503E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7" t="s">
+        <v>507</v>
+      </c>
+      <c r="K7" t="s">
+        <v>497</v>
+      </c>
+      <c r="L7">
+        <v>1.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="10" t="s">
         <v>258</v>
       </c>
@@ -5791,8 +7727,17 @@
       <c r="I8">
         <v>4.5779228210449198E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8" t="s">
+        <v>508</v>
+      </c>
+      <c r="K8" t="s">
+        <v>497</v>
+      </c>
+      <c r="L8">
+        <v>0.28000000000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
         <v>259</v>
       </c>
@@ -5820,8 +7765,17 @@
       <c r="I9">
         <v>4.58817481994628E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J9" t="s">
+        <v>509</v>
+      </c>
+      <c r="K9" t="s">
+        <v>497</v>
+      </c>
+      <c r="L9">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="10" t="s">
         <v>260</v>
       </c>
@@ -5849,8 +7803,17 @@
       <c r="I10">
         <v>4.4304609298705999E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J10" t="s">
+        <v>510</v>
+      </c>
+      <c r="K10" t="s">
+        <v>497</v>
+      </c>
+      <c r="L10">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
         <v>261</v>
       </c>
@@ -5878,8 +7841,17 @@
       <c r="I11">
         <v>4.4718265533447203E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J11" t="s">
+        <v>511</v>
+      </c>
+      <c r="K11" t="s">
+        <v>497</v>
+      </c>
+      <c r="L11">
+        <v>0.20399999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="10" t="s">
         <v>262</v>
       </c>
@@ -5907,8 +7879,17 @@
       <c r="I12">
         <v>4.4330596923828097E-2</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J12" t="s">
+        <v>512</v>
+      </c>
+      <c r="K12" t="s">
+        <v>497</v>
+      </c>
+      <c r="L12">
+        <v>0.21099999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
         <v>263</v>
       </c>
@@ -5936,8 +7917,17 @@
       <c r="I13">
         <v>4.4733524322509703E-2</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J13" t="s">
+        <v>513</v>
+      </c>
+      <c r="K13" t="s">
+        <v>497</v>
+      </c>
+      <c r="L13">
+        <v>0.192</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="10" t="s">
         <v>264</v>
       </c>
@@ -5965,8 +7955,17 @@
       <c r="I14">
         <v>4.4816970825195299E-2</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J14" t="s">
+        <v>514</v>
+      </c>
+      <c r="K14" t="s">
+        <v>497</v>
+      </c>
+      <c r="L14">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
         <v>265</v>
       </c>
@@ -5994,8 +7993,17 @@
       <c r="I15">
         <v>4.4156074523925698E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J15" t="s">
+        <v>515</v>
+      </c>
+      <c r="K15" t="s">
+        <v>497</v>
+      </c>
+      <c r="L15">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
         <v>266</v>
       </c>
@@ -6023,8 +8031,17 @@
       <c r="I16">
         <v>4.3086290359497001E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J16" t="s">
+        <v>516</v>
+      </c>
+      <c r="K16" t="s">
+        <v>497</v>
+      </c>
+      <c r="L16">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
         <v>267</v>
       </c>
@@ -6052,8 +8069,17 @@
       <c r="I17">
         <v>4.6988010406494099E-2</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J17" t="s">
+        <v>517</v>
+      </c>
+      <c r="K17" t="s">
+        <v>497</v>
+      </c>
+      <c r="L17">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="10" t="s">
         <v>268</v>
       </c>
@@ -6081,8 +8107,17 @@
       <c r="I18">
         <v>4.3082714080810498E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J18" t="s">
+        <v>518</v>
+      </c>
+      <c r="K18" t="s">
+        <v>497</v>
+      </c>
+      <c r="L18">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
         <v>269</v>
       </c>
@@ -6110,8 +8145,17 @@
       <c r="I19">
         <v>4.4025659561157199E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J19" t="s">
+        <v>519</v>
+      </c>
+      <c r="K19" t="s">
+        <v>497</v>
+      </c>
+      <c r="L19">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="10" t="s">
         <v>270</v>
       </c>
@@ -6139,8 +8183,17 @@
       <c r="I20">
         <v>4.9208641052245997E-2</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J20" t="s">
+        <v>520</v>
+      </c>
+      <c r="K20" t="s">
+        <v>497</v>
+      </c>
+      <c r="L20">
+        <v>0.215</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
         <v>271</v>
       </c>
@@ -6168,8 +8221,17 @@
       <c r="I21">
         <v>4.9638271331787102E-2</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J21" t="s">
+        <v>521</v>
+      </c>
+      <c r="K21" t="s">
+        <v>497</v>
+      </c>
+      <c r="L21">
+        <v>0.20200000000000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22" s="10" t="s">
         <v>272</v>
       </c>
@@ -6197,8 +8259,17 @@
       <c r="I22">
         <v>1.1879682540893499E-2</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J22" t="s">
+        <v>522</v>
+      </c>
+      <c r="K22" t="s">
+        <v>498</v>
+      </c>
+      <c r="L22">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
         <v>273</v>
       </c>
@@ -6226,8 +8297,17 @@
       <c r="I23">
         <v>4.5344114303588798E-2</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J23" t="s">
+        <v>523</v>
+      </c>
+      <c r="K23" t="s">
+        <v>497</v>
+      </c>
+      <c r="L23">
+        <v>0.20100000000000001</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24" s="10" t="s">
         <v>274</v>
       </c>
@@ -6255,8 +8335,17 @@
       <c r="I24">
         <v>1.0849714279174799E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J24" t="s">
+        <v>524</v>
+      </c>
+      <c r="K24" t="s">
+        <v>498</v>
+      </c>
+      <c r="L24">
+        <v>2.4E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
         <v>275</v>
       </c>
@@ -6284,8 +8373,17 @@
       <c r="I25">
         <v>4.9724578857421799E-2</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J25" t="s">
+        <v>525</v>
+      </c>
+      <c r="K25" t="s">
+        <v>497</v>
+      </c>
+      <c r="L25">
+        <v>0.19900000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
         <v>276</v>
       </c>
@@ -6313,8 +8411,17 @@
       <c r="I26">
         <v>1.3100862503051701E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J26" t="s">
+        <v>526</v>
+      </c>
+      <c r="K26" t="s">
+        <v>497</v>
+      </c>
+      <c r="L26">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
         <v>277</v>
       </c>
@@ -6342,8 +8449,17 @@
       <c r="I27">
         <v>1.2727499008178701E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J27" t="s">
+        <v>527</v>
+      </c>
+      <c r="K27" t="s">
+        <v>497</v>
+      </c>
+      <c r="L27">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28" s="10" t="s">
         <v>278</v>
       </c>
@@ -6371,8 +8487,17 @@
       <c r="I28">
         <v>1.29928588867187E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J28" t="s">
+        <v>528</v>
+      </c>
+      <c r="K28" t="s">
+        <v>497</v>
+      </c>
+      <c r="L28">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
         <v>279</v>
       </c>
@@ -6400,8 +8525,17 @@
       <c r="I29">
         <v>6.2685966491699205E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J29" t="s">
+        <v>529</v>
+      </c>
+      <c r="K29" t="s">
+        <v>498</v>
+      </c>
+      <c r="L29">
+        <v>0.22900000000000001</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30" s="10" t="s">
         <v>280</v>
       </c>
@@ -6429,8 +8563,17 @@
       <c r="I30">
         <v>0.122227668762207</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J30" t="s">
+        <v>530</v>
+      </c>
+      <c r="K30" t="s">
+        <v>497</v>
+      </c>
+      <c r="L30">
+        <v>0.22600000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
         <v>281</v>
       </c>
@@ -6458,8 +8601,17 @@
       <c r="I31">
         <v>1.16009712219238E-2</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J31" t="s">
+        <v>531</v>
+      </c>
+      <c r="K31" t="s">
+        <v>498</v>
+      </c>
+      <c r="L31">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32" s="10" t="s">
         <v>282</v>
       </c>
@@ -6487,8 +8639,17 @@
       <c r="I32">
         <v>4.8797607421875E-2</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J32" t="s">
+        <v>532</v>
+      </c>
+      <c r="K32" t="s">
+        <v>497</v>
+      </c>
+      <c r="L32">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
         <v>283</v>
       </c>
@@ -6516,8 +8677,17 @@
       <c r="I33">
         <v>9.9892616271972604E-3</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J33" t="s">
+        <v>533</v>
+      </c>
+      <c r="K33" t="s">
+        <v>498</v>
+      </c>
+      <c r="L33">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34" s="10" t="s">
         <v>284</v>
       </c>
@@ -6545,8 +8715,17 @@
       <c r="I34">
         <v>4.4088840484619099E-2</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J34" t="s">
+        <v>534</v>
+      </c>
+      <c r="K34" t="s">
+        <v>497</v>
+      </c>
+      <c r="L34">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
         <v>285</v>
       </c>
@@ -6574,8 +8753,17 @@
       <c r="I35">
         <v>9.7904205322265608E-3</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J35" t="s">
+        <v>535</v>
+      </c>
+      <c r="K35" t="s">
+        <v>498</v>
+      </c>
+      <c r="L35">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36" s="10" t="s">
         <v>286</v>
       </c>
@@ -6603,8 +8791,17 @@
       <c r="I36">
         <v>4.8144340515136698E-2</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J36" t="s">
+        <v>536</v>
+      </c>
+      <c r="K36" t="s">
+        <v>497</v>
+      </c>
+      <c r="L36">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
         <v>287</v>
       </c>
@@ -6632,8 +8829,17 @@
       <c r="I37">
         <v>1.2047529220580999E-2</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J37" t="s">
+        <v>537</v>
+      </c>
+      <c r="K37" t="s">
+        <v>497</v>
+      </c>
+      <c r="L37">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38" s="10" t="s">
         <v>288</v>
       </c>
@@ -6661,8 +8867,17 @@
       <c r="I38">
         <v>4.31671142578125E-2</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J38" t="s">
+        <v>538</v>
+      </c>
+      <c r="K38" t="s">
+        <v>497</v>
+      </c>
+      <c r="L38">
+        <v>0.189</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
         <v>289</v>
       </c>
@@ -6690,8 +8905,17 @@
       <c r="I39">
         <v>9.9687576293945295E-3</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J39" t="s">
+        <v>539</v>
+      </c>
+      <c r="K39" t="s">
+        <v>498</v>
+      </c>
+      <c r="L39">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40" s="10" t="s">
         <v>290</v>
       </c>
@@ -6719,8 +8943,17 @@
       <c r="I40">
         <v>4.4043779373168897E-2</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J40" t="s">
+        <v>540</v>
+      </c>
+      <c r="K40" t="s">
+        <v>497</v>
+      </c>
+      <c r="L40">
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
         <v>291</v>
       </c>
@@ -6748,8 +8981,17 @@
       <c r="I41">
         <v>9.9987983703613195E-3</v>
       </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J41" t="s">
+        <v>541</v>
+      </c>
+      <c r="K41" t="s">
+        <v>498</v>
+      </c>
+      <c r="L41">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42" s="10" t="s">
         <v>292</v>
       </c>
@@ -6777,8 +9019,17 @@
       <c r="I42">
         <v>4.6099662780761698E-2</v>
       </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J42" t="s">
+        <v>542</v>
+      </c>
+      <c r="K42" t="s">
+        <v>497</v>
+      </c>
+      <c r="L42">
+        <v>0.191</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
         <v>293</v>
       </c>
@@ -6806,8 +9057,17 @@
       <c r="I43">
         <v>1.2178897857666E-2</v>
       </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J43" t="s">
+        <v>543</v>
+      </c>
+      <c r="K43" t="s">
+        <v>497</v>
+      </c>
+      <c r="L43">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44" s="10" t="s">
         <v>294</v>
       </c>
@@ -6835,8 +9095,17 @@
       <c r="I44">
         <v>4.4809579849243102E-2</v>
       </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J44" t="s">
+        <v>544</v>
+      </c>
+      <c r="K44" t="s">
+        <v>497</v>
+      </c>
+      <c r="L44">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
         <v>295</v>
       </c>
@@ -6864,8 +9133,17 @@
       <c r="I45">
         <v>4.4211626052856397E-2</v>
       </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J45" t="s">
+        <v>545</v>
+      </c>
+      <c r="K45" t="s">
+        <v>497</v>
+      </c>
+      <c r="L45">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46" s="10" t="s">
         <v>296</v>
       </c>
@@ -6893,8 +9171,17 @@
       <c r="I46">
         <v>4.9978256225585903E-2</v>
       </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J46" t="s">
+        <v>546</v>
+      </c>
+      <c r="K46" t="s">
+        <v>498</v>
+      </c>
+      <c r="L46">
+        <v>0.22900000000000001</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
         <v>297</v>
       </c>
@@ -6922,8 +9209,17 @@
       <c r="I47">
         <v>4.6791315078735303E-2</v>
       </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J47" t="s">
+        <v>547</v>
+      </c>
+      <c r="K47" t="s">
+        <v>497</v>
+      </c>
+      <c r="L47">
+        <v>0.24099999999999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48" s="10" t="s">
         <v>298</v>
       </c>
@@ -6951,8 +9247,17 @@
       <c r="I48">
         <v>9.0545415878295898E-2</v>
       </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J48" t="s">
+        <v>548</v>
+      </c>
+      <c r="K48" t="s">
+        <v>498</v>
+      </c>
+      <c r="L48">
+        <v>0.222</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
         <v>299</v>
       </c>
@@ -6980,8 +9285,17 @@
       <c r="I49">
         <v>4.6838283538818297E-2</v>
       </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J49" t="s">
+        <v>549</v>
+      </c>
+      <c r="K49" t="s">
+        <v>497</v>
+      </c>
+      <c r="L49">
+        <v>0.215</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50" s="10" t="s">
         <v>300</v>
       </c>
@@ -7009,8 +9323,17 @@
       <c r="I50">
         <v>5.4154872894287102E-2</v>
       </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J50" t="s">
+        <v>550</v>
+      </c>
+      <c r="K50" t="s">
+        <v>497</v>
+      </c>
+      <c r="L50">
+        <v>0.22600000000000001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
         <v>301</v>
       </c>
@@ -7038,8 +9361,17 @@
       <c r="I51">
         <v>1.9216775894165001E-2</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J51" t="s">
+        <v>551</v>
+      </c>
+      <c r="K51" t="s">
+        <v>497</v>
+      </c>
+      <c r="L51">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52" s="10" t="s">
         <v>302</v>
       </c>
@@ -7067,8 +9399,17 @@
       <c r="I52">
         <v>5.2750825881958001E-2</v>
       </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J52" t="s">
+        <v>552</v>
+      </c>
+      <c r="K52" t="s">
+        <v>497</v>
+      </c>
+      <c r="L52">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
         <v>303</v>
       </c>
@@ -7096,8 +9437,17 @@
       <c r="I53">
         <v>0.161716699600219</v>
       </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J53" t="s">
+        <v>553</v>
+      </c>
+      <c r="K53" t="s">
+        <v>497</v>
+      </c>
+      <c r="L53">
+        <v>0.23499999999999999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54" s="10" t="s">
         <v>304</v>
       </c>
@@ -7125,8 +9475,17 @@
       <c r="I54">
         <v>5.3837537765502902E-2</v>
       </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J54" t="s">
+        <v>554</v>
+      </c>
+      <c r="K54" t="s">
+        <v>497</v>
+      </c>
+      <c r="L54">
+        <v>0.22600000000000001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
         <v>305</v>
       </c>
@@ -7154,8 +9513,17 @@
       <c r="I55">
         <v>6.1524391174316399E-2</v>
       </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J55" t="s">
+        <v>555</v>
+      </c>
+      <c r="K55" t="s">
+        <v>497</v>
+      </c>
+      <c r="L55">
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56" s="10" t="s">
         <v>306</v>
       </c>
@@ -7183,8 +9551,17 @@
       <c r="I56">
         <v>1.1770963668823201E-2</v>
       </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J56" t="s">
+        <v>556</v>
+      </c>
+      <c r="K56" t="s">
+        <v>498</v>
+      </c>
+      <c r="L56">
+        <v>3.4000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
         <v>307</v>
       </c>
@@ -7212,8 +9589,17 @@
       <c r="I57">
         <v>4.50634956359863E-2</v>
       </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J57" t="s">
+        <v>557</v>
+      </c>
+      <c r="K57" t="s">
+        <v>497</v>
+      </c>
+      <c r="L57">
+        <v>0.501</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58" s="10" t="s">
         <v>308</v>
       </c>
@@ -7241,8 +9627,17 @@
       <c r="I58">
         <v>4.7250747680664E-2</v>
       </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J58" t="s">
+        <v>558</v>
+      </c>
+      <c r="K58" t="s">
+        <v>497</v>
+      </c>
+      <c r="L58">
+        <v>0.28100000000000003</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
         <v>309</v>
       </c>
@@ -7270,8 +9665,17 @@
       <c r="I59">
         <v>5.5867433547973598E-2</v>
       </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J59" t="s">
+        <v>559</v>
+      </c>
+      <c r="K59" t="s">
+        <v>498</v>
+      </c>
+      <c r="L59">
+        <v>0.23300000000000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60" s="10" t="s">
         <v>310</v>
       </c>
@@ -7299,8 +9703,17 @@
       <c r="I60">
         <v>9.9360942840576102E-3</v>
       </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J60" t="s">
+        <v>560</v>
+      </c>
+      <c r="K60" t="s">
+        <v>498</v>
+      </c>
+      <c r="L60">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
         <v>311</v>
       </c>
@@ -7328,8 +9741,17 @@
       <c r="I61">
         <v>5.0779104232788003E-2</v>
       </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J61" t="s">
+        <v>561</v>
+      </c>
+      <c r="K61" t="s">
+        <v>498</v>
+      </c>
+      <c r="L61">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A62" s="10" t="s">
         <v>312</v>
       </c>
@@ -7357,8 +9779,17 @@
       <c r="I62">
         <v>4.8722743988037102E-2</v>
       </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J62" t="s">
+        <v>562</v>
+      </c>
+      <c r="K62" t="s">
+        <v>498</v>
+      </c>
+      <c r="L62">
+        <v>0.22700000000000001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A63" s="7" t="s">
         <v>313</v>
       </c>
@@ -7386,8 +9817,17 @@
       <c r="I63">
         <v>4.6223640441894497E-2</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J63" t="s">
+        <v>563</v>
+      </c>
+      <c r="K63" t="s">
+        <v>497</v>
+      </c>
+      <c r="L63">
+        <v>0.23400000000000001</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A64" s="10" t="s">
         <v>314</v>
       </c>
@@ -7415,8 +9855,17 @@
       <c r="I64">
         <v>4.4949531555175698E-2</v>
       </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J64" t="s">
+        <v>564</v>
+      </c>
+      <c r="K64" t="s">
+        <v>498</v>
+      </c>
+      <c r="L64">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A65" s="7" t="s">
         <v>315</v>
       </c>
@@ -7444,8 +9893,17 @@
       <c r="I65">
         <v>1.0486602783203101E-2</v>
       </c>
-    </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J65" t="s">
+        <v>565</v>
+      </c>
+      <c r="K65" t="s">
+        <v>498</v>
+      </c>
+      <c r="L65">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="10" t="s">
         <v>316</v>
       </c>
@@ -7473,8 +9931,17 @@
       <c r="I66">
         <v>4.6811819076538003E-2</v>
       </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J66" t="s">
+        <v>566</v>
+      </c>
+      <c r="K66" t="s">
+        <v>498</v>
+      </c>
+      <c r="L66">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A67" s="7" t="s">
         <v>317</v>
       </c>
@@ -7502,8 +9969,17 @@
       <c r="I67">
         <v>4.4660806655883699E-2</v>
       </c>
-    </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J67" t="s">
+        <v>567</v>
+      </c>
+      <c r="K67" t="s">
+        <v>498</v>
+      </c>
+      <c r="L67">
+        <v>0.23799999999999999</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A68" s="10" t="s">
         <v>318</v>
       </c>
@@ -7531,8 +10007,17 @@
       <c r="I68">
         <v>0.122978687286376</v>
       </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J68" t="s">
+        <v>568</v>
+      </c>
+      <c r="K68" t="s">
+        <v>498</v>
+      </c>
+      <c r="L68">
+        <v>0.23699999999999999</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A69" s="7" t="s">
         <v>319</v>
       </c>
@@ -7560,8 +10045,17 @@
       <c r="I69">
         <v>7.0685386657714802E-2</v>
       </c>
-    </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J69" t="s">
+        <v>569</v>
+      </c>
+      <c r="K69" t="s">
+        <v>498</v>
+      </c>
+      <c r="L69">
+        <v>0.22500000000000001</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A70" s="10" t="s">
         <v>320</v>
       </c>
@@ -7589,8 +10083,17 @@
       <c r="I70">
         <v>4.7506093978881801E-2</v>
       </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J70" t="s">
+        <v>570</v>
+      </c>
+      <c r="K70" t="s">
+        <v>497</v>
+      </c>
+      <c r="L70">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A71" s="7" t="s">
         <v>321</v>
       </c>
@@ -7618,8 +10121,17 @@
       <c r="I71">
         <v>5.5344104766845703E-2</v>
       </c>
-    </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J71" t="s">
+        <v>571</v>
+      </c>
+      <c r="K71" t="s">
+        <v>498</v>
+      </c>
+      <c r="L71">
+        <v>0.24299999999999999</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A72" s="10" t="s">
         <v>322</v>
       </c>
@@ -7647,8 +10159,17 @@
       <c r="I72">
         <v>5.0118207931518499E-2</v>
       </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J72" t="s">
+        <v>572</v>
+      </c>
+      <c r="K72" t="s">
+        <v>497</v>
+      </c>
+      <c r="L72">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A73" s="7" t="s">
         <v>323</v>
       </c>
@@ -7676,8 +10197,17 @@
       <c r="I73">
         <v>5.0841093063354402E-2</v>
       </c>
-    </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J73" t="s">
+        <v>573</v>
+      </c>
+      <c r="K73" t="s">
+        <v>497</v>
+      </c>
+      <c r="L73">
+        <v>0.23899999999999999</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A74" s="10" t="s">
         <v>324</v>
       </c>
@@ -7705,8 +10235,17 @@
       <c r="I74">
         <v>1.72088146209716E-2</v>
       </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J74" t="s">
+        <v>574</v>
+      </c>
+      <c r="K74" t="s">
+        <v>497</v>
+      </c>
+      <c r="L74">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A75" s="7" t="s">
         <v>325</v>
       </c>
@@ -7734,8 +10273,17 @@
       <c r="I75">
         <v>4.8106908798217697E-2</v>
       </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J75" t="s">
+        <v>575</v>
+      </c>
+      <c r="K75" t="s">
+        <v>497</v>
+      </c>
+      <c r="L75">
+        <v>0.39400000000000002</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A76" s="10" t="s">
         <v>326</v>
       </c>
@@ -7763,8 +10311,17 @@
       <c r="I76">
         <v>4.7061443328857401E-2</v>
       </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J76" t="s">
+        <v>576</v>
+      </c>
+      <c r="K76" t="s">
+        <v>497</v>
+      </c>
+      <c r="L76">
+        <v>0.55100000000000005</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A77" s="7" t="s">
         <v>327</v>
       </c>
@@ -7792,8 +10349,17 @@
       <c r="I77">
         <v>0.14733719825744601</v>
       </c>
-    </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J77" t="s">
+        <v>577</v>
+      </c>
+      <c r="K77" t="s">
+        <v>497</v>
+      </c>
+      <c r="L77">
+        <v>0.23200000000000001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A78" s="10" t="s">
         <v>328</v>
       </c>
@@ -7821,8 +10387,17 @@
       <c r="I78">
         <v>5.1762580871581997E-2</v>
       </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J78" t="s">
+        <v>578</v>
+      </c>
+      <c r="K78" t="s">
+        <v>497</v>
+      </c>
+      <c r="L78">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A79" s="7" t="s">
         <v>329</v>
       </c>
@@ -7850,8 +10425,17 @@
       <c r="I79">
         <v>1.2853860855102499E-2</v>
       </c>
-    </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J79" t="s">
+        <v>579</v>
+      </c>
+      <c r="K79" t="s">
+        <v>498</v>
+      </c>
+      <c r="L79">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A80" s="10" t="s">
         <v>330</v>
       </c>
@@ -7879,8 +10463,17 @@
       <c r="I80">
         <v>5.3411960601806599E-2</v>
       </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J80" t="s">
+        <v>580</v>
+      </c>
+      <c r="K80" t="s">
+        <v>497</v>
+      </c>
+      <c r="L80">
+        <v>0.20599999999999999</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A81" s="7" t="s">
         <v>331</v>
       </c>
@@ -7908,8 +10501,17 @@
       <c r="I81">
         <v>4.4915676116943297E-2</v>
       </c>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J81" t="s">
+        <v>581</v>
+      </c>
+      <c r="K81" t="s">
+        <v>497</v>
+      </c>
+      <c r="L81">
+        <v>0.186</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A82" s="10" t="s">
         <v>332</v>
       </c>
@@ -7937,8 +10539,17 @@
       <c r="I82">
         <v>9.6285343170165998E-3</v>
       </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J82" t="s">
+        <v>582</v>
+      </c>
+      <c r="K82" t="s">
+        <v>498</v>
+      </c>
+      <c r="L82">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
         <v>333</v>
       </c>
@@ -7966,8 +10577,17 @@
       <c r="I83">
         <v>4.5893430709838798E-2</v>
       </c>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J83" t="s">
+        <v>583</v>
+      </c>
+      <c r="K83" t="s">
+        <v>497</v>
+      </c>
+      <c r="L83">
+        <v>0.20599999999999999</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A84" s="10" t="s">
         <v>334</v>
       </c>
@@ -7995,8 +10615,17 @@
       <c r="I84">
         <v>1.0493993759155201E-2</v>
       </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J84" t="s">
+        <v>584</v>
+      </c>
+      <c r="K84" t="s">
+        <v>498</v>
+      </c>
+      <c r="L84">
+        <v>2.7E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
         <v>335</v>
       </c>
@@ -8024,8 +10653,17 @@
       <c r="I85">
         <v>4.95438575744628E-2</v>
       </c>
-    </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J85" t="s">
+        <v>585</v>
+      </c>
+      <c r="K85" t="s">
+        <v>497</v>
+      </c>
+      <c r="L85">
+        <v>0.54700000000000004</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="10" t="s">
         <v>336</v>
       </c>
@@ -8053,8 +10691,17 @@
       <c r="I86">
         <v>4.7630786895751898E-2</v>
       </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J86" t="s">
+        <v>586</v>
+      </c>
+      <c r="K86" t="s">
+        <v>498</v>
+      </c>
+      <c r="L86">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
         <v>337</v>
       </c>
@@ -8082,8 +10729,17 @@
       <c r="I87">
         <v>4.96673583984375E-2</v>
       </c>
-    </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J87" t="s">
+        <v>587</v>
+      </c>
+      <c r="K87" t="s">
+        <v>498</v>
+      </c>
+      <c r="L87">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A88" s="10" t="s">
         <v>338</v>
       </c>
@@ -8111,8 +10767,17 @@
       <c r="I88">
         <v>1.1652946472167899E-2</v>
       </c>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J88" t="s">
+        <v>588</v>
+      </c>
+      <c r="K88" t="s">
+        <v>498</v>
+      </c>
+      <c r="L88">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
         <v>339</v>
       </c>
@@ -8140,8 +10805,17 @@
       <c r="I89">
         <v>5.0182104110717697E-2</v>
       </c>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J89" t="s">
+        <v>589</v>
+      </c>
+      <c r="K89" t="s">
+        <v>498</v>
+      </c>
+      <c r="L89">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" s="10" t="s">
         <v>340</v>
       </c>
@@ -8169,8 +10843,17 @@
       <c r="I90">
         <v>5.2581310272216797E-2</v>
       </c>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J90" t="s">
+        <v>590</v>
+      </c>
+      <c r="K90" t="s">
+        <v>498</v>
+      </c>
+      <c r="L90">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
         <v>341</v>
       </c>
@@ -8198,8 +10881,17 @@
       <c r="I91">
         <v>4.3616771697997998E-2</v>
       </c>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J91" t="s">
+        <v>591</v>
+      </c>
+      <c r="K91" t="s">
+        <v>497</v>
+      </c>
+      <c r="L91">
+        <v>0.193</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" s="10" t="s">
         <v>342</v>
       </c>
@@ -8227,8 +10919,17 @@
       <c r="I92">
         <v>9.5777511596679601E-3</v>
       </c>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J92" t="s">
+        <v>592</v>
+      </c>
+      <c r="K92" t="s">
+        <v>498</v>
+      </c>
+      <c r="L92">
+        <v>1.9E-2</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
         <v>343</v>
       </c>
@@ -8256,8 +10957,17 @@
       <c r="I93">
         <v>1.09376907348632E-2</v>
       </c>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J93" t="s">
+        <v>593</v>
+      </c>
+      <c r="K93" t="s">
+        <v>498</v>
+      </c>
+      <c r="L93">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" s="10" t="s">
         <v>344</v>
       </c>
@@ -8285,8 +10995,17 @@
       <c r="I94">
         <v>1.01594924926757E-2</v>
       </c>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J94" t="s">
+        <v>594</v>
+      </c>
+      <c r="K94" t="s">
+        <v>498</v>
+      </c>
+      <c r="L94">
+        <v>3.5000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
         <v>345</v>
       </c>
@@ -8314,8 +11033,17 @@
       <c r="I95">
         <v>4.7819852828979402E-2</v>
       </c>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J95" t="s">
+        <v>595</v>
+      </c>
+      <c r="K95" t="s">
+        <v>498</v>
+      </c>
+      <c r="L95">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" s="10" t="s">
         <v>346</v>
       </c>
@@ -8343,8 +11071,17 @@
       <c r="I96">
         <v>4.8085451126098598E-2</v>
       </c>
-    </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J96" t="s">
+        <v>596</v>
+      </c>
+      <c r="K96" t="s">
+        <v>498</v>
+      </c>
+      <c r="L96">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
         <v>347</v>
       </c>
@@ -8372,8 +11109,17 @@
       <c r="I97">
         <v>4.7187328338622998E-2</v>
       </c>
-    </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J97" t="s">
+        <v>597</v>
+      </c>
+      <c r="K97" t="s">
+        <v>497</v>
+      </c>
+      <c r="L97">
+        <v>0.22800000000000001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A98" s="10" t="s">
         <v>348</v>
       </c>
@@ -8401,8 +11147,17 @@
       <c r="I98">
         <v>4.77674007415771E-2</v>
       </c>
-    </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J98" t="s">
+        <v>598</v>
+      </c>
+      <c r="K98" t="s">
+        <v>498</v>
+      </c>
+      <c r="L98">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
         <v>349</v>
       </c>
@@ -8430,8 +11185,17 @@
       <c r="I99">
         <v>4.6757459640502902E-2</v>
       </c>
-    </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J99" t="s">
+        <v>599</v>
+      </c>
+      <c r="K99" t="s">
+        <v>498</v>
+      </c>
+      <c r="L99">
+        <v>0.24299999999999999</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A100" s="10" t="s">
         <v>350</v>
       </c>
@@ -8459,8 +11223,17 @@
       <c r="I100">
         <v>4.6641349792480399E-2</v>
       </c>
-    </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J100" t="s">
+        <v>600</v>
+      </c>
+      <c r="K100" t="s">
+        <v>497</v>
+      </c>
+      <c r="L100">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
         <v>351</v>
       </c>
@@ -8488,8 +11261,17 @@
       <c r="I101">
         <v>4.5722961425781201E-2</v>
       </c>
-    </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J101" t="s">
+        <v>601</v>
+      </c>
+      <c r="K101" t="s">
+        <v>497</v>
+      </c>
+      <c r="L101">
+        <v>0.223</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A102" s="10" t="s">
         <v>352</v>
       </c>
@@ -8517,8 +11299,17 @@
       <c r="I102">
         <v>1.7483234405517498E-2</v>
       </c>
-    </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J102" t="s">
+        <v>602</v>
+      </c>
+      <c r="K102" t="s">
+        <v>497</v>
+      </c>
+      <c r="L102">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
         <v>353</v>
       </c>
@@ -8546,8 +11337,17 @@
       <c r="I103">
         <v>5.6472063064575098E-2</v>
       </c>
-    </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J103" t="s">
+        <v>603</v>
+      </c>
+      <c r="K103" t="s">
+        <v>497</v>
+      </c>
+      <c r="L103">
+        <v>0.22900000000000001</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A104" s="10" t="s">
         <v>354</v>
       </c>
@@ -8575,8 +11375,17 @@
       <c r="I104">
         <v>8.8441848754882799E-2</v>
       </c>
-    </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J104" t="s">
+        <v>604</v>
+      </c>
+      <c r="K104" t="s">
+        <v>497</v>
+      </c>
+      <c r="L104">
+        <v>0.22600000000000001</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
         <v>355</v>
       </c>
@@ -8604,8 +11413,17 @@
       <c r="I105">
         <v>8.3253383636474595E-2</v>
       </c>
-    </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J105" t="s">
+        <v>605</v>
+      </c>
+      <c r="K105" t="s">
+        <v>497</v>
+      </c>
+      <c r="L105">
+        <v>0.222</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A106" s="10" t="s">
         <v>356</v>
       </c>
@@ -8633,8 +11451,17 @@
       <c r="I106">
         <v>0.130986928939819</v>
       </c>
-    </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J106" t="s">
+        <v>606</v>
+      </c>
+      <c r="K106" t="s">
+        <v>497</v>
+      </c>
+      <c r="L106">
+        <v>0.22800000000000001</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
         <v>357</v>
       </c>
@@ -8662,8 +11489,17 @@
       <c r="I107">
         <v>0.205983877182006</v>
       </c>
-    </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J107" t="s">
+        <v>607</v>
+      </c>
+      <c r="K107" t="s">
+        <v>497</v>
+      </c>
+      <c r="L107">
+        <v>0.23100000000000001</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A108" s="10" t="s">
         <v>358</v>
       </c>
@@ -8691,8 +11527,17 @@
       <c r="I108">
         <v>1.12090110778808E-2</v>
       </c>
-    </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J108" t="s">
+        <v>608</v>
+      </c>
+      <c r="K108" t="s">
+        <v>498</v>
+      </c>
+      <c r="L108">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
         <v>359</v>
       </c>
@@ -8720,8 +11565,17 @@
       <c r="I109">
         <v>5.10697364807128E-2</v>
       </c>
-    </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J109" t="s">
+        <v>609</v>
+      </c>
+      <c r="K109" t="s">
+        <v>497</v>
+      </c>
+      <c r="L109">
+        <v>0.187</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A110" s="10" t="s">
         <v>360</v>
       </c>
@@ -8749,8 +11603,17 @@
       <c r="I110">
         <v>4.6656370162963798E-2</v>
       </c>
-    </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J110" t="s">
+        <v>610</v>
+      </c>
+      <c r="K110" t="s">
+        <v>497</v>
+      </c>
+      <c r="L110">
+        <v>0.22800000000000001</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
         <v>361</v>
       </c>
@@ -8778,8 +11641,17 @@
       <c r="I111">
         <v>4.4392347335815402E-2</v>
       </c>
-    </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J111" t="s">
+        <v>611</v>
+      </c>
+      <c r="K111" t="s">
+        <v>498</v>
+      </c>
+      <c r="L111">
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A112" s="10" t="s">
         <v>362</v>
       </c>
@@ -8807,8 +11679,17 @@
       <c r="I112">
         <v>1.0449886322021399E-2</v>
       </c>
-    </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J112" t="s">
+        <v>612</v>
+      </c>
+      <c r="K112" t="s">
+        <v>498</v>
+      </c>
+      <c r="L112">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
         <v>363</v>
       </c>
@@ -8836,8 +11717,17 @@
       <c r="I113">
         <v>4.7589778900146401E-2</v>
       </c>
-    </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J113" t="s">
+        <v>613</v>
+      </c>
+      <c r="K113" t="s">
+        <v>498</v>
+      </c>
+      <c r="L113">
+        <v>0.54200000000000004</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A114" s="10" t="s">
         <v>364</v>
       </c>
@@ -8865,8 +11755,17 @@
       <c r="I114">
         <v>4.43463325500488E-2</v>
       </c>
-    </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J114" t="s">
+        <v>614</v>
+      </c>
+      <c r="K114" t="s">
+        <v>497</v>
+      </c>
+      <c r="L114">
+        <v>0.47499999999999998</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
         <v>365</v>
       </c>
@@ -8894,8 +11793,17 @@
       <c r="I115">
         <v>1.0713100433349601E-2</v>
       </c>
-    </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J115" t="s">
+        <v>615</v>
+      </c>
+      <c r="K115" t="s">
+        <v>498</v>
+      </c>
+      <c r="L115">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A116" s="10" t="s">
         <v>366</v>
       </c>
@@ -8923,8 +11831,17 @@
       <c r="I116">
         <v>1.0607957839965799E-2</v>
       </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J116" t="s">
+        <v>616</v>
+      </c>
+      <c r="K116" t="s">
+        <v>498</v>
+      </c>
+      <c r="L116">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
         <v>367</v>
       </c>
@@ -8952,8 +11869,17 @@
       <c r="I117">
         <v>1.08428001403808E-2</v>
       </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J117" t="s">
+        <v>617</v>
+      </c>
+      <c r="K117" t="s">
+        <v>498</v>
+      </c>
+      <c r="L117">
+        <v>2.3E-2</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A118" s="10" t="s">
         <v>368</v>
       </c>
@@ -8981,8 +11907,17 @@
       <c r="I118">
         <v>4.5263528823852497E-2</v>
       </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J118" t="s">
+        <v>618</v>
+      </c>
+      <c r="K118" t="s">
+        <v>497</v>
+      </c>
+      <c r="L118">
+        <v>0.188</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
         <v>369</v>
       </c>
@@ -9010,8 +11945,17 @@
       <c r="I119">
         <v>4.5195817947387598E-2</v>
       </c>
-    </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J119" t="s">
+        <v>619</v>
+      </c>
+      <c r="K119" t="s">
+        <v>497</v>
+      </c>
+      <c r="L119">
+        <v>0.216</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A120" s="10" t="s">
         <v>370</v>
       </c>
@@ -9039,8 +11983,17 @@
       <c r="I120">
         <v>6.0981273651122998E-2</v>
       </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J120" t="s">
+        <v>620</v>
+      </c>
+      <c r="K120" t="s">
+        <v>498</v>
+      </c>
+      <c r="L120">
+        <v>0.22700000000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
         <v>371</v>
       </c>
@@ -9068,8 +12021,17 @@
       <c r="I121">
         <v>1.0813713073730399E-2</v>
       </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J121" t="s">
+        <v>621</v>
+      </c>
+      <c r="K121" t="s">
+        <v>498</v>
+      </c>
+      <c r="L121">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A122" s="10" t="s">
         <v>372</v>
       </c>
@@ -9097,8 +12059,17 @@
       <c r="I122">
         <v>1.2289762496948201E-2</v>
       </c>
-    </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J122" t="s">
+        <v>622</v>
+      </c>
+      <c r="K122" t="s">
+        <v>497</v>
+      </c>
+      <c r="L122">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
         <v>373</v>
       </c>
@@ -9126,8 +12097,17 @@
       <c r="I123">
         <v>1.30712985992431E-2</v>
       </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J123" t="s">
+        <v>623</v>
+      </c>
+      <c r="K123" t="s">
+        <v>497</v>
+      </c>
+      <c r="L123">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A124" s="10" t="s">
         <v>374</v>
       </c>
@@ -9155,8 +12135,17 @@
       <c r="I124">
         <v>1.15993022918701E-2</v>
       </c>
-    </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J124" t="s">
+        <v>624</v>
+      </c>
+      <c r="K124" t="s">
+        <v>497</v>
+      </c>
+      <c r="L124">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
         <v>375</v>
       </c>
@@ -9184,8 +12173,17 @@
       <c r="I125">
         <v>4.4612407684326102E-2</v>
       </c>
-    </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J125" t="s">
+        <v>625</v>
+      </c>
+      <c r="K125" t="s">
+        <v>497</v>
+      </c>
+      <c r="L125">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A126" s="10" t="s">
         <v>376</v>
       </c>
@@ -9213,8 +12211,17 @@
       <c r="I126">
         <v>4.2409181594848598E-2</v>
       </c>
-    </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J126" t="s">
+        <v>626</v>
+      </c>
+      <c r="K126" t="s">
+        <v>497</v>
+      </c>
+      <c r="L126">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
         <v>377</v>
       </c>
@@ -9242,8 +12249,17 @@
       <c r="I127">
         <v>5.1395416259765597E-2</v>
       </c>
-    </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J127" t="s">
+        <v>627</v>
+      </c>
+      <c r="K127" t="s">
+        <v>497</v>
+      </c>
+      <c r="L127">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A128" s="10" t="s">
         <v>378</v>
       </c>
@@ -9271,8 +12287,17 @@
       <c r="I128">
         <v>4.1522502899169901E-2</v>
       </c>
-    </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J128" t="s">
+        <v>628</v>
+      </c>
+      <c r="K128" t="s">
+        <v>497</v>
+      </c>
+      <c r="L128">
+        <v>0.184</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A129" s="7" t="s">
         <v>379</v>
       </c>
@@ -9300,8 +12325,17 @@
       <c r="I129">
         <v>4.2270660400390597E-2</v>
       </c>
-    </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J129" t="s">
+        <v>629</v>
+      </c>
+      <c r="K129" t="s">
+        <v>497</v>
+      </c>
+      <c r="L129">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A130" s="10" t="s">
         <v>380</v>
       </c>
@@ -9329,8 +12363,17 @@
       <c r="I130">
         <v>4.2980194091796799E-2</v>
       </c>
-    </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J130" t="s">
+        <v>630</v>
+      </c>
+      <c r="K130" t="s">
+        <v>497</v>
+      </c>
+      <c r="L130">
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A131" s="7" t="s">
         <v>381</v>
       </c>
@@ -9358,8 +12401,17 @@
       <c r="I131">
         <v>4.241943359375E-2</v>
       </c>
-    </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J131" t="s">
+        <v>631</v>
+      </c>
+      <c r="K131" t="s">
+        <v>497</v>
+      </c>
+      <c r="L131">
+        <v>0.18099999999999999</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A132" s="10" t="s">
         <v>382</v>
       </c>
@@ -9387,8 +12439,17 @@
       <c r="I132">
         <v>4.29434776306152E-2</v>
       </c>
-    </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J132" t="s">
+        <v>632</v>
+      </c>
+      <c r="K132" t="s">
+        <v>497</v>
+      </c>
+      <c r="L132">
+        <v>0.32600000000000001</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A133" s="7" t="s">
         <v>383</v>
       </c>
@@ -9416,8 +12477,17 @@
       <c r="I133">
         <v>4.2688608169555602E-2</v>
       </c>
-    </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J133" t="s">
+        <v>633</v>
+      </c>
+      <c r="K133" t="s">
+        <v>497</v>
+      </c>
+      <c r="L133">
+        <v>0.47499999999999998</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A134" s="10" t="s">
         <v>384</v>
       </c>
@@ -9445,8 +12515,17 @@
       <c r="I134">
         <v>4.3863058090209898E-2</v>
       </c>
-    </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J134" t="s">
+        <v>634</v>
+      </c>
+      <c r="K134" t="s">
+        <v>497</v>
+      </c>
+      <c r="L134">
+        <v>1.2E-2</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A135" s="7" t="s">
         <v>385</v>
       </c>
@@ -9474,8 +12553,17 @@
       <c r="I135">
         <v>4.3490171432495103E-2</v>
       </c>
-    </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J135" t="s">
+        <v>635</v>
+      </c>
+      <c r="K135" t="s">
+        <v>497</v>
+      </c>
+      <c r="L135">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A136" s="10" t="s">
         <v>386</v>
       </c>
@@ -9503,8 +12591,17 @@
       <c r="I136">
         <v>4.2840003967285101E-2</v>
       </c>
-    </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J136" t="s">
+        <v>636</v>
+      </c>
+      <c r="K136" t="s">
+        <v>497</v>
+      </c>
+      <c r="L136">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A137" s="7" t="s">
         <v>387</v>
       </c>
@@ -9532,8 +12629,17 @@
       <c r="I137">
         <v>4.4537067413330002E-2</v>
       </c>
-    </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J137" t="s">
+        <v>637</v>
+      </c>
+      <c r="K137" t="s">
+        <v>497</v>
+      </c>
+      <c r="L137">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A138" s="10" t="s">
         <v>388</v>
       </c>
@@ -9561,8 +12667,17 @@
       <c r="I138">
         <v>4.21948432922363E-2</v>
       </c>
-    </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J138" t="s">
+        <v>638</v>
+      </c>
+      <c r="K138" t="s">
+        <v>497</v>
+      </c>
+      <c r="L138">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A139" s="7" t="s">
         <v>389</v>
       </c>
@@ -9590,8 +12705,17 @@
       <c r="I139">
         <v>4.2753458023071199E-2</v>
       </c>
-    </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J139" t="s">
+        <v>639</v>
+      </c>
+      <c r="K139" t="s">
+        <v>497</v>
+      </c>
+      <c r="L139">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A140" s="10" t="s">
         <v>390</v>
       </c>
@@ -9619,8 +12743,17 @@
       <c r="I140">
         <v>4.7303676605224602E-2</v>
       </c>
-    </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J140" t="s">
+        <v>640</v>
+      </c>
+      <c r="K140" t="s">
+        <v>497</v>
+      </c>
+      <c r="L140">
+        <v>0.185</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A141" s="7" t="s">
         <v>391</v>
       </c>
@@ -9648,8 +12781,17 @@
       <c r="I141">
         <v>4.15787696838378E-2</v>
       </c>
-    </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J141" t="s">
+        <v>641</v>
+      </c>
+      <c r="K141" t="s">
+        <v>497</v>
+      </c>
+      <c r="L141">
+        <v>0.33600000000000002</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A142" s="10" t="s">
         <v>392</v>
       </c>
@@ -9677,8 +12819,17 @@
       <c r="I142">
         <v>1.1081695556640601E-2</v>
       </c>
-    </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J142" t="s">
+        <v>642</v>
+      </c>
+      <c r="K142" t="s">
+        <v>498</v>
+      </c>
+      <c r="L142">
+        <v>3.6999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A143" s="7" t="s">
         <v>393</v>
       </c>
@@ -9706,8 +12857,17 @@
       <c r="I143">
         <v>4.22806739807128E-2</v>
       </c>
-    </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J143" t="s">
+        <v>643</v>
+      </c>
+      <c r="K143" t="s">
+        <v>497</v>
+      </c>
+      <c r="L143">
+        <v>0.183</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A144" s="10" t="s">
         <v>394</v>
       </c>
@@ -9735,8 +12895,17 @@
       <c r="I144">
         <v>1.03745460510253E-2</v>
       </c>
-    </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J144" t="s">
+        <v>644</v>
+      </c>
+      <c r="K144" t="s">
+        <v>498</v>
+      </c>
+      <c r="L144">
+        <v>1.7000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A145" s="7" t="s">
         <v>395</v>
       </c>
@@ -9764,8 +12933,17 @@
       <c r="I145">
         <v>4.9272060394287102E-2</v>
       </c>
-    </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J145" t="s">
+        <v>645</v>
+      </c>
+      <c r="K145" t="s">
+        <v>497</v>
+      </c>
+      <c r="L145">
+        <v>0.183</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A146" s="10" t="s">
         <v>396</v>
       </c>
@@ -9793,8 +12971,17 @@
       <c r="I146">
         <v>1.22833251953125E-2</v>
       </c>
-    </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J146" t="s">
+        <v>646</v>
+      </c>
+      <c r="K146" t="s">
+        <v>497</v>
+      </c>
+      <c r="L146">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A147" s="7" t="s">
         <v>397</v>
       </c>
@@ -9822,8 +13009,17 @@
       <c r="I147">
         <v>1.35400295257568E-2</v>
       </c>
-    </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J147" t="s">
+        <v>647</v>
+      </c>
+      <c r="K147" t="s">
+        <v>497</v>
+      </c>
+      <c r="L147">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A148" s="10" t="s">
         <v>398</v>
       </c>
@@ -9851,8 +13047,17 @@
       <c r="I148">
         <v>1.2335538864135701E-2</v>
       </c>
-    </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J148" t="s">
+        <v>648</v>
+      </c>
+      <c r="K148" t="s">
+        <v>497</v>
+      </c>
+      <c r="L148">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A149" s="7" t="s">
         <v>399</v>
       </c>
@@ -9880,8 +13085,17 @@
       <c r="I149">
         <v>4.6390533447265597E-2</v>
       </c>
-    </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J149" t="s">
+        <v>649</v>
+      </c>
+      <c r="K149" t="s">
+        <v>498</v>
+      </c>
+      <c r="L149">
+        <v>0.215</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A150" s="10" t="s">
         <v>400</v>
       </c>
@@ -9909,8 +13123,17 @@
       <c r="I150">
         <v>4.5660257339477497E-2</v>
       </c>
-    </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J150" t="s">
+        <v>650</v>
+      </c>
+      <c r="K150" t="s">
+        <v>497</v>
+      </c>
+      <c r="L150">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A151" s="7" t="s">
         <v>401</v>
       </c>
@@ -9938,8 +13161,17 @@
       <c r="I151">
         <v>1.0617733001708899E-2</v>
       </c>
-    </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J151" t="s">
+        <v>651</v>
+      </c>
+      <c r="K151" t="s">
+        <v>498</v>
+      </c>
+      <c r="L151">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A152" s="10" t="s">
         <v>402</v>
       </c>
@@ -9967,8 +13199,17 @@
       <c r="I152">
         <v>4.3722391128539997E-2</v>
       </c>
-    </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J152" t="s">
+        <v>652</v>
+      </c>
+      <c r="K152" t="s">
+        <v>497</v>
+      </c>
+      <c r="L152">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A153" s="7" t="s">
         <v>403</v>
       </c>
@@ -9996,8 +13237,17 @@
       <c r="I153">
         <v>9.7038745880126901E-3</v>
       </c>
-    </row>
-    <row r="154" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J153" t="s">
+        <v>653</v>
+      </c>
+      <c r="K153" t="s">
+        <v>498</v>
+      </c>
+      <c r="L153">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A154" s="10" t="s">
         <v>404</v>
       </c>
@@ -10025,8 +13275,17 @@
       <c r="I154">
         <v>4.3673753738403299E-2</v>
       </c>
-    </row>
-    <row r="155" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J154" t="s">
+        <v>654</v>
+      </c>
+      <c r="K154" t="s">
+        <v>497</v>
+      </c>
+      <c r="L154">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A155" s="7" t="s">
         <v>405</v>
       </c>
@@ -10054,8 +13313,17 @@
       <c r="I155">
         <v>9.2990398406982405E-3</v>
       </c>
-    </row>
-    <row r="156" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J155" t="s">
+        <v>655</v>
+      </c>
+      <c r="K155" t="s">
+        <v>498</v>
+      </c>
+      <c r="L155">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A156" s="10" t="s">
         <v>406</v>
       </c>
@@ -10083,8 +13351,17 @@
       <c r="I156">
         <v>4.8962116241455002E-2</v>
       </c>
-    </row>
-    <row r="157" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J156" t="s">
+        <v>656</v>
+      </c>
+      <c r="K156" t="s">
+        <v>497</v>
+      </c>
+      <c r="L156">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A157" s="7" t="s">
         <v>407</v>
       </c>
@@ -10112,8 +13389,17 @@
       <c r="I157">
         <v>1.2424468994140601E-2</v>
       </c>
-    </row>
-    <row r="158" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J157" t="s">
+        <v>657</v>
+      </c>
+      <c r="K157" t="s">
+        <v>497</v>
+      </c>
+      <c r="L157">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A158" s="10" t="s">
         <v>408</v>
       </c>
@@ -10141,8 +13427,17 @@
       <c r="I158">
         <v>4.4213056564330999E-2</v>
       </c>
-    </row>
-    <row r="159" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J158" t="s">
+        <v>658</v>
+      </c>
+      <c r="K158" t="s">
+        <v>497</v>
+      </c>
+      <c r="L158">
+        <v>0.184</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A159" s="7" t="s">
         <v>409</v>
       </c>
@@ -10170,8 +13465,17 @@
       <c r="I159">
         <v>1.1805772781371999E-2</v>
       </c>
-    </row>
-    <row r="160" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J159" t="s">
+        <v>659</v>
+      </c>
+      <c r="K159" t="s">
+        <v>498</v>
+      </c>
+      <c r="L159">
+        <v>2.5999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A160" s="10" t="s">
         <v>410</v>
       </c>
@@ -10199,8 +13503,17 @@
       <c r="I160">
         <v>4.2194366455078097E-2</v>
       </c>
-    </row>
-    <row r="161" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J160" t="s">
+        <v>660</v>
+      </c>
+      <c r="K160" t="s">
+        <v>497</v>
+      </c>
+      <c r="L160">
+        <v>0.49199999999999999</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A161" s="7" t="s">
         <v>411</v>
       </c>
@@ -10228,8 +13541,17 @@
       <c r="I161">
         <v>9.7630023956298793E-3</v>
       </c>
-    </row>
-    <row r="162" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J161" t="s">
+        <v>661</v>
+      </c>
+      <c r="K161" t="s">
+        <v>498</v>
+      </c>
+      <c r="L161">
+        <v>3.3000000000000002E-2</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A162" s="10" t="s">
         <v>412</v>
       </c>
@@ -10257,8 +13579,17 @@
       <c r="I162">
         <v>4.3220043182372998E-2</v>
       </c>
-    </row>
-    <row r="163" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J162" t="s">
+        <v>662</v>
+      </c>
+      <c r="K162" t="s">
+        <v>497</v>
+      </c>
+      <c r="L162">
+        <v>0.187</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A163" s="7" t="s">
         <v>413</v>
       </c>
@@ -10286,8 +13617,17 @@
       <c r="I163">
         <v>1.1343717575073201E-2</v>
       </c>
-    </row>
-    <row r="164" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J163" t="s">
+        <v>663</v>
+      </c>
+      <c r="K163" t="s">
+        <v>497</v>
+      </c>
+      <c r="L163">
+        <v>1.0999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A164" s="10" t="s">
         <v>414</v>
       </c>
@@ -10315,8 +13655,17 @@
       <c r="I164">
         <v>4.6789646148681599E-2</v>
       </c>
-    </row>
-    <row r="165" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J164" t="s">
+        <v>664</v>
+      </c>
+      <c r="K164" t="s">
+        <v>497</v>
+      </c>
+      <c r="L164">
+        <v>0.24199999999999999</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A165" s="7" t="s">
         <v>415</v>
       </c>
@@ -10344,8 +13693,17 @@
       <c r="I165">
         <v>4.3131351470947203E-2</v>
       </c>
-    </row>
-    <row r="166" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J165" t="s">
+        <v>665</v>
+      </c>
+      <c r="K165" t="s">
+        <v>497</v>
+      </c>
+      <c r="L165">
+        <v>8.9999999999999993E-3</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A166" s="10" t="s">
         <v>416</v>
       </c>
@@ -10373,8 +13731,17 @@
       <c r="I166">
         <v>5.8704376220703097E-2</v>
       </c>
-    </row>
-    <row r="167" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J166" t="s">
+        <v>666</v>
+      </c>
+      <c r="K166" t="s">
+        <v>498</v>
+      </c>
+      <c r="L166">
+        <v>1.63</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A167" s="7" t="s">
         <v>417</v>
       </c>
@@ -10402,8 +13769,17 @@
       <c r="I167">
         <v>0.116800069808959</v>
       </c>
-    </row>
-    <row r="168" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J167" t="s">
+        <v>667</v>
+      </c>
+      <c r="K167" t="s">
+        <v>497</v>
+      </c>
+      <c r="L167">
+        <v>16.096</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A168" s="10" t="s">
         <v>418</v>
       </c>
@@ -10431,8 +13807,17 @@
       <c r="I168">
         <v>0.12814307212829501</v>
       </c>
-    </row>
-    <row r="169" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J168" t="s">
+        <v>668</v>
+      </c>
+      <c r="K168" t="s">
+        <v>498</v>
+      </c>
+      <c r="L168">
+        <v>23.457999999999998</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A169" s="7" t="s">
         <v>419</v>
       </c>
@@ -10460,8 +13845,17 @@
       <c r="I169">
         <v>8.0286900997161794</v>
       </c>
-    </row>
-    <row r="170" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J169" t="s">
+        <v>669</v>
+      </c>
+      <c r="K169" t="s">
+        <v>173</v>
+      </c>
+      <c r="L169">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A170" s="10" t="s">
         <v>420</v>
       </c>
@@ -10489,8 +13883,17 @@
       <c r="I170">
         <v>7.9743127822875897</v>
       </c>
-    </row>
-    <row r="171" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J170" t="s">
+        <v>670</v>
+      </c>
+      <c r="K170" t="s">
+        <v>173</v>
+      </c>
+      <c r="L170">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A171" s="7" t="s">
         <v>421</v>
       </c>
@@ -10518,8 +13921,17 @@
       <c r="I171">
         <v>2.15697288513183E-2</v>
       </c>
-    </row>
-    <row r="172" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J171" t="s">
+        <v>671</v>
+      </c>
+      <c r="K171" t="s">
+        <v>497</v>
+      </c>
+      <c r="L171">
+        <v>0.32500000000000001</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A172" s="10" t="s">
         <v>422</v>
       </c>
@@ -10547,8 +13959,17 @@
       <c r="I172">
         <v>0.13244318962097101</v>
       </c>
-    </row>
-    <row r="173" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J172" t="s">
+        <v>672</v>
+      </c>
+      <c r="K172" t="s">
+        <v>497</v>
+      </c>
+      <c r="L172">
+        <v>15.702999999999999</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A173" s="7" t="s">
         <v>423</v>
       </c>
@@ -10576,8 +13997,17 @@
       <c r="I173">
         <v>0.113091468811035</v>
       </c>
-    </row>
-    <row r="174" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J173" t="s">
+        <v>673</v>
+      </c>
+      <c r="K173" t="s">
+        <v>497</v>
+      </c>
+      <c r="L173">
+        <v>15.803000000000001</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A174" s="10" t="s">
         <v>424</v>
       </c>
@@ -10605,8 +14035,17 @@
       <c r="I174">
         <v>0.11482834815979</v>
       </c>
-    </row>
-    <row r="175" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J174" t="s">
+        <v>674</v>
+      </c>
+      <c r="K174" t="s">
+        <v>497</v>
+      </c>
+      <c r="L174">
+        <v>15.404</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A175" s="7" t="s">
         <v>425</v>
       </c>
@@ -10634,8 +14073,17 @@
       <c r="I175">
         <v>0.113204717636108</v>
       </c>
-    </row>
-    <row r="176" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J175" t="s">
+        <v>675</v>
+      </c>
+      <c r="K175" t="s">
+        <v>497</v>
+      </c>
+      <c r="L175">
+        <v>15.613</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A176" s="10" t="s">
         <v>426</v>
       </c>
@@ -10663,8 +14111,17 @@
       <c r="I176">
         <v>10.3423652648925</v>
       </c>
-    </row>
-    <row r="177" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J176" t="s">
+        <v>676</v>
+      </c>
+      <c r="K176" t="s">
+        <v>497</v>
+      </c>
+      <c r="L176">
+        <v>63.076999999999998</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A177" s="7" t="s">
         <v>427</v>
       </c>
@@ -10692,8 +14149,17 @@
       <c r="I177">
         <v>2.2301673889160101E-2</v>
       </c>
-    </row>
-    <row r="178" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J177" t="s">
+        <v>677</v>
+      </c>
+      <c r="K177" t="s">
+        <v>497</v>
+      </c>
+      <c r="L177">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A178" s="10" t="s">
         <v>428</v>
       </c>
@@ -10721,8 +14187,17 @@
       <c r="I178">
         <v>6.3155651092529297E-2</v>
       </c>
-    </row>
-    <row r="179" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J178" t="s">
+        <v>678</v>
+      </c>
+      <c r="K178" t="s">
+        <v>497</v>
+      </c>
+      <c r="L178">
+        <v>1.696</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A179" s="7" t="s">
         <v>429</v>
       </c>
@@ -10750,8 +14225,17 @@
       <c r="I179">
         <v>4.9031496047973598E-2</v>
       </c>
-    </row>
-    <row r="180" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J179" t="s">
+        <v>679</v>
+      </c>
+      <c r="K179" t="s">
+        <v>498</v>
+      </c>
+      <c r="L179">
+        <v>0.248</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A180" s="10" t="s">
         <v>430</v>
       </c>
@@ -10779,8 +14263,17 @@
       <c r="I180">
         <v>7.9343318939208898E-3</v>
       </c>
-    </row>
-    <row r="181" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J180" t="s">
+        <v>680</v>
+      </c>
+      <c r="K180" t="s">
+        <v>498</v>
+      </c>
+      <c r="L180">
+        <v>1.4E-2</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A181" s="7" t="s">
         <v>431</v>
       </c>
@@ -10808,8 +14301,17 @@
       <c r="I181">
         <v>7.5896024703979395E-2</v>
       </c>
-    </row>
-    <row r="182" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J181" t="s">
+        <v>681</v>
+      </c>
+      <c r="K181" t="s">
+        <v>498</v>
+      </c>
+      <c r="L181">
+        <v>1.64</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A182" s="10" t="s">
         <v>432</v>
       </c>
@@ -10837,8 +14339,17 @@
       <c r="I182">
         <v>6.6768407821655204E-2</v>
       </c>
-    </row>
-    <row r="183" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J182" t="s">
+        <v>682</v>
+      </c>
+      <c r="K182" t="s">
+        <v>498</v>
+      </c>
+      <c r="L182">
+        <v>1.6819999999999999</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A183" s="7" t="s">
         <v>433</v>
       </c>
@@ -10866,8 +14377,17 @@
       <c r="I183">
         <v>6.4674854278564398E-2</v>
       </c>
-    </row>
-    <row r="184" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J183" t="s">
+        <v>683</v>
+      </c>
+      <c r="K183" t="s">
+        <v>497</v>
+      </c>
+      <c r="L183">
+        <v>1.76</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A184" s="10" t="s">
         <v>434</v>
       </c>
@@ -10895,8 +14415,17 @@
       <c r="I184">
         <v>0.140614509582519</v>
       </c>
-    </row>
-    <row r="185" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J184" t="s">
+        <v>684</v>
+      </c>
+      <c r="K184" t="s">
+        <v>498</v>
+      </c>
+      <c r="L184">
+        <v>0.224</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A185" s="7" t="s">
         <v>435</v>
       </c>
@@ -10924,8 +14453,17 @@
       <c r="I185">
         <v>9.9568367004394497E-3</v>
       </c>
-    </row>
-    <row r="186" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J185" t="s">
+        <v>685</v>
+      </c>
+      <c r="K185" t="s">
+        <v>498</v>
+      </c>
+      <c r="L185">
+        <v>1.4999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A186" s="10" t="s">
         <v>436</v>
       </c>
@@ -10953,8 +14491,17 @@
       <c r="I186">
         <v>6.7728042602538993E-2</v>
       </c>
-    </row>
-    <row r="187" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J186" t="s">
+        <v>686</v>
+      </c>
+      <c r="K186" t="s">
+        <v>498</v>
+      </c>
+      <c r="L186">
+        <v>1.728</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A187" s="7" t="s">
         <v>437</v>
       </c>
@@ -10982,8 +14529,17 @@
       <c r="I187">
         <v>7.1146249771118095E-2</v>
       </c>
-    </row>
-    <row r="188" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J187" t="s">
+        <v>687</v>
+      </c>
+      <c r="K187" t="s">
+        <v>498</v>
+      </c>
+      <c r="L187">
+        <v>1.7050000000000001</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A188" s="10" t="s">
         <v>438</v>
       </c>
@@ -11011,8 +14567,17 @@
       <c r="I188">
         <v>6.0230970382690402E-2</v>
       </c>
-    </row>
-    <row r="189" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J188" t="s">
+        <v>688</v>
+      </c>
+      <c r="K188" t="s">
+        <v>498</v>
+      </c>
+      <c r="L188">
+        <v>3.915</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A189" s="7" t="s">
         <v>439</v>
       </c>
@@ -11040,8 +14605,17 @@
       <c r="I189">
         <v>6.1934709548950098E-2</v>
       </c>
-    </row>
-    <row r="190" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J189" t="s">
+        <v>689</v>
+      </c>
+      <c r="K189" t="s">
+        <v>498</v>
+      </c>
+      <c r="L189">
+        <v>3.83</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A190" s="10" t="s">
         <v>440</v>
       </c>
@@ -11069,8 +14643,17 @@
       <c r="I190">
         <v>0.116948127746582</v>
       </c>
-    </row>
-    <row r="191" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J190" t="s">
+        <v>690</v>
+      </c>
+      <c r="K190" t="s">
+        <v>497</v>
+      </c>
+      <c r="L190">
+        <v>16.097999999999999</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A191" s="7" t="s">
         <v>441</v>
       </c>
@@ -11098,8 +14681,17 @@
       <c r="I191">
         <v>0.119216680526733</v>
       </c>
-    </row>
-    <row r="192" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J191" t="s">
+        <v>691</v>
+      </c>
+      <c r="K191" t="s">
+        <v>498</v>
+      </c>
+      <c r="L191">
+        <v>15.481</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A192" s="10" t="s">
         <v>442</v>
       </c>
@@ -11127,8 +14719,17 @@
       <c r="I192">
         <v>8.1073417663574201</v>
       </c>
-    </row>
-    <row r="193" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J192" t="s">
+        <v>692</v>
+      </c>
+      <c r="K192" t="s">
+        <v>173</v>
+      </c>
+      <c r="L192">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A193" s="7" t="s">
         <v>443</v>
       </c>
@@ -11156,8 +14757,17 @@
       <c r="I193">
         <v>8.0363807678222603</v>
       </c>
-    </row>
-    <row r="194" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J193" t="s">
+        <v>693</v>
+      </c>
+      <c r="K193" t="s">
+        <v>173</v>
+      </c>
+      <c r="L193">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A194" s="10" t="s">
         <v>444</v>
       </c>
@@ -11185,8 +14795,17 @@
       <c r="I194">
         <v>2.2228240966796799E-2</v>
       </c>
-    </row>
-    <row r="195" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J194" t="s">
+        <v>694</v>
+      </c>
+      <c r="K194" t="s">
+        <v>497</v>
+      </c>
+      <c r="L194">
+        <v>0.128</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A195" s="7" t="s">
         <v>445</v>
       </c>
@@ -11214,8 +14833,17 @@
       <c r="I195">
         <v>0.113598823547363</v>
       </c>
-    </row>
-    <row r="196" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J195" t="s">
+        <v>695</v>
+      </c>
+      <c r="K195" t="s">
+        <v>497</v>
+      </c>
+      <c r="L195">
+        <v>15.534000000000001</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A196" s="10" t="s">
         <v>446</v>
       </c>
@@ -11243,8 +14871,17 @@
       <c r="I196">
         <v>0.116568088531494</v>
       </c>
-    </row>
-    <row r="197" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J196" t="s">
+        <v>696</v>
+      </c>
+      <c r="K196" t="s">
+        <v>497</v>
+      </c>
+      <c r="L196">
+        <v>15.747999999999999</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A197" s="7" t="s">
         <v>447</v>
       </c>
@@ -11272,8 +14909,17 @@
       <c r="I197">
         <v>0.11711072921752901</v>
       </c>
-    </row>
-    <row r="198" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J197" t="s">
+        <v>697</v>
+      </c>
+      <c r="K197" t="s">
+        <v>497</v>
+      </c>
+      <c r="L197">
+        <v>60.073999999999998</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A198" s="10" t="s">
         <v>448</v>
       </c>
@@ -11301,8 +14947,17 @@
       <c r="I198">
         <v>0.116960048675537</v>
       </c>
-    </row>
-    <row r="199" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J198" t="s">
+        <v>698</v>
+      </c>
+      <c r="K198" t="s">
+        <v>497</v>
+      </c>
+      <c r="L198">
+        <v>15.144</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A199" s="7" t="s">
         <v>449</v>
       </c>
@@ -11330,8 +14985,17 @@
       <c r="I199">
         <v>10.3725688457489</v>
       </c>
-    </row>
-    <row r="200" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J199" t="s">
+        <v>699</v>
+      </c>
+      <c r="K199" t="s">
+        <v>497</v>
+      </c>
+      <c r="L199">
+        <v>67.650999999999996</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A200" s="10" t="s">
         <v>450</v>
       </c>
@@ -11359,8 +15023,17 @@
       <c r="I200">
         <v>2.2059679031372001E-2</v>
       </c>
-    </row>
-    <row r="201" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J200" t="s">
+        <v>700</v>
+      </c>
+      <c r="K200" t="s">
+        <v>497</v>
+      </c>
+      <c r="L200">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A201" s="7" t="s">
         <v>451</v>
       </c>
@@ -11388,8 +15061,17 @@
       <c r="I201">
         <v>0.75850510597229004</v>
       </c>
-    </row>
-    <row r="202" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J201" t="s">
+        <v>701</v>
+      </c>
+      <c r="K201" t="s">
+        <v>497</v>
+      </c>
+      <c r="L201">
+        <v>9.3689999999999998</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A202" s="10" t="s">
         <v>452</v>
       </c>
@@ -11417,8 +15099,17 @@
       <c r="I202">
         <v>8.6221694946288993E-3</v>
       </c>
-    </row>
-    <row r="203" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J202" t="s">
+        <v>702</v>
+      </c>
+      <c r="K202" t="s">
+        <v>498</v>
+      </c>
+      <c r="L202">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A203" s="7" t="s">
         <v>453</v>
       </c>
@@ -11446,8 +15137,17 @@
       <c r="I203">
         <v>1.3046307563781701</v>
       </c>
-    </row>
-    <row r="204" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J203" t="s">
+        <v>703</v>
+      </c>
+      <c r="K203" t="s">
+        <v>497</v>
+      </c>
+      <c r="L203">
+        <v>9.0129999999999999</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A204" s="10" t="s">
         <v>454</v>
       </c>
@@ -11475,8 +15175,17 @@
       <c r="I204">
         <v>0.75070405006408603</v>
       </c>
-    </row>
-    <row r="205" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J204" t="s">
+        <v>704</v>
+      </c>
+      <c r="K204" t="s">
+        <v>498</v>
+      </c>
+      <c r="L204">
+        <v>9.2249999999999996</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A205" s="7" t="s">
         <v>455</v>
       </c>
@@ -11504,8 +15213,17 @@
       <c r="I205">
         <v>0.122172594070434</v>
       </c>
-    </row>
-    <row r="206" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J205" t="s">
+        <v>705</v>
+      </c>
+      <c r="K205" t="s">
+        <v>497</v>
+      </c>
+      <c r="L205">
+        <v>15.917</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A206" s="10" t="s">
         <v>456</v>
       </c>
@@ -11533,8 +15251,17 @@
       <c r="I206">
         <v>6.2417268753051702E-2</v>
       </c>
-    </row>
-    <row r="207" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J206" t="s">
+        <v>706</v>
+      </c>
+      <c r="K206" t="s">
+        <v>498</v>
+      </c>
+      <c r="L206">
+        <v>2.0960000000000001</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A207" s="7" t="s">
         <v>457</v>
       </c>
@@ -11562,8 +15289,17 @@
       <c r="I207">
         <v>5.80039024353027E-2</v>
       </c>
-    </row>
-    <row r="208" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J207" t="s">
+        <v>707</v>
+      </c>
+      <c r="K207" t="s">
+        <v>498</v>
+      </c>
+      <c r="L207">
+        <v>1.6639999999999999</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A208" s="10" t="s">
         <v>458</v>
       </c>
@@ -11591,8 +15327,17 @@
       <c r="I208">
         <v>0.74081039428710904</v>
       </c>
-    </row>
-    <row r="209" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J208" t="s">
+        <v>708</v>
+      </c>
+      <c r="K208" t="s">
+        <v>498</v>
+      </c>
+      <c r="L208">
+        <v>21.257000000000001</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A209" s="7" t="s">
         <v>459</v>
       </c>
@@ -11620,8 +15365,17 @@
       <c r="I209">
         <v>0.11642408370971601</v>
       </c>
-    </row>
-    <row r="210" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J209" t="s">
+        <v>709</v>
+      </c>
+      <c r="K209" t="s">
+        <v>498</v>
+      </c>
+      <c r="L209">
+        <v>31.742999999999999</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A210" s="10" t="s">
         <v>460</v>
       </c>
@@ -11649,8 +15403,17 @@
       <c r="I210">
         <v>0.119226694107055</v>
       </c>
-    </row>
-    <row r="211" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J210" t="s">
+        <v>710</v>
+      </c>
+      <c r="K210" t="s">
+        <v>498</v>
+      </c>
+      <c r="L210">
+        <v>18.033999999999999</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A211" s="7" t="s">
         <v>461</v>
       </c>
@@ -11678,8 +15441,17 @@
       <c r="I211">
         <v>0.77145075798034601</v>
       </c>
-    </row>
-    <row r="212" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J211" t="s">
+        <v>711</v>
+      </c>
+      <c r="K211" t="s">
+        <v>497</v>
+      </c>
+      <c r="L211">
+        <v>9.3960000000000008</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A212" s="10" t="s">
         <v>462</v>
       </c>
@@ -11707,8 +15479,17 @@
       <c r="I212">
         <v>1.2113094329833899E-2</v>
       </c>
-    </row>
-    <row r="213" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J212" t="s">
+        <v>712</v>
+      </c>
+      <c r="K212" t="s">
+        <v>498</v>
+      </c>
+      <c r="L212">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A213" s="7" t="s">
         <v>463</v>
       </c>
@@ -11736,8 +15517,17 @@
       <c r="I213">
         <v>0.736497402191162</v>
       </c>
-    </row>
-    <row r="214" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J213" t="s">
+        <v>713</v>
+      </c>
+      <c r="K213" t="s">
+        <v>498</v>
+      </c>
+      <c r="L213">
+        <v>8.9459999999999997</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A214" s="10" t="s">
         <v>464</v>
       </c>
@@ -11765,8 +15555,17 @@
       <c r="I214">
         <v>0.73891758918762196</v>
       </c>
-    </row>
-    <row r="215" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J214" t="s">
+        <v>714</v>
+      </c>
+      <c r="K214" t="s">
+        <v>498</v>
+      </c>
+      <c r="L214">
+        <v>11.537000000000001</v>
+      </c>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A215" s="7" t="s">
         <v>465</v>
       </c>
@@ -11794,8 +15593,17 @@
       <c r="I215">
         <v>6.00049495697021E-2</v>
       </c>
-    </row>
-    <row r="216" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J215" t="s">
+        <v>715</v>
+      </c>
+      <c r="K215" t="s">
+        <v>498</v>
+      </c>
+      <c r="L215">
+        <v>1.708</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A216" s="10" t="s">
         <v>466</v>
       </c>
@@ -11823,8 +15631,17 @@
       <c r="I216">
         <v>0.13203740119933999</v>
       </c>
-    </row>
-    <row r="217" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J216" t="s">
+        <v>716</v>
+      </c>
+      <c r="K216" t="s">
+        <v>498</v>
+      </c>
+      <c r="L216">
+        <v>15.978999999999999</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A217" s="7" t="s">
         <v>467</v>
       </c>
@@ -11852,8 +15669,17 @@
       <c r="I217">
         <v>8.0429515838622994</v>
       </c>
-    </row>
-    <row r="218" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J217" t="s">
+        <v>717</v>
+      </c>
+      <c r="K217" t="s">
+        <v>173</v>
+      </c>
+      <c r="L217">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A218" s="10" t="s">
         <v>468</v>
       </c>
@@ -11881,8 +15707,17 @@
       <c r="I218">
         <v>7.9874482154846103</v>
       </c>
-    </row>
-    <row r="219" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J218" t="s">
+        <v>718</v>
+      </c>
+      <c r="K218" t="s">
+        <v>173</v>
+      </c>
+      <c r="L218">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A219" s="7" t="s">
         <v>469</v>
       </c>
@@ -11910,8 +15745,17 @@
       <c r="I219">
         <v>100.045338630676</v>
       </c>
-    </row>
-    <row r="220" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J219" t="s">
+        <v>719</v>
+      </c>
+      <c r="K219" t="s">
+        <v>173</v>
+      </c>
+      <c r="L219">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A220" s="10" t="s">
         <v>470</v>
       </c>
@@ -11939,8 +15783,17 @@
       <c r="I220">
         <v>100.057497739791</v>
       </c>
-    </row>
-    <row r="221" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J220" t="s">
+        <v>720</v>
+      </c>
+      <c r="K220" t="s">
+        <v>173</v>
+      </c>
+      <c r="L220">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A221" s="7" t="s">
         <v>471</v>
       </c>
@@ -11968,8 +15821,17 @@
       <c r="I221">
         <v>100.041392326354</v>
       </c>
-    </row>
-    <row r="222" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J221" t="s">
+        <v>721</v>
+      </c>
+      <c r="K221" t="s">
+        <v>173</v>
+      </c>
+      <c r="L221">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A222" s="10" t="s">
         <v>472</v>
       </c>
@@ -11997,8 +15859,17 @@
       <c r="I222">
         <v>2.8535127639770501E-2</v>
       </c>
-    </row>
-    <row r="223" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J222" t="s">
+        <v>722</v>
+      </c>
+      <c r="K222" t="s">
+        <v>497</v>
+      </c>
+      <c r="L222">
+        <v>0.33400000000000002</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A223" s="7" t="s">
         <v>473</v>
       </c>
@@ -12026,8 +15897,17 @@
       <c r="I223">
         <v>100.053363323211</v>
       </c>
-    </row>
-    <row r="224" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J223" t="s">
+        <v>723</v>
+      </c>
+      <c r="K223" t="s">
+        <v>173</v>
+      </c>
+      <c r="L223">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A224" s="10" t="s">
         <v>474</v>
       </c>
@@ -12055,8 +15935,17 @@
       <c r="I224">
         <v>100.045784235</v>
       </c>
-    </row>
-    <row r="225" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J224" t="s">
+        <v>724</v>
+      </c>
+      <c r="K224" t="s">
+        <v>173</v>
+      </c>
+      <c r="L224">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A225" s="7" t="s">
         <v>475</v>
       </c>
@@ -12084,8 +15973,17 @@
       <c r="I225">
         <v>100.048868894577</v>
       </c>
-    </row>
-    <row r="226" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J225" t="s">
+        <v>725</v>
+      </c>
+      <c r="K225" t="s">
+        <v>173</v>
+      </c>
+      <c r="L225">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A226" s="10" t="s">
         <v>476</v>
       </c>
@@ -12113,8 +16011,17 @@
       <c r="I226">
         <v>100.044727563858</v>
       </c>
-    </row>
-    <row r="227" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J226" t="s">
+        <v>726</v>
+      </c>
+      <c r="K226" t="s">
+        <v>173</v>
+      </c>
+      <c r="L226">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A227" s="7" t="s">
         <v>477</v>
       </c>
@@ -12142,8 +16049,17 @@
       <c r="I227">
         <v>100.039130210876</v>
       </c>
-    </row>
-    <row r="228" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J227" t="s">
+        <v>727</v>
+      </c>
+      <c r="K227" t="s">
+        <v>173</v>
+      </c>
+      <c r="L227">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A228" s="10" t="s">
         <v>478</v>
       </c>
@@ -12171,8 +16087,17 @@
       <c r="I228">
         <v>100.04731726646401</v>
       </c>
-    </row>
-    <row r="229" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J228" t="s">
+        <v>728</v>
+      </c>
+      <c r="K228" t="s">
+        <v>173</v>
+      </c>
+      <c r="L228">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A229" s="7" t="s">
         <v>479</v>
       </c>
@@ -12200,8 +16125,17 @@
       <c r="I229">
         <v>2.94163227081298E-2</v>
       </c>
-    </row>
-    <row r="230" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J229" t="s">
+        <v>729</v>
+      </c>
+      <c r="K229" t="s">
+        <v>497</v>
+      </c>
+      <c r="L229">
+        <v>8.6999999999999994E-2</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A230" s="10" t="s">
         <v>480</v>
       </c>
@@ -12229,8 +16163,17 @@
       <c r="I230">
         <v>0.119300603866577</v>
       </c>
-    </row>
-    <row r="231" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J230" t="s">
+        <v>730</v>
+      </c>
+      <c r="K230" t="s">
+        <v>497</v>
+      </c>
+      <c r="L230">
+        <v>58.322000000000003</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A231" s="7" t="s">
         <v>481</v>
       </c>
@@ -12258,8 +16201,17 @@
       <c r="I231">
         <v>6.1893463134765597E-2</v>
       </c>
-    </row>
-    <row r="232" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J231" t="s">
+        <v>731</v>
+      </c>
+      <c r="K231" t="s">
+        <v>498</v>
+      </c>
+      <c r="L231">
+        <v>1.742</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A232" s="10" t="s">
         <v>482</v>
       </c>
@@ -12287,8 +16239,17 @@
       <c r="I232">
         <v>0.72359490394592196</v>
       </c>
-    </row>
-    <row r="233" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J232" t="s">
+        <v>732</v>
+      </c>
+      <c r="K232" t="s">
+        <v>498</v>
+      </c>
+      <c r="L232">
+        <v>9.4939999999999998</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A233" s="7" t="s">
         <v>483</v>
       </c>
@@ -12316,8 +16277,17 @@
       <c r="I233">
         <v>0.11482429504394499</v>
       </c>
-    </row>
-    <row r="234" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J233" t="s">
+        <v>733</v>
+      </c>
+      <c r="K233" t="s">
+        <v>498</v>
+      </c>
+      <c r="L233">
+        <v>15.724</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A234" s="10" t="s">
         <v>484</v>
       </c>
@@ -12345,8 +16315,17 @@
       <c r="I234">
         <v>11.814095258712699</v>
       </c>
-    </row>
-    <row r="235" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J234" t="s">
+        <v>734</v>
+      </c>
+      <c r="K234" t="s">
+        <v>497</v>
+      </c>
+      <c r="L234">
+        <v>83.8</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A235" s="7" t="s">
         <v>485</v>
       </c>
@@ -12374,8 +16353,17 @@
       <c r="I235">
         <v>0.71333432197570801</v>
       </c>
-    </row>
-    <row r="236" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J235" t="s">
+        <v>735</v>
+      </c>
+      <c r="K235" t="s">
+        <v>498</v>
+      </c>
+      <c r="L235">
+        <v>22.172999999999998</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A236" s="10" t="s">
         <v>486</v>
       </c>
@@ -12403,8 +16391,17 @@
       <c r="I236">
         <v>0.72495794296264604</v>
       </c>
-    </row>
-    <row r="237" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J236" t="s">
+        <v>736</v>
+      </c>
+      <c r="K236" t="s">
+        <v>498</v>
+      </c>
+      <c r="L236">
+        <v>21.673999999999999</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A237" s="7" t="s">
         <v>487</v>
       </c>
@@ -12432,8 +16429,17 @@
       <c r="I237">
         <v>10.506611585617</v>
       </c>
-    </row>
-    <row r="238" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J237" t="s">
+        <v>737</v>
+      </c>
+      <c r="K237" t="s">
+        <v>497</v>
+      </c>
+      <c r="L237">
+        <v>49.466000000000001</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A238" s="10" t="s">
         <v>488</v>
       </c>
@@ -12461,8 +16467,17 @@
       <c r="I238">
         <v>11.802000522613501</v>
       </c>
-    </row>
-    <row r="239" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J238" t="s">
+        <v>738</v>
+      </c>
+      <c r="K238" t="s">
+        <v>497</v>
+      </c>
+      <c r="L238">
+        <v>55.52</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A239" s="7" t="s">
         <v>489</v>
       </c>
@@ -12490,8 +16505,17 @@
       <c r="I239">
         <v>7.9867048263549796</v>
       </c>
-    </row>
-    <row r="240" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J239" t="s">
+        <v>739</v>
+      </c>
+      <c r="K239" t="s">
+        <v>173</v>
+      </c>
+      <c r="L239">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A240" s="1" t="s">
         <v>490</v>
       </c>
@@ -12519,8 +16543,17 @@
       <c r="I240">
         <v>0.115933895111083</v>
       </c>
-    </row>
-    <row r="241" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J240" t="s">
+        <v>740</v>
+      </c>
+      <c r="K240" t="s">
+        <v>498</v>
+      </c>
+      <c r="L240">
+        <v>16.396000000000001</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A241" t="s">
         <v>491</v>
       </c>
@@ -12547,6 +16580,15 @@
       </c>
       <c r="I241">
         <v>10.4824538230896</v>
+      </c>
+      <c r="J241" t="s">
+        <v>741</v>
+      </c>
+      <c r="K241" t="s">
+        <v>497</v>
+      </c>
+      <c r="L241">
+        <v>61.933999999999997</v>
       </c>
     </row>
   </sheetData>
